--- a/SAL_JIG/SAL_JIG_CS1/Docs/sal_cs1_trim_sequence_250226.xlsx
+++ b/SAL_JIG/SAL_JIG_CS1/Docs/sal_cs1_trim_sequence_250226.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\SAL_JIG\SAL_JIG_CS1\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E437A779-C0AC-4DC2-AF70-F140EEE9373E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FED0CD0-B471-43C6-B8DA-269487243DAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3278,23 +3278,23 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="18">
     <numFmt numFmtId="176" formatCode="0.0"/>
-    <numFmt numFmtId="179" formatCode="0&quot;mA&quot;"/>
-    <numFmt numFmtId="180" formatCode="0&quot;uA&quot;"/>
-    <numFmt numFmtId="181" formatCode="0&quot;V&quot;"/>
-    <numFmt numFmtId="182" formatCode="0.0000&quot;mV&quot;"/>
-    <numFmt numFmtId="183" formatCode="0.000&quot;V&quot;"/>
-    <numFmt numFmtId="184" formatCode="0.000&quot;uA&quot;"/>
-    <numFmt numFmtId="185" formatCode="0.000&quot;mV&quot;"/>
-    <numFmt numFmtId="186" formatCode="0.00&quot;mV&quot;"/>
-    <numFmt numFmtId="187" formatCode="0&quot;Ω&quot;"/>
-    <numFmt numFmtId="188" formatCode="0.0&quot;Ω&quot;"/>
-    <numFmt numFmtId="189" formatCode="0.0000&quot;V&quot;"/>
-    <numFmt numFmtId="190" formatCode="0.000&quot;mA&quot;"/>
-    <numFmt numFmtId="191" formatCode="0.0000&quot;uA&quot;"/>
-    <numFmt numFmtId="192" formatCode="0.0&quot;mA&quot;"/>
-    <numFmt numFmtId="193" formatCode="0&quot;uV&quot;"/>
-    <numFmt numFmtId="194" formatCode="0.000&quot;uV&quot;"/>
-    <numFmt numFmtId="195" formatCode="0.0%"/>
+    <numFmt numFmtId="177" formatCode="0&quot;mA&quot;"/>
+    <numFmt numFmtId="178" formatCode="0&quot;uA&quot;"/>
+    <numFmt numFmtId="179" formatCode="0&quot;V&quot;"/>
+    <numFmt numFmtId="180" formatCode="0.0000&quot;mV&quot;"/>
+    <numFmt numFmtId="181" formatCode="0.000&quot;V&quot;"/>
+    <numFmt numFmtId="182" formatCode="0.000&quot;uA&quot;"/>
+    <numFmt numFmtId="183" formatCode="0.000&quot;mV&quot;"/>
+    <numFmt numFmtId="184" formatCode="0.00&quot;mV&quot;"/>
+    <numFmt numFmtId="185" formatCode="0&quot;Ω&quot;"/>
+    <numFmt numFmtId="186" formatCode="0.0&quot;Ω&quot;"/>
+    <numFmt numFmtId="187" formatCode="0.0000&quot;V&quot;"/>
+    <numFmt numFmtId="188" formatCode="0.000&quot;mA&quot;"/>
+    <numFmt numFmtId="189" formatCode="0.0000&quot;uA&quot;"/>
+    <numFmt numFmtId="190" formatCode="0.0&quot;mA&quot;"/>
+    <numFmt numFmtId="191" formatCode="0&quot;uV&quot;"/>
+    <numFmt numFmtId="192" formatCode="0.000&quot;uV&quot;"/>
+    <numFmt numFmtId="193" formatCode="0.0%"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -4439,11 +4439,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="5" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="5" applyFill="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4460,13 +4466,16 @@
     <xf numFmtId="184" fontId="1" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="185" fontId="1" fillId="7" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="185" fontId="1" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="186" fontId="1" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="1" fillId="7" borderId="0" xfId="5" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="187" fontId="1" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
@@ -4475,10 +4484,10 @@
     <xf numFmtId="188" fontId="1" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="189" fontId="1" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="189" fontId="1" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="190" fontId="1" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
@@ -4487,19 +4496,10 @@
     <xf numFmtId="191" fontId="1" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="192" fontId="1" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="193" fontId="1" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="5" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="194" fontId="1" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="192" fontId="1" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -4547,6 +4547,9 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="193" fontId="0" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4555,6 +4558,12 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4568,32 +4577,65 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -4606,57 +4648,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4676,14 +4667,23 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4693,6 +4693,60 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -4706,62 +4760,8 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="195" fontId="0" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -5303,20 +5303,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:35" ht="15" customHeight="1">
-      <c r="B2" s="157" t="s">
+      <c r="B2" s="158" t="s">
         <v>314</v>
       </c>
-      <c r="C2" s="158" t="s">
+      <c r="C2" s="159" t="s">
         <v>315</v>
       </c>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="157" t="s">
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="158" t="s">
         <v>316</v>
       </c>
-      <c r="G2" s="157"/>
-      <c r="H2" s="157"/>
-      <c r="I2" s="157" t="s">
+      <c r="G2" s="158"/>
+      <c r="H2" s="158"/>
+      <c r="I2" s="158" t="s">
         <v>317</v>
       </c>
       <c r="O2" s="68">
@@ -5369,7 +5369,7 @@
       </c>
     </row>
     <row r="3" spans="2:35" ht="23.25">
-      <c r="B3" s="157"/>
+      <c r="B3" s="158"/>
       <c r="C3" s="67" t="s">
         <v>318</v>
       </c>
@@ -5388,7 +5388,7 @@
       <c r="H3" s="67" t="s">
         <v>320</v>
       </c>
-      <c r="I3" s="157"/>
+      <c r="I3" s="158"/>
       <c r="L3" s="69" t="s">
         <v>323</v>
       </c>
@@ -5644,10 +5644,10 @@
       <c r="L7" s="69" t="s">
         <v>338</v>
       </c>
-      <c r="M7" s="159" t="s">
+      <c r="M7" s="160" t="s">
         <v>339</v>
       </c>
-      <c r="N7" s="159"/>
+      <c r="N7" s="160"/>
       <c r="O7" s="68">
         <v>1</v>
       </c>
@@ -8926,12 +8926,12 @@
       <c r="W2" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="X2" s="161" t="s">
+      <c r="X2" s="164" t="s">
         <v>49</v>
       </c>
-      <c r="Y2" s="162"/>
-      <c r="Z2" s="162"/>
-      <c r="AA2" s="163"/>
+      <c r="Y2" s="165"/>
+      <c r="Z2" s="165"/>
+      <c r="AA2" s="166"/>
       <c r="AB2" s="3" t="s">
         <v>50</v>
       </c>
@@ -8946,12 +8946,12 @@
       <c r="E3" s="2"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="164" t="s">
+      <c r="H3" s="168" t="s">
         <v>52</v>
       </c>
-      <c r="I3" s="164"/>
-      <c r="J3" s="164"/>
-      <c r="K3" s="164"/>
+      <c r="I3" s="168"/>
+      <c r="J3" s="168"/>
+      <c r="K3" s="168"/>
       <c r="L3" s="3" t="s">
         <v>53</v>
       </c>
@@ -9049,19 +9049,19 @@
       <c r="P4" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="Q4" s="160" t="s">
+      <c r="Q4" s="163" t="s">
         <v>67</v>
       </c>
-      <c r="R4" s="160"/>
-      <c r="S4" s="160"/>
-      <c r="T4" s="160" t="s">
+      <c r="R4" s="163"/>
+      <c r="S4" s="163"/>
+      <c r="T4" s="163" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="160"/>
-      <c r="V4" s="160" t="s">
+      <c r="U4" s="163"/>
+      <c r="V4" s="163" t="s">
         <v>69</v>
       </c>
-      <c r="W4" s="160"/>
+      <c r="W4" s="163"/>
       <c r="X4" s="6">
         <v>0</v>
       </c>
@@ -9206,18 +9206,18 @@
       <c r="M6" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="N6" s="160" t="s">
+      <c r="N6" s="163" t="s">
         <v>88</v>
       </c>
-      <c r="O6" s="160"/>
-      <c r="P6" s="160"/>
-      <c r="Q6" s="160"/>
-      <c r="R6" s="160"/>
-      <c r="S6" s="160"/>
-      <c r="T6" s="160"/>
-      <c r="U6" s="160"/>
-      <c r="V6" s="160"/>
-      <c r="W6" s="160"/>
+      <c r="O6" s="163"/>
+      <c r="P6" s="163"/>
+      <c r="Q6" s="163"/>
+      <c r="R6" s="163"/>
+      <c r="S6" s="163"/>
+      <c r="T6" s="163"/>
+      <c r="U6" s="163"/>
+      <c r="V6" s="163"/>
+      <c r="W6" s="163"/>
       <c r="X6" s="6">
         <v>0</v>
       </c>
@@ -9275,18 +9275,18 @@
       <c r="M7" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="N7" s="160" t="s">
+      <c r="N7" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="O7" s="160"/>
-      <c r="P7" s="160"/>
-      <c r="Q7" s="160"/>
-      <c r="R7" s="160"/>
-      <c r="S7" s="160"/>
-      <c r="T7" s="160"/>
-      <c r="U7" s="160"/>
-      <c r="V7" s="160"/>
-      <c r="W7" s="160"/>
+      <c r="O7" s="163"/>
+      <c r="P7" s="163"/>
+      <c r="Q7" s="163"/>
+      <c r="R7" s="163"/>
+      <c r="S7" s="163"/>
+      <c r="T7" s="163"/>
+      <c r="U7" s="163"/>
+      <c r="V7" s="163"/>
+      <c r="W7" s="163"/>
       <c r="X7" s="6">
         <v>0</v>
       </c>
@@ -9362,12 +9362,12 @@
       <c r="S8" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="T8" s="160" t="s">
+      <c r="T8" s="163" t="s">
         <v>103</v>
       </c>
-      <c r="U8" s="160"/>
-      <c r="V8" s="160"/>
-      <c r="W8" s="160"/>
+      <c r="U8" s="163"/>
+      <c r="V8" s="163"/>
+      <c r="W8" s="163"/>
       <c r="X8" s="6">
         <v>0</v>
       </c>
@@ -9443,14 +9443,14 @@
       <c r="S9" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="T9" s="160" t="s">
+      <c r="T9" s="163" t="s">
         <v>109</v>
       </c>
-      <c r="U9" s="160"/>
-      <c r="V9" s="160" t="s">
+      <c r="U9" s="163"/>
+      <c r="V9" s="163" t="s">
         <v>110</v>
       </c>
-      <c r="W9" s="160"/>
+      <c r="W9" s="163"/>
       <c r="X9" s="6">
         <v>0</v>
       </c>
@@ -9508,18 +9508,18 @@
       <c r="M10" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="N10" s="160" t="s">
+      <c r="N10" s="163" t="s">
         <v>114</v>
       </c>
-      <c r="O10" s="160"/>
-      <c r="P10" s="160"/>
-      <c r="Q10" s="160"/>
-      <c r="R10" s="160"/>
-      <c r="S10" s="160"/>
-      <c r="T10" s="160"/>
-      <c r="U10" s="160"/>
-      <c r="V10" s="160"/>
-      <c r="W10" s="160"/>
+      <c r="O10" s="163"/>
+      <c r="P10" s="163"/>
+      <c r="Q10" s="163"/>
+      <c r="R10" s="163"/>
+      <c r="S10" s="163"/>
+      <c r="T10" s="163"/>
+      <c r="U10" s="163"/>
+      <c r="V10" s="163"/>
+      <c r="W10" s="163"/>
       <c r="X10" s="6">
         <v>0</v>
       </c>
@@ -9577,18 +9577,18 @@
       <c r="M11" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="N11" s="160" t="s">
+      <c r="N11" s="163" t="s">
         <v>117</v>
       </c>
-      <c r="O11" s="160"/>
-      <c r="P11" s="160"/>
-      <c r="Q11" s="160"/>
-      <c r="R11" s="160"/>
-      <c r="S11" s="160"/>
-      <c r="T11" s="160"/>
-      <c r="U11" s="160"/>
-      <c r="V11" s="160"/>
-      <c r="W11" s="160"/>
+      <c r="O11" s="163"/>
+      <c r="P11" s="163"/>
+      <c r="Q11" s="163"/>
+      <c r="R11" s="163"/>
+      <c r="S11" s="163"/>
+      <c r="T11" s="163"/>
+      <c r="U11" s="163"/>
+      <c r="V11" s="163"/>
+      <c r="W11" s="163"/>
       <c r="X11" s="6">
         <v>0</v>
       </c>
@@ -9640,20 +9640,20 @@
       <c r="K12" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="L12" s="160" t="s">
+      <c r="L12" s="163" t="s">
         <v>120</v>
       </c>
-      <c r="M12" s="160"/>
-      <c r="N12" s="160"/>
-      <c r="O12" s="160"/>
-      <c r="P12" s="160"/>
-      <c r="Q12" s="160"/>
-      <c r="R12" s="160"/>
-      <c r="S12" s="160"/>
-      <c r="T12" s="160"/>
-      <c r="U12" s="160"/>
-      <c r="V12" s="160"/>
-      <c r="W12" s="160"/>
+      <c r="M12" s="163"/>
+      <c r="N12" s="163"/>
+      <c r="O12" s="163"/>
+      <c r="P12" s="163"/>
+      <c r="Q12" s="163"/>
+      <c r="R12" s="163"/>
+      <c r="S12" s="163"/>
+      <c r="T12" s="163"/>
+      <c r="U12" s="163"/>
+      <c r="V12" s="163"/>
+      <c r="W12" s="163"/>
       <c r="X12" s="6">
         <v>0</v>
       </c>
@@ -9705,20 +9705,20 @@
       <c r="K13" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="L13" s="160" t="s">
+      <c r="L13" s="163" t="s">
         <v>123</v>
       </c>
-      <c r="M13" s="160"/>
-      <c r="N13" s="160"/>
-      <c r="O13" s="160"/>
-      <c r="P13" s="160"/>
-      <c r="Q13" s="160"/>
-      <c r="R13" s="160"/>
-      <c r="S13" s="160"/>
-      <c r="T13" s="160"/>
-      <c r="U13" s="160"/>
-      <c r="V13" s="160"/>
-      <c r="W13" s="160"/>
+      <c r="M13" s="163"/>
+      <c r="N13" s="163"/>
+      <c r="O13" s="163"/>
+      <c r="P13" s="163"/>
+      <c r="Q13" s="163"/>
+      <c r="R13" s="163"/>
+      <c r="S13" s="163"/>
+      <c r="T13" s="163"/>
+      <c r="U13" s="163"/>
+      <c r="V13" s="163"/>
+      <c r="W13" s="163"/>
       <c r="X13" s="6">
         <v>0</v>
       </c>
@@ -9770,20 +9770,20 @@
       <c r="K14" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="L14" s="160" t="s">
+      <c r="L14" s="163" t="s">
         <v>126</v>
       </c>
-      <c r="M14" s="160"/>
-      <c r="N14" s="160"/>
-      <c r="O14" s="160"/>
-      <c r="P14" s="160"/>
-      <c r="Q14" s="160"/>
-      <c r="R14" s="160"/>
-      <c r="S14" s="160"/>
-      <c r="T14" s="160"/>
-      <c r="U14" s="160"/>
-      <c r="V14" s="160"/>
-      <c r="W14" s="160"/>
+      <c r="M14" s="163"/>
+      <c r="N14" s="163"/>
+      <c r="O14" s="163"/>
+      <c r="P14" s="163"/>
+      <c r="Q14" s="163"/>
+      <c r="R14" s="163"/>
+      <c r="S14" s="163"/>
+      <c r="T14" s="163"/>
+      <c r="U14" s="163"/>
+      <c r="V14" s="163"/>
+      <c r="W14" s="163"/>
       <c r="X14" s="6">
         <v>0</v>
       </c>
@@ -9835,24 +9835,24 @@
       <c r="K15" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="L15" s="160" t="s">
+      <c r="L15" s="163" t="s">
         <v>129</v>
       </c>
-      <c r="M15" s="160"/>
-      <c r="N15" s="160"/>
-      <c r="O15" s="160"/>
-      <c r="P15" s="160" t="s">
+      <c r="M15" s="163"/>
+      <c r="N15" s="163"/>
+      <c r="O15" s="163"/>
+      <c r="P15" s="163" t="s">
         <v>130</v>
       </c>
-      <c r="Q15" s="160"/>
-      <c r="R15" s="160"/>
-      <c r="S15" s="160"/>
-      <c r="T15" s="160" t="s">
+      <c r="Q15" s="163"/>
+      <c r="R15" s="163"/>
+      <c r="S15" s="163"/>
+      <c r="T15" s="163" t="s">
         <v>131</v>
       </c>
-      <c r="U15" s="160"/>
-      <c r="V15" s="160"/>
-      <c r="W15" s="160"/>
+      <c r="U15" s="163"/>
+      <c r="V15" s="163"/>
+      <c r="W15" s="163"/>
       <c r="X15" s="6">
         <v>0</v>
       </c>
@@ -9904,20 +9904,20 @@
       <c r="K16" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="L16" s="160" t="s">
+      <c r="L16" s="163" t="s">
         <v>135</v>
       </c>
-      <c r="M16" s="160"/>
-      <c r="N16" s="160"/>
-      <c r="O16" s="160"/>
-      <c r="P16" s="160"/>
-      <c r="Q16" s="160"/>
-      <c r="R16" s="160"/>
-      <c r="S16" s="160"/>
-      <c r="T16" s="160"/>
-      <c r="U16" s="160"/>
-      <c r="V16" s="160"/>
-      <c r="W16" s="160"/>
+      <c r="M16" s="163"/>
+      <c r="N16" s="163"/>
+      <c r="O16" s="163"/>
+      <c r="P16" s="163"/>
+      <c r="Q16" s="163"/>
+      <c r="R16" s="163"/>
+      <c r="S16" s="163"/>
+      <c r="T16" s="163"/>
+      <c r="U16" s="163"/>
+      <c r="V16" s="163"/>
+      <c r="W16" s="163"/>
       <c r="X16" s="6">
         <v>0</v>
       </c>
@@ -9969,20 +9969,20 @@
       <c r="K17" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="L17" s="160" t="s">
+      <c r="L17" s="163" t="s">
         <v>139</v>
       </c>
-      <c r="M17" s="160"/>
-      <c r="N17" s="160"/>
-      <c r="O17" s="160"/>
-      <c r="P17" s="160"/>
-      <c r="Q17" s="160"/>
-      <c r="R17" s="160"/>
-      <c r="S17" s="160"/>
-      <c r="T17" s="160"/>
-      <c r="U17" s="160"/>
-      <c r="V17" s="160"/>
-      <c r="W17" s="160"/>
+      <c r="M17" s="163"/>
+      <c r="N17" s="163"/>
+      <c r="O17" s="163"/>
+      <c r="P17" s="163"/>
+      <c r="Q17" s="163"/>
+      <c r="R17" s="163"/>
+      <c r="S17" s="163"/>
+      <c r="T17" s="163"/>
+      <c r="U17" s="163"/>
+      <c r="V17" s="163"/>
+      <c r="W17" s="163"/>
       <c r="X17" s="6">
         <v>0</v>
       </c>
@@ -10034,20 +10034,20 @@
       <c r="K18" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="L18" s="160" t="s">
+      <c r="L18" s="163" t="s">
         <v>142</v>
       </c>
-      <c r="M18" s="160"/>
-      <c r="N18" s="160"/>
-      <c r="O18" s="160"/>
-      <c r="P18" s="160"/>
-      <c r="Q18" s="160"/>
-      <c r="R18" s="160"/>
-      <c r="S18" s="160"/>
-      <c r="T18" s="160"/>
-      <c r="U18" s="160"/>
-      <c r="V18" s="160"/>
-      <c r="W18" s="160"/>
+      <c r="M18" s="163"/>
+      <c r="N18" s="163"/>
+      <c r="O18" s="163"/>
+      <c r="P18" s="163"/>
+      <c r="Q18" s="163"/>
+      <c r="R18" s="163"/>
+      <c r="S18" s="163"/>
+      <c r="T18" s="163"/>
+      <c r="U18" s="163"/>
+      <c r="V18" s="163"/>
+      <c r="W18" s="163"/>
       <c r="X18" s="6">
         <v>0</v>
       </c>
@@ -10099,20 +10099,20 @@
       <c r="K19" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="L19" s="160" t="s">
+      <c r="L19" s="163" t="s">
         <v>146</v>
       </c>
-      <c r="M19" s="160"/>
-      <c r="N19" s="160"/>
-      <c r="O19" s="160"/>
-      <c r="P19" s="160"/>
-      <c r="Q19" s="160"/>
-      <c r="R19" s="160"/>
-      <c r="S19" s="160"/>
-      <c r="T19" s="160"/>
-      <c r="U19" s="160"/>
-      <c r="V19" s="160"/>
-      <c r="W19" s="160"/>
+      <c r="M19" s="163"/>
+      <c r="N19" s="163"/>
+      <c r="O19" s="163"/>
+      <c r="P19" s="163"/>
+      <c r="Q19" s="163"/>
+      <c r="R19" s="163"/>
+      <c r="S19" s="163"/>
+      <c r="T19" s="163"/>
+      <c r="U19" s="163"/>
+      <c r="V19" s="163"/>
+      <c r="W19" s="163"/>
       <c r="X19" s="6">
         <v>0</v>
       </c>
@@ -10164,20 +10164,20 @@
       <c r="K20" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="L20" s="160" t="s">
+      <c r="L20" s="163" t="s">
         <v>150</v>
       </c>
-      <c r="M20" s="160"/>
-      <c r="N20" s="160"/>
-      <c r="O20" s="160"/>
-      <c r="P20" s="160"/>
-      <c r="Q20" s="160"/>
-      <c r="R20" s="160"/>
-      <c r="S20" s="160"/>
-      <c r="T20" s="160"/>
-      <c r="U20" s="160"/>
-      <c r="V20" s="160"/>
-      <c r="W20" s="160"/>
+      <c r="M20" s="163"/>
+      <c r="N20" s="163"/>
+      <c r="O20" s="163"/>
+      <c r="P20" s="163"/>
+      <c r="Q20" s="163"/>
+      <c r="R20" s="163"/>
+      <c r="S20" s="163"/>
+      <c r="T20" s="163"/>
+      <c r="U20" s="163"/>
+      <c r="V20" s="163"/>
+      <c r="W20" s="163"/>
       <c r="X20" s="6">
         <v>0</v>
       </c>
@@ -10229,20 +10229,20 @@
       <c r="K21" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="L21" s="160" t="s">
+      <c r="L21" s="163" t="s">
         <v>154</v>
       </c>
-      <c r="M21" s="160"/>
-      <c r="N21" s="160"/>
-      <c r="O21" s="160"/>
-      <c r="P21" s="160"/>
-      <c r="Q21" s="160"/>
-      <c r="R21" s="160"/>
-      <c r="S21" s="160"/>
-      <c r="T21" s="160"/>
-      <c r="U21" s="160"/>
-      <c r="V21" s="160"/>
-      <c r="W21" s="160"/>
+      <c r="M21" s="163"/>
+      <c r="N21" s="163"/>
+      <c r="O21" s="163"/>
+      <c r="P21" s="163"/>
+      <c r="Q21" s="163"/>
+      <c r="R21" s="163"/>
+      <c r="S21" s="163"/>
+      <c r="T21" s="163"/>
+      <c r="U21" s="163"/>
+      <c r="V21" s="163"/>
+      <c r="W21" s="163"/>
       <c r="X21" s="6">
         <v>0</v>
       </c>
@@ -10294,20 +10294,20 @@
       <c r="K22" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="L22" s="160" t="s">
+      <c r="L22" s="163" t="s">
         <v>158</v>
       </c>
-      <c r="M22" s="160"/>
-      <c r="N22" s="160"/>
-      <c r="O22" s="160"/>
-      <c r="P22" s="160"/>
-      <c r="Q22" s="160"/>
-      <c r="R22" s="160"/>
-      <c r="S22" s="160"/>
-      <c r="T22" s="160"/>
-      <c r="U22" s="160"/>
-      <c r="V22" s="160"/>
-      <c r="W22" s="160"/>
+      <c r="M22" s="163"/>
+      <c r="N22" s="163"/>
+      <c r="O22" s="163"/>
+      <c r="P22" s="163"/>
+      <c r="Q22" s="163"/>
+      <c r="R22" s="163"/>
+      <c r="S22" s="163"/>
+      <c r="T22" s="163"/>
+      <c r="U22" s="163"/>
+      <c r="V22" s="163"/>
+      <c r="W22" s="163"/>
       <c r="X22" s="6">
         <v>0</v>
       </c>
@@ -10359,20 +10359,20 @@
       <c r="K23" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="L23" s="160" t="s">
+      <c r="L23" s="163" t="s">
         <v>162</v>
       </c>
-      <c r="M23" s="160"/>
-      <c r="N23" s="160"/>
-      <c r="O23" s="160"/>
-      <c r="P23" s="160"/>
-      <c r="Q23" s="160"/>
-      <c r="R23" s="160"/>
-      <c r="S23" s="160"/>
-      <c r="T23" s="160"/>
-      <c r="U23" s="160"/>
-      <c r="V23" s="160"/>
-      <c r="W23" s="160"/>
+      <c r="M23" s="163"/>
+      <c r="N23" s="163"/>
+      <c r="O23" s="163"/>
+      <c r="P23" s="163"/>
+      <c r="Q23" s="163"/>
+      <c r="R23" s="163"/>
+      <c r="S23" s="163"/>
+      <c r="T23" s="163"/>
+      <c r="U23" s="163"/>
+      <c r="V23" s="163"/>
+      <c r="W23" s="163"/>
       <c r="X23" s="6">
         <v>0</v>
       </c>
@@ -10424,20 +10424,20 @@
       <c r="K24" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="L24" s="160" t="s">
+      <c r="L24" s="163" t="s">
         <v>166</v>
       </c>
-      <c r="M24" s="160"/>
-      <c r="N24" s="160"/>
-      <c r="O24" s="160"/>
-      <c r="P24" s="160"/>
-      <c r="Q24" s="160"/>
-      <c r="R24" s="160"/>
-      <c r="S24" s="160"/>
-      <c r="T24" s="160"/>
-      <c r="U24" s="160"/>
-      <c r="V24" s="160"/>
-      <c r="W24" s="160"/>
+      <c r="M24" s="163"/>
+      <c r="N24" s="163"/>
+      <c r="O24" s="163"/>
+      <c r="P24" s="163"/>
+      <c r="Q24" s="163"/>
+      <c r="R24" s="163"/>
+      <c r="S24" s="163"/>
+      <c r="T24" s="163"/>
+      <c r="U24" s="163"/>
+      <c r="V24" s="163"/>
+      <c r="W24" s="163"/>
       <c r="X24" s="6">
         <v>0</v>
       </c>
@@ -10489,20 +10489,20 @@
       <c r="K25" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="L25" s="160" t="s">
+      <c r="L25" s="163" t="s">
         <v>170</v>
       </c>
-      <c r="M25" s="160"/>
-      <c r="N25" s="160"/>
-      <c r="O25" s="160"/>
-      <c r="P25" s="160"/>
-      <c r="Q25" s="160"/>
-      <c r="R25" s="160"/>
-      <c r="S25" s="160"/>
-      <c r="T25" s="160"/>
-      <c r="U25" s="160"/>
-      <c r="V25" s="160"/>
-      <c r="W25" s="160"/>
+      <c r="M25" s="163"/>
+      <c r="N25" s="163"/>
+      <c r="O25" s="163"/>
+      <c r="P25" s="163"/>
+      <c r="Q25" s="163"/>
+      <c r="R25" s="163"/>
+      <c r="S25" s="163"/>
+      <c r="T25" s="163"/>
+      <c r="U25" s="163"/>
+      <c r="V25" s="163"/>
+      <c r="W25" s="163"/>
       <c r="X25" s="6">
         <v>0</v>
       </c>
@@ -10554,20 +10554,20 @@
       <c r="K26" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="L26" s="160" t="s">
+      <c r="L26" s="163" t="s">
         <v>174</v>
       </c>
-      <c r="M26" s="160"/>
-      <c r="N26" s="160"/>
-      <c r="O26" s="160"/>
-      <c r="P26" s="160"/>
-      <c r="Q26" s="160"/>
-      <c r="R26" s="160"/>
-      <c r="S26" s="160"/>
-      <c r="T26" s="160"/>
-      <c r="U26" s="160"/>
-      <c r="V26" s="160"/>
-      <c r="W26" s="160"/>
+      <c r="M26" s="163"/>
+      <c r="N26" s="163"/>
+      <c r="O26" s="163"/>
+      <c r="P26" s="163"/>
+      <c r="Q26" s="163"/>
+      <c r="R26" s="163"/>
+      <c r="S26" s="163"/>
+      <c r="T26" s="163"/>
+      <c r="U26" s="163"/>
+      <c r="V26" s="163"/>
+      <c r="W26" s="163"/>
       <c r="X26" s="6">
         <v>0</v>
       </c>
@@ -10589,10 +10589,10 @@
       </c>
     </row>
     <row r="28" spans="2:29" ht="17" customHeight="1">
-      <c r="B28" s="165" t="s">
+      <c r="B28" s="169" t="s">
         <v>29</v>
       </c>
-      <c r="C28" s="165" t="s">
+      <c r="C28" s="169" t="s">
         <v>30</v>
       </c>
       <c r="D28" s="2" t="s">
@@ -10601,10 +10601,10 @@
       <c r="E28" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="F28" s="166" t="s">
+      <c r="F28" s="167" t="s">
         <v>31</v>
       </c>
-      <c r="G28" s="166" t="s">
+      <c r="G28" s="167" t="s">
         <v>32</v>
       </c>
       <c r="H28" s="3" t="s">
@@ -10655,30 +10655,30 @@
       <c r="W28" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="X28" s="161"/>
-      <c r="Y28" s="162"/>
-      <c r="Z28" s="162"/>
-      <c r="AA28" s="163"/>
-      <c r="AB28" s="166" t="s">
+      <c r="X28" s="164"/>
+      <c r="Y28" s="165"/>
+      <c r="Z28" s="165"/>
+      <c r="AA28" s="166"/>
+      <c r="AB28" s="167" t="s">
         <v>50</v>
       </c>
-      <c r="AC28" s="166" t="s">
+      <c r="AC28" s="167" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="29" spans="2:29" ht="17" customHeight="1">
-      <c r="B29" s="165"/>
-      <c r="C29" s="165"/>
+      <c r="B29" s="169"/>
+      <c r="C29" s="169"/>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
-      <c r="F29" s="166"/>
-      <c r="G29" s="166"/>
-      <c r="H29" s="164" t="s">
+      <c r="F29" s="167"/>
+      <c r="G29" s="167"/>
+      <c r="H29" s="168" t="s">
         <v>52</v>
       </c>
-      <c r="I29" s="164"/>
-      <c r="J29" s="164"/>
-      <c r="K29" s="164"/>
+      <c r="I29" s="168"/>
+      <c r="J29" s="168"/>
+      <c r="K29" s="168"/>
       <c r="L29" s="3" t="s">
         <v>55</v>
       </c>
@@ -10719,14 +10719,14 @@
       <c r="Y29" s="3"/>
       <c r="Z29" s="3"/>
       <c r="AA29" s="3"/>
-      <c r="AB29" s="166"/>
-      <c r="AC29" s="166"/>
+      <c r="AB29" s="167"/>
+      <c r="AC29" s="167"/>
     </row>
     <row r="30" spans="2:29" ht="17" customHeight="1">
       <c r="B30" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="C30" s="167" t="s">
+      <c r="C30" s="161" t="s">
         <v>189</v>
       </c>
       <c r="D30" s="106" t="s">
@@ -10735,10 +10735,10 @@
       <c r="E30" s="106" t="s">
         <v>584</v>
       </c>
-      <c r="F30" s="167" t="s">
+      <c r="F30" s="161" t="s">
         <v>63</v>
       </c>
-      <c r="G30" s="167" t="s">
+      <c r="G30" s="161" t="s">
         <v>94</v>
       </c>
       <c r="H30" s="6" t="s">
@@ -10777,12 +10777,12 @@
       <c r="S30" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="T30" s="160" t="s">
+      <c r="T30" s="163" t="s">
         <v>190</v>
       </c>
-      <c r="U30" s="160"/>
-      <c r="V30" s="160"/>
-      <c r="W30" s="160"/>
+      <c r="U30" s="163"/>
+      <c r="V30" s="163"/>
+      <c r="W30" s="163"/>
       <c r="X30" s="11"/>
       <c r="Y30" s="11"/>
       <c r="Z30" s="11"/>
@@ -10799,11 +10799,11 @@
       <c r="B31" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="C31" s="168"/>
+      <c r="C31" s="162"/>
       <c r="D31" s="107"/>
       <c r="E31" s="107"/>
-      <c r="F31" s="168"/>
-      <c r="G31" s="168"/>
+      <c r="F31" s="162"/>
+      <c r="G31" s="162"/>
       <c r="H31" s="6" t="s">
         <v>65</v>
       </c>
@@ -10816,20 +10816,20 @@
       <c r="K31" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="L31" s="160" t="s">
+      <c r="L31" s="163" t="s">
         <v>192</v>
       </c>
-      <c r="M31" s="160"/>
-      <c r="N31" s="160"/>
-      <c r="O31" s="160"/>
-      <c r="P31" s="160"/>
-      <c r="Q31" s="160"/>
-      <c r="R31" s="160"/>
-      <c r="S31" s="160"/>
-      <c r="T31" s="160"/>
-      <c r="U31" s="160"/>
-      <c r="V31" s="160"/>
-      <c r="W31" s="160"/>
+      <c r="M31" s="163"/>
+      <c r="N31" s="163"/>
+      <c r="O31" s="163"/>
+      <c r="P31" s="163"/>
+      <c r="Q31" s="163"/>
+      <c r="R31" s="163"/>
+      <c r="S31" s="163"/>
+      <c r="T31" s="163"/>
+      <c r="U31" s="163"/>
+      <c r="V31" s="163"/>
+      <c r="W31" s="163"/>
       <c r="X31" s="11"/>
       <c r="Y31" s="11"/>
       <c r="Z31" s="11"/>
@@ -10846,7 +10846,7 @@
       <c r="B32" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="C32" s="167" t="s">
+      <c r="C32" s="161" t="s">
         <v>194</v>
       </c>
       <c r="D32" s="106" t="s">
@@ -10855,10 +10855,10 @@
       <c r="E32" s="106" t="s">
         <v>585</v>
       </c>
-      <c r="F32" s="167" t="s">
+      <c r="F32" s="161" t="s">
         <v>63</v>
       </c>
-      <c r="G32" s="167" t="s">
+      <c r="G32" s="161" t="s">
         <v>94</v>
       </c>
       <c r="H32" s="6" t="s">
@@ -10873,22 +10873,22 @@
       <c r="K32" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="L32" s="160" t="s">
+      <c r="L32" s="163" t="s">
         <v>195</v>
       </c>
-      <c r="M32" s="160"/>
-      <c r="N32" s="160"/>
-      <c r="O32" s="160"/>
-      <c r="P32" s="160"/>
-      <c r="Q32" s="160"/>
-      <c r="R32" s="160"/>
-      <c r="S32" s="160"/>
-      <c r="T32" s="160" t="s">
+      <c r="M32" s="163"/>
+      <c r="N32" s="163"/>
+      <c r="O32" s="163"/>
+      <c r="P32" s="163"/>
+      <c r="Q32" s="163"/>
+      <c r="R32" s="163"/>
+      <c r="S32" s="163"/>
+      <c r="T32" s="163" t="s">
         <v>196</v>
       </c>
-      <c r="U32" s="160"/>
-      <c r="V32" s="160"/>
-      <c r="W32" s="160"/>
+      <c r="U32" s="163"/>
+      <c r="V32" s="163"/>
+      <c r="W32" s="163"/>
       <c r="X32" s="11"/>
       <c r="Y32" s="11"/>
       <c r="Z32" s="11"/>
@@ -10905,11 +10905,11 @@
       <c r="B33" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="C33" s="168"/>
+      <c r="C33" s="162"/>
       <c r="D33" s="107"/>
       <c r="E33" s="107"/>
-      <c r="F33" s="168"/>
-      <c r="G33" s="168"/>
+      <c r="F33" s="162"/>
+      <c r="G33" s="162"/>
       <c r="H33" s="6" t="s">
         <v>65</v>
       </c>
@@ -10922,22 +10922,22 @@
       <c r="K33" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="L33" s="160" t="s">
+      <c r="L33" s="163" t="s">
         <v>689</v>
       </c>
-      <c r="M33" s="160"/>
-      <c r="N33" s="160"/>
-      <c r="O33" s="160"/>
-      <c r="P33" s="160" t="s">
+      <c r="M33" s="163"/>
+      <c r="N33" s="163"/>
+      <c r="O33" s="163"/>
+      <c r="P33" s="163" t="s">
         <v>198</v>
       </c>
-      <c r="Q33" s="160"/>
-      <c r="R33" s="160"/>
-      <c r="S33" s="160"/>
-      <c r="T33" s="160"/>
-      <c r="U33" s="160"/>
-      <c r="V33" s="160"/>
-      <c r="W33" s="160"/>
+      <c r="Q33" s="163"/>
+      <c r="R33" s="163"/>
+      <c r="S33" s="163"/>
+      <c r="T33" s="163"/>
+      <c r="U33" s="163"/>
+      <c r="V33" s="163"/>
+      <c r="W33" s="163"/>
       <c r="X33" s="11"/>
       <c r="Y33" s="11"/>
       <c r="Z33" s="11"/>
@@ -10952,22 +10952,24 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="L32:S32"/>
-    <mergeCell ref="T32:W32"/>
-    <mergeCell ref="L33:O33"/>
-    <mergeCell ref="P33:W33"/>
-    <mergeCell ref="X28:AA28"/>
-    <mergeCell ref="AB28:AB29"/>
-    <mergeCell ref="AC28:AC29"/>
-    <mergeCell ref="H29:K29"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="T30:W30"/>
-    <mergeCell ref="L31:W31"/>
+    <mergeCell ref="N11:W11"/>
+    <mergeCell ref="X2:AA2"/>
+    <mergeCell ref="H3:K3"/>
+    <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="N6:W6"/>
+    <mergeCell ref="N7:W7"/>
+    <mergeCell ref="T8:W8"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="V9:W9"/>
+    <mergeCell ref="N10:W10"/>
+    <mergeCell ref="L12:W12"/>
+    <mergeCell ref="L13:W13"/>
+    <mergeCell ref="L14:W14"/>
+    <mergeCell ref="L15:O15"/>
+    <mergeCell ref="P15:S15"/>
+    <mergeCell ref="T15:W15"/>
     <mergeCell ref="B28:B29"/>
     <mergeCell ref="C28:C29"/>
     <mergeCell ref="F28:F29"/>
@@ -10983,24 +10985,22 @@
     <mergeCell ref="L24:W24"/>
     <mergeCell ref="L25:W25"/>
     <mergeCell ref="L26:W26"/>
-    <mergeCell ref="L12:W12"/>
-    <mergeCell ref="L13:W13"/>
-    <mergeCell ref="L14:W14"/>
-    <mergeCell ref="L15:O15"/>
-    <mergeCell ref="P15:S15"/>
-    <mergeCell ref="T15:W15"/>
-    <mergeCell ref="N11:W11"/>
-    <mergeCell ref="X2:AA2"/>
-    <mergeCell ref="H3:K3"/>
-    <mergeCell ref="Q4:S4"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="N6:W6"/>
-    <mergeCell ref="N7:W7"/>
-    <mergeCell ref="T8:W8"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="V9:W9"/>
-    <mergeCell ref="N10:W10"/>
+    <mergeCell ref="X28:AA28"/>
+    <mergeCell ref="AB28:AB29"/>
+    <mergeCell ref="AC28:AC29"/>
+    <mergeCell ref="H29:K29"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="T30:W30"/>
+    <mergeCell ref="L31:W31"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="L32:S32"/>
+    <mergeCell ref="T32:W32"/>
+    <mergeCell ref="L33:O33"/>
+    <mergeCell ref="P33:W33"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="T8">
@@ -11035,55 +11035,55 @@
   <sheetData>
     <row r="3" spans="2:17" ht="17.25" thickBot="1"/>
     <row r="4" spans="2:17">
-      <c r="E4" s="173" t="s">
+      <c r="E4" s="187" t="s">
         <v>386</v>
       </c>
-      <c r="F4" s="173"/>
-      <c r="G4" s="173"/>
-      <c r="H4" s="173"/>
-      <c r="I4" s="173"/>
-      <c r="J4" s="173"/>
-      <c r="K4" s="173"/>
-      <c r="L4" s="173"/>
-      <c r="M4" s="173"/>
-      <c r="N4" s="173"/>
-      <c r="O4" s="173"/>
-      <c r="P4" s="173"/>
-      <c r="Q4" s="174"/>
+      <c r="F4" s="187"/>
+      <c r="G4" s="187"/>
+      <c r="H4" s="187"/>
+      <c r="I4" s="187"/>
+      <c r="J4" s="187"/>
+      <c r="K4" s="187"/>
+      <c r="L4" s="187"/>
+      <c r="M4" s="187"/>
+      <c r="N4" s="187"/>
+      <c r="O4" s="187"/>
+      <c r="P4" s="187"/>
+      <c r="Q4" s="188"/>
     </row>
     <row r="5" spans="2:17">
-      <c r="E5" s="175" t="s">
+      <c r="E5" s="189" t="s">
         <v>387</v>
       </c>
-      <c r="F5" s="175"/>
-      <c r="G5" s="175"/>
-      <c r="H5" s="175"/>
-      <c r="I5" s="175"/>
-      <c r="J5" s="175"/>
-      <c r="K5" s="175"/>
-      <c r="L5" s="175"/>
-      <c r="M5" s="175"/>
-      <c r="N5" s="175"/>
-      <c r="O5" s="175"/>
-      <c r="P5" s="175"/>
-      <c r="Q5" s="176"/>
+      <c r="F5" s="189"/>
+      <c r="G5" s="189"/>
+      <c r="H5" s="189"/>
+      <c r="I5" s="189"/>
+      <c r="J5" s="189"/>
+      <c r="K5" s="189"/>
+      <c r="L5" s="189"/>
+      <c r="M5" s="189"/>
+      <c r="N5" s="189"/>
+      <c r="O5" s="189"/>
+      <c r="P5" s="189"/>
+      <c r="Q5" s="190"/>
     </row>
     <row r="6" spans="2:17" ht="17.25" thickBot="1">
-      <c r="E6" s="169" t="s">
+      <c r="E6" s="185" t="s">
         <v>388</v>
       </c>
-      <c r="F6" s="169"/>
-      <c r="G6" s="169"/>
-      <c r="H6" s="169"/>
-      <c r="I6" s="169"/>
-      <c r="J6" s="169"/>
-      <c r="K6" s="169"/>
-      <c r="L6" s="169"/>
-      <c r="M6" s="169"/>
-      <c r="N6" s="169"/>
-      <c r="O6" s="169"/>
-      <c r="P6" s="169"/>
-      <c r="Q6" s="170"/>
+      <c r="F6" s="185"/>
+      <c r="G6" s="185"/>
+      <c r="H6" s="185"/>
+      <c r="I6" s="185"/>
+      <c r="J6" s="185"/>
+      <c r="K6" s="185"/>
+      <c r="L6" s="185"/>
+      <c r="M6" s="185"/>
+      <c r="N6" s="185"/>
+      <c r="O6" s="185"/>
+      <c r="P6" s="185"/>
+      <c r="Q6" s="186"/>
     </row>
     <row r="7" spans="2:17">
       <c r="E7" s="78"/>
@@ -11102,72 +11102,72 @@
     </row>
     <row r="8" spans="2:17" ht="17.25" thickBot="1"/>
     <row r="9" spans="2:17">
-      <c r="E9" s="173" t="s">
+      <c r="E9" s="187" t="s">
         <v>389</v>
       </c>
-      <c r="F9" s="173"/>
-      <c r="G9" s="173"/>
-      <c r="H9" s="173"/>
-      <c r="I9" s="173"/>
-      <c r="J9" s="173"/>
-      <c r="K9" s="173"/>
-      <c r="L9" s="173"/>
-      <c r="M9" s="173"/>
-      <c r="N9" s="173"/>
-      <c r="O9" s="173"/>
-      <c r="P9" s="173"/>
-      <c r="Q9" s="174"/>
+      <c r="F9" s="187"/>
+      <c r="G9" s="187"/>
+      <c r="H9" s="187"/>
+      <c r="I9" s="187"/>
+      <c r="J9" s="187"/>
+      <c r="K9" s="187"/>
+      <c r="L9" s="187"/>
+      <c r="M9" s="187"/>
+      <c r="N9" s="187"/>
+      <c r="O9" s="187"/>
+      <c r="P9" s="187"/>
+      <c r="Q9" s="188"/>
     </row>
     <row r="10" spans="2:17">
-      <c r="E10" s="175" t="s">
+      <c r="E10" s="189" t="s">
         <v>390</v>
       </c>
-      <c r="F10" s="175"/>
-      <c r="G10" s="175"/>
-      <c r="H10" s="175"/>
-      <c r="I10" s="175"/>
-      <c r="J10" s="175"/>
-      <c r="K10" s="175"/>
-      <c r="L10" s="175"/>
-      <c r="M10" s="175"/>
-      <c r="N10" s="175"/>
-      <c r="O10" s="175"/>
-      <c r="P10" s="175"/>
-      <c r="Q10" s="176"/>
+      <c r="F10" s="189"/>
+      <c r="G10" s="189"/>
+      <c r="H10" s="189"/>
+      <c r="I10" s="189"/>
+      <c r="J10" s="189"/>
+      <c r="K10" s="189"/>
+      <c r="L10" s="189"/>
+      <c r="M10" s="189"/>
+      <c r="N10" s="189"/>
+      <c r="O10" s="189"/>
+      <c r="P10" s="189"/>
+      <c r="Q10" s="190"/>
     </row>
     <row r="11" spans="2:17">
-      <c r="E11" s="175" t="s">
+      <c r="E11" s="189" t="s">
         <v>391</v>
       </c>
-      <c r="F11" s="175"/>
-      <c r="G11" s="175"/>
-      <c r="H11" s="175"/>
-      <c r="I11" s="175"/>
-      <c r="J11" s="175"/>
-      <c r="K11" s="175"/>
-      <c r="L11" s="175"/>
-      <c r="M11" s="175"/>
-      <c r="N11" s="175"/>
-      <c r="O11" s="175"/>
-      <c r="P11" s="175"/>
-      <c r="Q11" s="176"/>
+      <c r="F11" s="189"/>
+      <c r="G11" s="189"/>
+      <c r="H11" s="189"/>
+      <c r="I11" s="189"/>
+      <c r="J11" s="189"/>
+      <c r="K11" s="189"/>
+      <c r="L11" s="189"/>
+      <c r="M11" s="189"/>
+      <c r="N11" s="189"/>
+      <c r="O11" s="189"/>
+      <c r="P11" s="189"/>
+      <c r="Q11" s="190"/>
     </row>
     <row r="12" spans="2:17" ht="17.25" thickBot="1">
-      <c r="E12" s="169" t="s">
+      <c r="E12" s="185" t="s">
         <v>392</v>
       </c>
-      <c r="F12" s="169"/>
-      <c r="G12" s="169"/>
-      <c r="H12" s="169"/>
-      <c r="I12" s="169"/>
-      <c r="J12" s="169"/>
-      <c r="K12" s="169"/>
-      <c r="L12" s="169"/>
-      <c r="M12" s="169"/>
-      <c r="N12" s="169"/>
-      <c r="O12" s="169"/>
-      <c r="P12" s="169"/>
-      <c r="Q12" s="170"/>
+      <c r="F12" s="185"/>
+      <c r="G12" s="185"/>
+      <c r="H12" s="185"/>
+      <c r="I12" s="185"/>
+      <c r="J12" s="185"/>
+      <c r="K12" s="185"/>
+      <c r="L12" s="185"/>
+      <c r="M12" s="185"/>
+      <c r="N12" s="185"/>
+      <c r="O12" s="185"/>
+      <c r="P12" s="185"/>
+      <c r="Q12" s="186"/>
     </row>
     <row r="13" spans="2:17">
       <c r="E13" s="78"/>
@@ -11254,19 +11254,19 @@
       <c r="J17" s="82" t="s">
         <v>244</v>
       </c>
-      <c r="K17" s="171" t="s">
+      <c r="K17" s="173" t="s">
         <v>67</v>
       </c>
-      <c r="L17" s="171"/>
-      <c r="M17" s="171"/>
-      <c r="N17" s="171" t="s">
+      <c r="L17" s="173"/>
+      <c r="M17" s="173"/>
+      <c r="N17" s="173" t="s">
         <v>68</v>
       </c>
-      <c r="O17" s="171"/>
-      <c r="P17" s="171" t="s">
+      <c r="O17" s="173"/>
+      <c r="P17" s="173" t="s">
         <v>69</v>
       </c>
-      <c r="Q17" s="172"/>
+      <c r="Q17" s="179"/>
     </row>
     <row r="18" spans="2:17">
       <c r="E18" s="80" t="s">
@@ -11277,19 +11277,19 @@
       <c r="H18" s="83"/>
       <c r="I18" s="83"/>
       <c r="J18" s="83"/>
-      <c r="K18" s="171" t="s">
+      <c r="K18" s="173" t="s">
         <v>410</v>
       </c>
-      <c r="L18" s="171"/>
-      <c r="M18" s="171"/>
-      <c r="N18" s="171" t="s">
+      <c r="L18" s="173"/>
+      <c r="M18" s="173"/>
+      <c r="N18" s="173" t="s">
         <v>410</v>
       </c>
-      <c r="O18" s="171"/>
-      <c r="P18" s="171" t="s">
+      <c r="O18" s="173"/>
+      <c r="P18" s="173" t="s">
         <v>410</v>
       </c>
-      <c r="Q18" s="172"/>
+      <c r="Q18" s="179"/>
     </row>
     <row r="19" spans="2:17">
       <c r="E19" s="80" t="s">
@@ -11300,19 +11300,19 @@
       <c r="H19" s="83"/>
       <c r="I19" s="83"/>
       <c r="J19" s="83"/>
-      <c r="K19" s="171" t="s">
+      <c r="K19" s="173" t="s">
         <v>411</v>
       </c>
-      <c r="L19" s="171"/>
-      <c r="M19" s="171"/>
-      <c r="N19" s="171" t="s">
+      <c r="L19" s="173"/>
+      <c r="M19" s="173"/>
+      <c r="N19" s="173" t="s">
         <v>411</v>
       </c>
-      <c r="O19" s="171"/>
-      <c r="P19" s="171" t="s">
+      <c r="O19" s="173"/>
+      <c r="P19" s="173" t="s">
         <v>411</v>
       </c>
-      <c r="Q19" s="172"/>
+      <c r="Q19" s="179"/>
     </row>
     <row r="20" spans="2:17">
       <c r="E20" s="80" t="s">
@@ -11323,38 +11323,38 @@
       <c r="H20" s="83"/>
       <c r="I20" s="83"/>
       <c r="J20" s="83"/>
-      <c r="K20" s="171" t="s">
+      <c r="K20" s="173" t="s">
         <v>412</v>
       </c>
-      <c r="L20" s="171"/>
-      <c r="M20" s="171"/>
-      <c r="N20" s="171" t="s">
+      <c r="L20" s="173"/>
+      <c r="M20" s="173"/>
+      <c r="N20" s="173" t="s">
         <v>412</v>
       </c>
-      <c r="O20" s="171"/>
-      <c r="P20" s="171" t="s">
+      <c r="O20" s="173"/>
+      <c r="P20" s="173" t="s">
         <v>412</v>
       </c>
-      <c r="Q20" s="172"/>
+      <c r="Q20" s="179"/>
     </row>
     <row r="21" spans="2:17" ht="301.5" customHeight="1">
       <c r="E21" s="80" t="s">
         <v>413</v>
       </c>
-      <c r="F21" s="177" t="s">
+      <c r="F21" s="184" t="s">
         <v>414</v>
       </c>
-      <c r="G21" s="177"/>
-      <c r="H21" s="177"/>
-      <c r="I21" s="177"/>
-      <c r="J21" s="177"/>
-      <c r="K21" s="177"/>
-      <c r="L21" s="177"/>
-      <c r="M21" s="177"/>
-      <c r="N21" s="177"/>
-      <c r="O21" s="177"/>
-      <c r="P21" s="177"/>
-      <c r="Q21" s="177"/>
+      <c r="G21" s="184"/>
+      <c r="H21" s="184"/>
+      <c r="I21" s="184"/>
+      <c r="J21" s="184"/>
+      <c r="K21" s="184"/>
+      <c r="L21" s="184"/>
+      <c r="M21" s="184"/>
+      <c r="N21" s="184"/>
+      <c r="O21" s="184"/>
+      <c r="P21" s="184"/>
+      <c r="Q21" s="184"/>
     </row>
     <row r="23" spans="2:17">
       <c r="B23" s="79" t="s">
@@ -11575,20 +11575,20 @@
       <c r="E28" s="80" t="s">
         <v>413</v>
       </c>
-      <c r="F28" s="178" t="s">
+      <c r="F28" s="176" t="s">
         <v>417</v>
       </c>
-      <c r="G28" s="178"/>
-      <c r="H28" s="178"/>
-      <c r="I28" s="178"/>
-      <c r="J28" s="178"/>
-      <c r="K28" s="178"/>
-      <c r="L28" s="178"/>
-      <c r="M28" s="178"/>
-      <c r="N28" s="178"/>
-      <c r="O28" s="178"/>
-      <c r="P28" s="178"/>
-      <c r="Q28" s="177"/>
+      <c r="G28" s="176"/>
+      <c r="H28" s="176"/>
+      <c r="I28" s="176"/>
+      <c r="J28" s="176"/>
+      <c r="K28" s="176"/>
+      <c r="L28" s="176"/>
+      <c r="M28" s="176"/>
+      <c r="N28" s="176"/>
+      <c r="O28" s="176"/>
+      <c r="P28" s="176"/>
+      <c r="Q28" s="184"/>
     </row>
     <row r="30" spans="2:17">
       <c r="B30" s="79" t="s">
@@ -11651,18 +11651,18 @@
       <c r="G31" s="82" t="s">
         <v>244</v>
       </c>
-      <c r="H31" s="172" t="s">
+      <c r="H31" s="179" t="s">
         <v>88</v>
       </c>
-      <c r="I31" s="172"/>
-      <c r="J31" s="172"/>
-      <c r="K31" s="172"/>
-      <c r="L31" s="172"/>
-      <c r="M31" s="172"/>
-      <c r="N31" s="172"/>
-      <c r="O31" s="172"/>
-      <c r="P31" s="172"/>
-      <c r="Q31" s="172"/>
+      <c r="I31" s="179"/>
+      <c r="J31" s="179"/>
+      <c r="K31" s="179"/>
+      <c r="L31" s="179"/>
+      <c r="M31" s="179"/>
+      <c r="N31" s="179"/>
+      <c r="O31" s="179"/>
+      <c r="P31" s="179"/>
+      <c r="Q31" s="179"/>
     </row>
     <row r="32" spans="2:17">
       <c r="E32" s="80" t="s">
@@ -11670,18 +11670,18 @@
       </c>
       <c r="F32" s="83"/>
       <c r="G32" s="83"/>
-      <c r="H32" s="172" t="s">
+      <c r="H32" s="179" t="s">
         <v>420</v>
       </c>
-      <c r="I32" s="172"/>
-      <c r="J32" s="172"/>
-      <c r="K32" s="172"/>
-      <c r="L32" s="172"/>
-      <c r="M32" s="172"/>
-      <c r="N32" s="172"/>
-      <c r="O32" s="172"/>
-      <c r="P32" s="172"/>
-      <c r="Q32" s="172"/>
+      <c r="I32" s="179"/>
+      <c r="J32" s="179"/>
+      <c r="K32" s="179"/>
+      <c r="L32" s="179"/>
+      <c r="M32" s="179"/>
+      <c r="N32" s="179"/>
+      <c r="O32" s="179"/>
+      <c r="P32" s="179"/>
+      <c r="Q32" s="179"/>
     </row>
     <row r="33" spans="2:17">
       <c r="E33" s="80" t="s">
@@ -11689,18 +11689,18 @@
       </c>
       <c r="F33" s="83"/>
       <c r="G33" s="83"/>
-      <c r="H33" s="172" t="s">
+      <c r="H33" s="179" t="s">
         <v>411</v>
       </c>
-      <c r="I33" s="172"/>
-      <c r="J33" s="172"/>
-      <c r="K33" s="172"/>
-      <c r="L33" s="172"/>
-      <c r="M33" s="172"/>
-      <c r="N33" s="172"/>
-      <c r="O33" s="172"/>
-      <c r="P33" s="172"/>
-      <c r="Q33" s="172"/>
+      <c r="I33" s="179"/>
+      <c r="J33" s="179"/>
+      <c r="K33" s="179"/>
+      <c r="L33" s="179"/>
+      <c r="M33" s="179"/>
+      <c r="N33" s="179"/>
+      <c r="O33" s="179"/>
+      <c r="P33" s="179"/>
+      <c r="Q33" s="179"/>
     </row>
     <row r="34" spans="2:17">
       <c r="E34" s="80" t="s">
@@ -11708,37 +11708,37 @@
       </c>
       <c r="F34" s="83"/>
       <c r="G34" s="83"/>
-      <c r="H34" s="172" t="s">
+      <c r="H34" s="179" t="s">
         <v>412</v>
       </c>
-      <c r="I34" s="172"/>
-      <c r="J34" s="172"/>
-      <c r="K34" s="172"/>
-      <c r="L34" s="172"/>
-      <c r="M34" s="172"/>
-      <c r="N34" s="172"/>
-      <c r="O34" s="172"/>
-      <c r="P34" s="172"/>
-      <c r="Q34" s="172"/>
+      <c r="I34" s="179"/>
+      <c r="J34" s="179"/>
+      <c r="K34" s="179"/>
+      <c r="L34" s="179"/>
+      <c r="M34" s="179"/>
+      <c r="N34" s="179"/>
+      <c r="O34" s="179"/>
+      <c r="P34" s="179"/>
+      <c r="Q34" s="179"/>
     </row>
     <row r="35" spans="2:17">
       <c r="E35" s="80" t="s">
         <v>413</v>
       </c>
-      <c r="F35" s="180" t="s">
+      <c r="F35" s="170" t="s">
         <v>421</v>
       </c>
-      <c r="G35" s="180"/>
-      <c r="H35" s="180"/>
-      <c r="I35" s="180"/>
-      <c r="J35" s="180"/>
-      <c r="K35" s="180"/>
-      <c r="L35" s="180"/>
-      <c r="M35" s="180"/>
-      <c r="N35" s="180"/>
-      <c r="O35" s="180"/>
-      <c r="P35" s="180"/>
-      <c r="Q35" s="180"/>
+      <c r="G35" s="170"/>
+      <c r="H35" s="170"/>
+      <c r="I35" s="170"/>
+      <c r="J35" s="170"/>
+      <c r="K35" s="170"/>
+      <c r="L35" s="170"/>
+      <c r="M35" s="170"/>
+      <c r="N35" s="170"/>
+      <c r="O35" s="170"/>
+      <c r="P35" s="170"/>
+      <c r="Q35" s="170"/>
     </row>
     <row r="37" spans="2:17">
       <c r="B37" s="79" t="s">
@@ -11801,18 +11801,18 @@
       <c r="G38" s="82" t="s">
         <v>244</v>
       </c>
-      <c r="H38" s="172" t="s">
+      <c r="H38" s="179" t="s">
         <v>91</v>
       </c>
-      <c r="I38" s="172"/>
-      <c r="J38" s="172"/>
-      <c r="K38" s="172"/>
-      <c r="L38" s="172"/>
-      <c r="M38" s="172"/>
-      <c r="N38" s="172"/>
-      <c r="O38" s="172"/>
-      <c r="P38" s="172"/>
-      <c r="Q38" s="172"/>
+      <c r="I38" s="179"/>
+      <c r="J38" s="179"/>
+      <c r="K38" s="179"/>
+      <c r="L38" s="179"/>
+      <c r="M38" s="179"/>
+      <c r="N38" s="179"/>
+      <c r="O38" s="179"/>
+      <c r="P38" s="179"/>
+      <c r="Q38" s="179"/>
     </row>
     <row r="39" spans="2:17">
       <c r="E39" s="80" t="s">
@@ -11820,18 +11820,18 @@
       </c>
       <c r="F39" s="83"/>
       <c r="G39" s="83"/>
-      <c r="H39" s="172" t="s">
+      <c r="H39" s="179" t="s">
         <v>420</v>
       </c>
-      <c r="I39" s="172"/>
-      <c r="J39" s="172"/>
-      <c r="K39" s="172"/>
-      <c r="L39" s="172"/>
-      <c r="M39" s="172"/>
-      <c r="N39" s="172"/>
-      <c r="O39" s="172"/>
-      <c r="P39" s="172"/>
-      <c r="Q39" s="172"/>
+      <c r="I39" s="179"/>
+      <c r="J39" s="179"/>
+      <c r="K39" s="179"/>
+      <c r="L39" s="179"/>
+      <c r="M39" s="179"/>
+      <c r="N39" s="179"/>
+      <c r="O39" s="179"/>
+      <c r="P39" s="179"/>
+      <c r="Q39" s="179"/>
     </row>
     <row r="40" spans="2:17">
       <c r="E40" s="80" t="s">
@@ -11839,18 +11839,18 @@
       </c>
       <c r="F40" s="83"/>
       <c r="G40" s="83"/>
-      <c r="H40" s="172" t="s">
+      <c r="H40" s="179" t="s">
         <v>411</v>
       </c>
-      <c r="I40" s="172"/>
-      <c r="J40" s="172"/>
-      <c r="K40" s="172"/>
-      <c r="L40" s="172"/>
-      <c r="M40" s="172"/>
-      <c r="N40" s="172"/>
-      <c r="O40" s="172"/>
-      <c r="P40" s="172"/>
-      <c r="Q40" s="172"/>
+      <c r="I40" s="179"/>
+      <c r="J40" s="179"/>
+      <c r="K40" s="179"/>
+      <c r="L40" s="179"/>
+      <c r="M40" s="179"/>
+      <c r="N40" s="179"/>
+      <c r="O40" s="179"/>
+      <c r="P40" s="179"/>
+      <c r="Q40" s="179"/>
     </row>
     <row r="41" spans="2:17">
       <c r="E41" s="80" t="s">
@@ -11858,37 +11858,37 @@
       </c>
       <c r="F41" s="83"/>
       <c r="G41" s="83"/>
-      <c r="H41" s="172" t="s">
+      <c r="H41" s="179" t="s">
         <v>412</v>
       </c>
-      <c r="I41" s="172"/>
-      <c r="J41" s="172"/>
-      <c r="K41" s="172"/>
-      <c r="L41" s="172"/>
-      <c r="M41" s="172"/>
-      <c r="N41" s="172"/>
-      <c r="O41" s="172"/>
-      <c r="P41" s="172"/>
-      <c r="Q41" s="172"/>
+      <c r="I41" s="179"/>
+      <c r="J41" s="179"/>
+      <c r="K41" s="179"/>
+      <c r="L41" s="179"/>
+      <c r="M41" s="179"/>
+      <c r="N41" s="179"/>
+      <c r="O41" s="179"/>
+      <c r="P41" s="179"/>
+      <c r="Q41" s="179"/>
     </row>
     <row r="42" spans="2:17">
       <c r="E42" s="80" t="s">
         <v>413</v>
       </c>
-      <c r="F42" s="180" t="s">
+      <c r="F42" s="170" t="s">
         <v>424</v>
       </c>
-      <c r="G42" s="180"/>
-      <c r="H42" s="180"/>
-      <c r="I42" s="180"/>
-      <c r="J42" s="180"/>
-      <c r="K42" s="180"/>
-      <c r="L42" s="180"/>
-      <c r="M42" s="180"/>
-      <c r="N42" s="180"/>
-      <c r="O42" s="180"/>
-      <c r="P42" s="180"/>
-      <c r="Q42" s="180"/>
+      <c r="G42" s="170"/>
+      <c r="H42" s="170"/>
+      <c r="I42" s="170"/>
+      <c r="J42" s="170"/>
+      <c r="K42" s="170"/>
+      <c r="L42" s="170"/>
+      <c r="M42" s="170"/>
+      <c r="N42" s="170"/>
+      <c r="O42" s="170"/>
+      <c r="P42" s="170"/>
+      <c r="Q42" s="170"/>
     </row>
     <row r="44" spans="2:17">
       <c r="B44" s="79" t="s">
@@ -11969,12 +11969,12 @@
       <c r="M45" s="83" t="s">
         <v>102</v>
       </c>
-      <c r="N45" s="172" t="s">
+      <c r="N45" s="179" t="s">
         <v>427</v>
       </c>
-      <c r="O45" s="172"/>
-      <c r="P45" s="172"/>
-      <c r="Q45" s="172"/>
+      <c r="O45" s="179"/>
+      <c r="P45" s="179"/>
+      <c r="Q45" s="179"/>
     </row>
     <row r="46" spans="2:17">
       <c r="E46" s="80" t="s">
@@ -12004,12 +12004,12 @@
       <c r="M46" s="83">
         <v>0</v>
       </c>
-      <c r="N46" s="172" t="s">
+      <c r="N46" s="179" t="s">
         <v>410</v>
       </c>
-      <c r="O46" s="172"/>
-      <c r="P46" s="172"/>
-      <c r="Q46" s="172"/>
+      <c r="O46" s="179"/>
+      <c r="P46" s="179"/>
+      <c r="Q46" s="179"/>
     </row>
     <row r="47" spans="2:17">
       <c r="E47" s="80" t="s">
@@ -12039,12 +12039,12 @@
       <c r="M47" s="83" t="s">
         <v>411</v>
       </c>
-      <c r="N47" s="172" t="s">
+      <c r="N47" s="179" t="s">
         <v>411</v>
       </c>
-      <c r="O47" s="172"/>
-      <c r="P47" s="172"/>
-      <c r="Q47" s="172"/>
+      <c r="O47" s="179"/>
+      <c r="P47" s="179"/>
+      <c r="Q47" s="179"/>
     </row>
     <row r="48" spans="2:17">
       <c r="E48" s="80" t="s">
@@ -12074,31 +12074,31 @@
       <c r="M48" s="83" t="s">
         <v>203</v>
       </c>
-      <c r="N48" s="172" t="s">
+      <c r="N48" s="179" t="s">
         <v>203</v>
       </c>
-      <c r="O48" s="172"/>
-      <c r="P48" s="172"/>
-      <c r="Q48" s="172"/>
+      <c r="O48" s="179"/>
+      <c r="P48" s="179"/>
+      <c r="Q48" s="179"/>
     </row>
     <row r="49" spans="2:17" ht="409.5" customHeight="1">
       <c r="E49" s="80" t="s">
         <v>413</v>
       </c>
-      <c r="F49" s="178" t="s">
+      <c r="F49" s="176" t="s">
         <v>429</v>
       </c>
-      <c r="G49" s="178"/>
-      <c r="H49" s="178"/>
-      <c r="I49" s="178"/>
-      <c r="J49" s="178"/>
-      <c r="K49" s="178"/>
-      <c r="L49" s="178"/>
-      <c r="M49" s="178"/>
-      <c r="N49" s="178"/>
-      <c r="O49" s="178"/>
-      <c r="P49" s="178"/>
-      <c r="Q49" s="177"/>
+      <c r="G49" s="176"/>
+      <c r="H49" s="176"/>
+      <c r="I49" s="176"/>
+      <c r="J49" s="176"/>
+      <c r="K49" s="176"/>
+      <c r="L49" s="176"/>
+      <c r="M49" s="176"/>
+      <c r="N49" s="176"/>
+      <c r="O49" s="176"/>
+      <c r="P49" s="176"/>
+      <c r="Q49" s="184"/>
     </row>
     <row r="51" spans="2:17" ht="16.5" customHeight="1">
       <c r="B51" s="79" t="s">
@@ -12179,14 +12179,14 @@
       <c r="M52" s="83" t="s">
         <v>108</v>
       </c>
-      <c r="N52" s="171" t="s">
+      <c r="N52" s="173" t="s">
         <v>109</v>
       </c>
-      <c r="O52" s="179"/>
-      <c r="P52" s="171" t="s">
+      <c r="O52" s="175"/>
+      <c r="P52" s="173" t="s">
         <v>110</v>
       </c>
-      <c r="Q52" s="179"/>
+      <c r="Q52" s="175"/>
     </row>
     <row r="53" spans="2:17" ht="16.5" customHeight="1">
       <c r="E53" s="80" t="s">
@@ -12206,14 +12206,14 @@
       <c r="M53" s="83">
         <v>0</v>
       </c>
-      <c r="N53" s="171" t="s">
+      <c r="N53" s="173" t="s">
         <v>432</v>
       </c>
-      <c r="O53" s="179"/>
-      <c r="P53" s="171" t="s">
+      <c r="O53" s="175"/>
+      <c r="P53" s="173" t="s">
         <v>433</v>
       </c>
-      <c r="Q53" s="179"/>
+      <c r="Q53" s="175"/>
     </row>
     <row r="54" spans="2:17" ht="16.5" customHeight="1">
       <c r="E54" s="80" t="s">
@@ -12233,14 +12233,14 @@
       <c r="M54" s="83" t="s">
         <v>411</v>
       </c>
-      <c r="N54" s="171" t="s">
+      <c r="N54" s="173" t="s">
         <v>411</v>
       </c>
-      <c r="O54" s="179"/>
-      <c r="P54" s="171" t="s">
+      <c r="O54" s="175"/>
+      <c r="P54" s="173" t="s">
         <v>411</v>
       </c>
-      <c r="Q54" s="179"/>
+      <c r="Q54" s="175"/>
     </row>
     <row r="55" spans="2:17" ht="16.5" customHeight="1">
       <c r="E55" s="80" t="s">
@@ -12260,33 +12260,33 @@
       <c r="M55" s="83" t="s">
         <v>203</v>
       </c>
-      <c r="N55" s="171" t="s">
+      <c r="N55" s="173" t="s">
         <v>203</v>
       </c>
-      <c r="O55" s="179"/>
-      <c r="P55" s="171" t="s">
+      <c r="O55" s="175"/>
+      <c r="P55" s="173" t="s">
         <v>203</v>
       </c>
-      <c r="Q55" s="179"/>
+      <c r="Q55" s="175"/>
     </row>
     <row r="56" spans="2:17" ht="378.75" customHeight="1">
       <c r="E56" s="80" t="s">
         <v>413</v>
       </c>
-      <c r="F56" s="177" t="s">
+      <c r="F56" s="184" t="s">
         <v>434</v>
       </c>
-      <c r="G56" s="177"/>
-      <c r="H56" s="177"/>
-      <c r="I56" s="177"/>
-      <c r="J56" s="177"/>
-      <c r="K56" s="177"/>
-      <c r="L56" s="177"/>
-      <c r="M56" s="177"/>
-      <c r="N56" s="177"/>
-      <c r="O56" s="177"/>
-      <c r="P56" s="177"/>
-      <c r="Q56" s="177"/>
+      <c r="G56" s="184"/>
+      <c r="H56" s="184"/>
+      <c r="I56" s="184"/>
+      <c r="J56" s="184"/>
+      <c r="K56" s="184"/>
+      <c r="L56" s="184"/>
+      <c r="M56" s="184"/>
+      <c r="N56" s="184"/>
+      <c r="O56" s="184"/>
+      <c r="P56" s="184"/>
+      <c r="Q56" s="184"/>
     </row>
     <row r="58" spans="2:17">
       <c r="B58" s="79" t="s">
@@ -12367,12 +12367,12 @@
       <c r="M59" s="82" t="s">
         <v>244</v>
       </c>
-      <c r="N59" s="172" t="s">
+      <c r="N59" s="179" t="s">
         <v>190</v>
       </c>
-      <c r="O59" s="172"/>
-      <c r="P59" s="172"/>
-      <c r="Q59" s="172"/>
+      <c r="O59" s="179"/>
+      <c r="P59" s="179"/>
+      <c r="Q59" s="179"/>
     </row>
     <row r="60" spans="2:17">
       <c r="B60" s="81" t="s">
@@ -12392,12 +12392,12 @@
       <c r="K60" s="81"/>
       <c r="L60" s="81"/>
       <c r="M60" s="81"/>
-      <c r="N60" s="172" t="s">
+      <c r="N60" s="179" t="s">
         <v>410</v>
       </c>
-      <c r="O60" s="172"/>
-      <c r="P60" s="172"/>
-      <c r="Q60" s="172"/>
+      <c r="O60" s="179"/>
+      <c r="P60" s="179"/>
+      <c r="Q60" s="179"/>
     </row>
     <row r="61" spans="2:17">
       <c r="E61" s="80" t="s">
@@ -12411,12 +12411,12 @@
       <c r="K61" s="81"/>
       <c r="L61" s="81"/>
       <c r="M61" s="81"/>
-      <c r="N61" s="172" t="s">
+      <c r="N61" s="179" t="s">
         <v>411</v>
       </c>
-      <c r="O61" s="172"/>
-      <c r="P61" s="172"/>
-      <c r="Q61" s="172"/>
+      <c r="O61" s="179"/>
+      <c r="P61" s="179"/>
+      <c r="Q61" s="179"/>
     </row>
     <row r="62" spans="2:17">
       <c r="E62" s="80" t="s">
@@ -12430,12 +12430,12 @@
       <c r="K62" s="81"/>
       <c r="L62" s="81"/>
       <c r="M62" s="81"/>
-      <c r="N62" s="172" t="s">
+      <c r="N62" s="179" t="s">
         <v>203</v>
       </c>
-      <c r="O62" s="172"/>
-      <c r="P62" s="172"/>
-      <c r="Q62" s="172"/>
+      <c r="O62" s="179"/>
+      <c r="P62" s="179"/>
+      <c r="Q62" s="179"/>
     </row>
     <row r="63" spans="2:17">
       <c r="E63" s="80"/>
@@ -12480,77 +12480,77 @@
       <c r="E64" s="80" t="s">
         <v>408</v>
       </c>
-      <c r="F64" s="172" t="s">
+      <c r="F64" s="179" t="s">
         <v>192</v>
       </c>
-      <c r="G64" s="172"/>
-      <c r="H64" s="172"/>
-      <c r="I64" s="172"/>
-      <c r="J64" s="172"/>
-      <c r="K64" s="172"/>
-      <c r="L64" s="172"/>
-      <c r="M64" s="172"/>
-      <c r="N64" s="172"/>
-      <c r="O64" s="172"/>
-      <c r="P64" s="172"/>
-      <c r="Q64" s="172"/>
+      <c r="G64" s="179"/>
+      <c r="H64" s="179"/>
+      <c r="I64" s="179"/>
+      <c r="J64" s="179"/>
+      <c r="K64" s="179"/>
+      <c r="L64" s="179"/>
+      <c r="M64" s="179"/>
+      <c r="N64" s="179"/>
+      <c r="O64" s="179"/>
+      <c r="P64" s="179"/>
+      <c r="Q64" s="179"/>
     </row>
     <row r="65" spans="2:17">
       <c r="E65" s="80" t="s">
         <v>409</v>
       </c>
-      <c r="F65" s="172" t="s">
+      <c r="F65" s="179" t="s">
         <v>420</v>
       </c>
-      <c r="G65" s="172"/>
-      <c r="H65" s="172"/>
-      <c r="I65" s="172"/>
-      <c r="J65" s="172"/>
-      <c r="K65" s="172"/>
-      <c r="L65" s="172"/>
-      <c r="M65" s="172"/>
-      <c r="N65" s="172"/>
-      <c r="O65" s="172"/>
-      <c r="P65" s="172"/>
-      <c r="Q65" s="172"/>
+      <c r="G65" s="179"/>
+      <c r="H65" s="179"/>
+      <c r="I65" s="179"/>
+      <c r="J65" s="179"/>
+      <c r="K65" s="179"/>
+      <c r="L65" s="179"/>
+      <c r="M65" s="179"/>
+      <c r="N65" s="179"/>
+      <c r="O65" s="179"/>
+      <c r="P65" s="179"/>
+      <c r="Q65" s="179"/>
     </row>
     <row r="66" spans="2:17">
       <c r="E66" s="80" t="s">
         <v>386</v>
       </c>
-      <c r="F66" s="172" t="s">
+      <c r="F66" s="179" t="s">
         <v>411</v>
       </c>
-      <c r="G66" s="172"/>
-      <c r="H66" s="172"/>
-      <c r="I66" s="172"/>
-      <c r="J66" s="172"/>
-      <c r="K66" s="172"/>
-      <c r="L66" s="172"/>
-      <c r="M66" s="172"/>
-      <c r="N66" s="172"/>
-      <c r="O66" s="172"/>
-      <c r="P66" s="172"/>
-      <c r="Q66" s="172"/>
+      <c r="G66" s="179"/>
+      <c r="H66" s="179"/>
+      <c r="I66" s="179"/>
+      <c r="J66" s="179"/>
+      <c r="K66" s="179"/>
+      <c r="L66" s="179"/>
+      <c r="M66" s="179"/>
+      <c r="N66" s="179"/>
+      <c r="O66" s="179"/>
+      <c r="P66" s="179"/>
+      <c r="Q66" s="179"/>
     </row>
     <row r="67" spans="2:17">
       <c r="E67" s="80" t="s">
         <v>389</v>
       </c>
-      <c r="F67" s="172" t="s">
+      <c r="F67" s="179" t="s">
         <v>203</v>
       </c>
-      <c r="G67" s="172"/>
-      <c r="H67" s="172"/>
-      <c r="I67" s="172"/>
-      <c r="J67" s="172"/>
-      <c r="K67" s="172"/>
-      <c r="L67" s="172"/>
-      <c r="M67" s="172"/>
-      <c r="N67" s="172"/>
-      <c r="O67" s="172"/>
-      <c r="P67" s="172"/>
-      <c r="Q67" s="172"/>
+      <c r="G67" s="179"/>
+      <c r="H67" s="179"/>
+      <c r="I67" s="179"/>
+      <c r="J67" s="179"/>
+      <c r="K67" s="179"/>
+      <c r="L67" s="179"/>
+      <c r="M67" s="179"/>
+      <c r="N67" s="179"/>
+      <c r="O67" s="179"/>
+      <c r="P67" s="179"/>
+      <c r="Q67" s="179"/>
     </row>
     <row r="68" spans="2:17" ht="360" customHeight="1">
       <c r="E68" s="84" t="s">
@@ -12626,22 +12626,22 @@
       <c r="E71" s="80" t="s">
         <v>408</v>
       </c>
-      <c r="F71" s="172" t="s">
+      <c r="F71" s="179" t="s">
         <v>195</v>
       </c>
-      <c r="G71" s="172"/>
-      <c r="H71" s="172"/>
-      <c r="I71" s="172"/>
-      <c r="J71" s="172"/>
-      <c r="K71" s="172"/>
-      <c r="L71" s="172"/>
-      <c r="M71" s="172"/>
-      <c r="N71" s="172" t="s">
+      <c r="G71" s="179"/>
+      <c r="H71" s="179"/>
+      <c r="I71" s="179"/>
+      <c r="J71" s="179"/>
+      <c r="K71" s="179"/>
+      <c r="L71" s="179"/>
+      <c r="M71" s="179"/>
+      <c r="N71" s="179" t="s">
         <v>196</v>
       </c>
-      <c r="O71" s="172"/>
-      <c r="P71" s="172"/>
-      <c r="Q71" s="172"/>
+      <c r="O71" s="179"/>
+      <c r="P71" s="179"/>
+      <c r="Q71" s="179"/>
     </row>
     <row r="72" spans="2:17">
       <c r="B72" s="81" t="s">
@@ -12653,64 +12653,64 @@
       <c r="E72" s="80" t="s">
         <v>409</v>
       </c>
-      <c r="F72" s="172" t="s">
+      <c r="F72" s="179" t="s">
         <v>449</v>
       </c>
-      <c r="G72" s="172"/>
-      <c r="H72" s="172"/>
-      <c r="I72" s="172"/>
-      <c r="J72" s="172"/>
-      <c r="K72" s="172"/>
-      <c r="L72" s="172"/>
-      <c r="M72" s="172"/>
-      <c r="N72" s="172" t="s">
+      <c r="G72" s="179"/>
+      <c r="H72" s="179"/>
+      <c r="I72" s="179"/>
+      <c r="J72" s="179"/>
+      <c r="K72" s="179"/>
+      <c r="L72" s="179"/>
+      <c r="M72" s="179"/>
+      <c r="N72" s="179" t="s">
         <v>410</v>
       </c>
-      <c r="O72" s="172"/>
-      <c r="P72" s="172"/>
-      <c r="Q72" s="172"/>
+      <c r="O72" s="179"/>
+      <c r="P72" s="179"/>
+      <c r="Q72" s="179"/>
     </row>
     <row r="73" spans="2:17">
       <c r="E73" s="80" t="s">
         <v>386</v>
       </c>
-      <c r="F73" s="172" t="s">
+      <c r="F73" s="179" t="s">
         <v>411</v>
       </c>
-      <c r="G73" s="172"/>
-      <c r="H73" s="172"/>
-      <c r="I73" s="172"/>
-      <c r="J73" s="172"/>
-      <c r="K73" s="172"/>
-      <c r="L73" s="172"/>
-      <c r="M73" s="172"/>
-      <c r="N73" s="172" t="s">
+      <c r="G73" s="179"/>
+      <c r="H73" s="179"/>
+      <c r="I73" s="179"/>
+      <c r="J73" s="179"/>
+      <c r="K73" s="179"/>
+      <c r="L73" s="179"/>
+      <c r="M73" s="179"/>
+      <c r="N73" s="179" t="s">
         <v>411</v>
       </c>
-      <c r="O73" s="172"/>
-      <c r="P73" s="172"/>
-      <c r="Q73" s="172"/>
+      <c r="O73" s="179"/>
+      <c r="P73" s="179"/>
+      <c r="Q73" s="179"/>
     </row>
     <row r="74" spans="2:17">
       <c r="E74" s="80" t="s">
         <v>389</v>
       </c>
-      <c r="F74" s="172" t="s">
+      <c r="F74" s="179" t="s">
         <v>203</v>
       </c>
-      <c r="G74" s="172"/>
-      <c r="H74" s="172"/>
-      <c r="I74" s="172"/>
-      <c r="J74" s="172"/>
-      <c r="K74" s="172"/>
-      <c r="L74" s="172"/>
-      <c r="M74" s="172"/>
-      <c r="N74" s="172" t="s">
+      <c r="G74" s="179"/>
+      <c r="H74" s="179"/>
+      <c r="I74" s="179"/>
+      <c r="J74" s="179"/>
+      <c r="K74" s="179"/>
+      <c r="L74" s="179"/>
+      <c r="M74" s="179"/>
+      <c r="N74" s="179" t="s">
         <v>203</v>
       </c>
-      <c r="O74" s="172"/>
-      <c r="P74" s="172"/>
-      <c r="Q74" s="172"/>
+      <c r="O74" s="179"/>
+      <c r="P74" s="179"/>
+      <c r="Q74" s="179"/>
     </row>
     <row r="75" spans="2:17">
       <c r="E75" s="80"/>
@@ -12755,104 +12755,104 @@
       <c r="E76" s="80" t="s">
         <v>408</v>
       </c>
-      <c r="F76" s="172" t="s">
+      <c r="F76" s="179" t="s">
         <v>196</v>
       </c>
-      <c r="G76" s="172"/>
-      <c r="H76" s="172"/>
-      <c r="I76" s="172"/>
-      <c r="J76" s="172" t="s">
+      <c r="G76" s="179"/>
+      <c r="H76" s="179"/>
+      <c r="I76" s="179"/>
+      <c r="J76" s="179" t="s">
         <v>198</v>
       </c>
-      <c r="K76" s="172"/>
-      <c r="L76" s="172"/>
-      <c r="M76" s="172"/>
-      <c r="N76" s="172"/>
-      <c r="O76" s="172"/>
-      <c r="P76" s="172"/>
-      <c r="Q76" s="172"/>
+      <c r="K76" s="179"/>
+      <c r="L76" s="179"/>
+      <c r="M76" s="179"/>
+      <c r="N76" s="179"/>
+      <c r="O76" s="179"/>
+      <c r="P76" s="179"/>
+      <c r="Q76" s="179"/>
     </row>
     <row r="77" spans="2:17">
       <c r="E77" s="80" t="s">
         <v>409</v>
       </c>
-      <c r="F77" s="172" t="s">
+      <c r="F77" s="179" t="s">
         <v>410</v>
       </c>
-      <c r="G77" s="172"/>
-      <c r="H77" s="172"/>
-      <c r="I77" s="172"/>
-      <c r="J77" s="172" t="s">
+      <c r="G77" s="179"/>
+      <c r="H77" s="179"/>
+      <c r="I77" s="179"/>
+      <c r="J77" s="179" t="s">
         <v>420</v>
       </c>
-      <c r="K77" s="172"/>
-      <c r="L77" s="172"/>
-      <c r="M77" s="172"/>
-      <c r="N77" s="172"/>
-      <c r="O77" s="172"/>
-      <c r="P77" s="172"/>
-      <c r="Q77" s="172"/>
+      <c r="K77" s="179"/>
+      <c r="L77" s="179"/>
+      <c r="M77" s="179"/>
+      <c r="N77" s="179"/>
+      <c r="O77" s="179"/>
+      <c r="P77" s="179"/>
+      <c r="Q77" s="179"/>
     </row>
     <row r="78" spans="2:17">
       <c r="E78" s="80" t="s">
         <v>386</v>
       </c>
-      <c r="F78" s="172" t="s">
+      <c r="F78" s="179" t="s">
         <v>411</v>
       </c>
-      <c r="G78" s="172"/>
-      <c r="H78" s="172"/>
-      <c r="I78" s="172"/>
-      <c r="J78" s="172" t="s">
+      <c r="G78" s="179"/>
+      <c r="H78" s="179"/>
+      <c r="I78" s="179"/>
+      <c r="J78" s="179" t="s">
         <v>411</v>
       </c>
-      <c r="K78" s="172"/>
-      <c r="L78" s="172"/>
-      <c r="M78" s="172"/>
-      <c r="N78" s="172"/>
-      <c r="O78" s="172"/>
-      <c r="P78" s="172"/>
-      <c r="Q78" s="172"/>
+      <c r="K78" s="179"/>
+      <c r="L78" s="179"/>
+      <c r="M78" s="179"/>
+      <c r="N78" s="179"/>
+      <c r="O78" s="179"/>
+      <c r="P78" s="179"/>
+      <c r="Q78" s="179"/>
     </row>
     <row r="79" spans="2:17">
       <c r="E79" s="80" t="s">
         <v>389</v>
       </c>
-      <c r="F79" s="172" t="s">
+      <c r="F79" s="179" t="s">
         <v>203</v>
       </c>
-      <c r="G79" s="172"/>
-      <c r="H79" s="172"/>
-      <c r="I79" s="172"/>
-      <c r="J79" s="172" t="s">
+      <c r="G79" s="179"/>
+      <c r="H79" s="179"/>
+      <c r="I79" s="179"/>
+      <c r="J79" s="179" t="s">
         <v>203</v>
       </c>
-      <c r="K79" s="172"/>
-      <c r="L79" s="172"/>
-      <c r="M79" s="172"/>
-      <c r="N79" s="172"/>
-      <c r="O79" s="172"/>
-      <c r="P79" s="172"/>
-      <c r="Q79" s="172"/>
+      <c r="K79" s="179"/>
+      <c r="L79" s="179"/>
+      <c r="M79" s="179"/>
+      <c r="N79" s="179"/>
+      <c r="O79" s="179"/>
+      <c r="P79" s="179"/>
+      <c r="Q79" s="179"/>
     </row>
     <row r="80" spans="2:17" ht="29.25" customHeight="1">
       <c r="E80" s="80" t="s">
         <v>413</v>
       </c>
-      <c r="F80" s="184" t="s">
+      <c r="F80" s="180" t="s">
         <v>450</v>
       </c>
-      <c r="G80" s="184"/>
-      <c r="H80" s="184"/>
-      <c r="I80" s="184"/>
-      <c r="J80" s="184"/>
-      <c r="K80" s="184"/>
-      <c r="L80" s="184"/>
-      <c r="M80" s="184"/>
-      <c r="N80" s="184"/>
-      <c r="O80" s="184"/>
-      <c r="P80" s="184"/>
-      <c r="Q80" s="184"/>
+      <c r="G80" s="180"/>
+      <c r="H80" s="180"/>
+      <c r="I80" s="180"/>
+      <c r="J80" s="180"/>
+      <c r="K80" s="180"/>
+      <c r="L80" s="180"/>
+      <c r="M80" s="180"/>
+      <c r="N80" s="180"/>
+      <c r="O80" s="180"/>
+      <c r="P80" s="180"/>
+      <c r="Q80" s="180"/>
     </row>
     <row r="82" spans="2:17">
       <c r="B82" s="79" t="s">
@@ -12915,18 +12915,18 @@
       <c r="G83" s="82" t="s">
         <v>244</v>
       </c>
-      <c r="H83" s="172" t="s">
+      <c r="H83" s="179" t="s">
         <v>114</v>
       </c>
-      <c r="I83" s="172"/>
-      <c r="J83" s="172"/>
-      <c r="K83" s="172"/>
-      <c r="L83" s="172"/>
-      <c r="M83" s="172"/>
-      <c r="N83" s="172"/>
-      <c r="O83" s="172"/>
-      <c r="P83" s="172"/>
-      <c r="Q83" s="172"/>
+      <c r="I83" s="179"/>
+      <c r="J83" s="179"/>
+      <c r="K83" s="179"/>
+      <c r="L83" s="179"/>
+      <c r="M83" s="179"/>
+      <c r="N83" s="179"/>
+      <c r="O83" s="179"/>
+      <c r="P83" s="179"/>
+      <c r="Q83" s="179"/>
     </row>
     <row r="84" spans="2:17">
       <c r="E84" s="80" t="s">
@@ -12934,18 +12934,18 @@
       </c>
       <c r="F84" s="83"/>
       <c r="G84" s="83"/>
-      <c r="H84" s="172" t="s">
+      <c r="H84" s="179" t="s">
         <v>420</v>
       </c>
-      <c r="I84" s="172"/>
-      <c r="J84" s="172"/>
-      <c r="K84" s="172"/>
-      <c r="L84" s="172"/>
-      <c r="M84" s="172"/>
-      <c r="N84" s="172"/>
-      <c r="O84" s="172"/>
-      <c r="P84" s="172"/>
-      <c r="Q84" s="172"/>
+      <c r="I84" s="179"/>
+      <c r="J84" s="179"/>
+      <c r="K84" s="179"/>
+      <c r="L84" s="179"/>
+      <c r="M84" s="179"/>
+      <c r="N84" s="179"/>
+      <c r="O84" s="179"/>
+      <c r="P84" s="179"/>
+      <c r="Q84" s="179"/>
     </row>
     <row r="85" spans="2:17">
       <c r="E85" s="80" t="s">
@@ -12953,18 +12953,18 @@
       </c>
       <c r="F85" s="83"/>
       <c r="G85" s="83"/>
-      <c r="H85" s="172" t="s">
+      <c r="H85" s="179" t="s">
         <v>411</v>
       </c>
-      <c r="I85" s="172"/>
-      <c r="J85" s="172"/>
-      <c r="K85" s="172"/>
-      <c r="L85" s="172"/>
-      <c r="M85" s="172"/>
-      <c r="N85" s="172"/>
-      <c r="O85" s="172"/>
-      <c r="P85" s="172"/>
-      <c r="Q85" s="172"/>
+      <c r="I85" s="179"/>
+      <c r="J85" s="179"/>
+      <c r="K85" s="179"/>
+      <c r="L85" s="179"/>
+      <c r="M85" s="179"/>
+      <c r="N85" s="179"/>
+      <c r="O85" s="179"/>
+      <c r="P85" s="179"/>
+      <c r="Q85" s="179"/>
     </row>
     <row r="86" spans="2:17">
       <c r="E86" s="80" t="s">
@@ -12972,37 +12972,37 @@
       </c>
       <c r="F86" s="83"/>
       <c r="G86" s="83"/>
-      <c r="H86" s="172" t="s">
+      <c r="H86" s="179" t="s">
         <v>203</v>
       </c>
-      <c r="I86" s="172"/>
-      <c r="J86" s="172"/>
-      <c r="K86" s="172"/>
-      <c r="L86" s="172"/>
-      <c r="M86" s="172"/>
-      <c r="N86" s="172"/>
-      <c r="O86" s="172"/>
-      <c r="P86" s="172"/>
-      <c r="Q86" s="172"/>
+      <c r="I86" s="179"/>
+      <c r="J86" s="179"/>
+      <c r="K86" s="179"/>
+      <c r="L86" s="179"/>
+      <c r="M86" s="179"/>
+      <c r="N86" s="179"/>
+      <c r="O86" s="179"/>
+      <c r="P86" s="179"/>
+      <c r="Q86" s="179"/>
     </row>
     <row r="87" spans="2:17" ht="28.05" customHeight="1">
       <c r="E87" s="80" t="s">
         <v>413</v>
       </c>
-      <c r="F87" s="184" t="s">
+      <c r="F87" s="180" t="s">
         <v>453</v>
       </c>
-      <c r="G87" s="184"/>
-      <c r="H87" s="184"/>
-      <c r="I87" s="184"/>
-      <c r="J87" s="184"/>
-      <c r="K87" s="184"/>
-      <c r="L87" s="184"/>
-      <c r="M87" s="184"/>
-      <c r="N87" s="184"/>
-      <c r="O87" s="184"/>
-      <c r="P87" s="184"/>
-      <c r="Q87" s="184"/>
+      <c r="G87" s="180"/>
+      <c r="H87" s="180"/>
+      <c r="I87" s="180"/>
+      <c r="J87" s="180"/>
+      <c r="K87" s="180"/>
+      <c r="L87" s="180"/>
+      <c r="M87" s="180"/>
+      <c r="N87" s="180"/>
+      <c r="O87" s="180"/>
+      <c r="P87" s="180"/>
+      <c r="Q87" s="180"/>
     </row>
     <row r="88" spans="2:17">
       <c r="E88" s="85"/>
@@ -13080,18 +13080,18 @@
       <c r="G90" s="82" t="s">
         <v>244</v>
       </c>
-      <c r="H90" s="172" t="s">
+      <c r="H90" s="179" t="s">
         <v>117</v>
       </c>
-      <c r="I90" s="172"/>
-      <c r="J90" s="172"/>
-      <c r="K90" s="172"/>
-      <c r="L90" s="172"/>
-      <c r="M90" s="172"/>
-      <c r="N90" s="172"/>
-      <c r="O90" s="172"/>
-      <c r="P90" s="172"/>
-      <c r="Q90" s="172"/>
+      <c r="I90" s="179"/>
+      <c r="J90" s="179"/>
+      <c r="K90" s="179"/>
+      <c r="L90" s="179"/>
+      <c r="M90" s="179"/>
+      <c r="N90" s="179"/>
+      <c r="O90" s="179"/>
+      <c r="P90" s="179"/>
+      <c r="Q90" s="179"/>
     </row>
     <row r="91" spans="2:17">
       <c r="E91" s="80" t="s">
@@ -13099,18 +13099,18 @@
       </c>
       <c r="F91" s="83"/>
       <c r="G91" s="83"/>
-      <c r="H91" s="172" t="s">
+      <c r="H91" s="179" t="s">
         <v>420</v>
       </c>
-      <c r="I91" s="172"/>
-      <c r="J91" s="172"/>
-      <c r="K91" s="172"/>
-      <c r="L91" s="172"/>
-      <c r="M91" s="172"/>
-      <c r="N91" s="172"/>
-      <c r="O91" s="172"/>
-      <c r="P91" s="172"/>
-      <c r="Q91" s="172"/>
+      <c r="I91" s="179"/>
+      <c r="J91" s="179"/>
+      <c r="K91" s="179"/>
+      <c r="L91" s="179"/>
+      <c r="M91" s="179"/>
+      <c r="N91" s="179"/>
+      <c r="O91" s="179"/>
+      <c r="P91" s="179"/>
+      <c r="Q91" s="179"/>
     </row>
     <row r="92" spans="2:17">
       <c r="E92" s="80" t="s">
@@ -13118,18 +13118,18 @@
       </c>
       <c r="F92" s="83"/>
       <c r="G92" s="83"/>
-      <c r="H92" s="172" t="s">
+      <c r="H92" s="179" t="s">
         <v>411</v>
       </c>
-      <c r="I92" s="172"/>
-      <c r="J92" s="172"/>
-      <c r="K92" s="172"/>
-      <c r="L92" s="172"/>
-      <c r="M92" s="172"/>
-      <c r="N92" s="172"/>
-      <c r="O92" s="172"/>
-      <c r="P92" s="172"/>
-      <c r="Q92" s="172"/>
+      <c r="I92" s="179"/>
+      <c r="J92" s="179"/>
+      <c r="K92" s="179"/>
+      <c r="L92" s="179"/>
+      <c r="M92" s="179"/>
+      <c r="N92" s="179"/>
+      <c r="O92" s="179"/>
+      <c r="P92" s="179"/>
+      <c r="Q92" s="179"/>
     </row>
     <row r="93" spans="2:17">
       <c r="E93" s="80" t="s">
@@ -13137,37 +13137,37 @@
       </c>
       <c r="F93" s="83"/>
       <c r="G93" s="83"/>
-      <c r="H93" s="172" t="s">
+      <c r="H93" s="179" t="s">
         <v>203</v>
       </c>
-      <c r="I93" s="172"/>
-      <c r="J93" s="172"/>
-      <c r="K93" s="172"/>
-      <c r="L93" s="172"/>
-      <c r="M93" s="172"/>
-      <c r="N93" s="172"/>
-      <c r="O93" s="172"/>
-      <c r="P93" s="172"/>
-      <c r="Q93" s="172"/>
+      <c r="I93" s="179"/>
+      <c r="J93" s="179"/>
+      <c r="K93" s="179"/>
+      <c r="L93" s="179"/>
+      <c r="M93" s="179"/>
+      <c r="N93" s="179"/>
+      <c r="O93" s="179"/>
+      <c r="P93" s="179"/>
+      <c r="Q93" s="179"/>
     </row>
     <row r="94" spans="2:17" ht="29.25" customHeight="1">
       <c r="E94" s="80" t="s">
         <v>413</v>
       </c>
-      <c r="F94" s="184" t="s">
+      <c r="F94" s="180" t="s">
         <v>456</v>
       </c>
-      <c r="G94" s="184"/>
-      <c r="H94" s="184"/>
-      <c r="I94" s="184"/>
-      <c r="J94" s="184"/>
-      <c r="K94" s="184"/>
-      <c r="L94" s="184"/>
-      <c r="M94" s="184"/>
-      <c r="N94" s="184"/>
-      <c r="O94" s="184"/>
-      <c r="P94" s="184"/>
-      <c r="Q94" s="184"/>
+      <c r="G94" s="180"/>
+      <c r="H94" s="180"/>
+      <c r="I94" s="180"/>
+      <c r="J94" s="180"/>
+      <c r="K94" s="180"/>
+      <c r="L94" s="180"/>
+      <c r="M94" s="180"/>
+      <c r="N94" s="180"/>
+      <c r="O94" s="180"/>
+      <c r="P94" s="180"/>
+      <c r="Q94" s="180"/>
     </row>
     <row r="95" spans="2:17" ht="16.5" customHeight="1"/>
     <row r="96" spans="2:17">
@@ -13225,96 +13225,96 @@
       <c r="E97" s="80" t="s">
         <v>408</v>
       </c>
-      <c r="F97" s="171" t="s">
+      <c r="F97" s="173" t="s">
         <v>120</v>
       </c>
-      <c r="G97" s="185"/>
-      <c r="H97" s="185"/>
-      <c r="I97" s="185"/>
-      <c r="J97" s="185"/>
-      <c r="K97" s="185"/>
-      <c r="L97" s="185"/>
-      <c r="M97" s="185"/>
-      <c r="N97" s="185"/>
-      <c r="O97" s="185"/>
-      <c r="P97" s="185"/>
-      <c r="Q97" s="179"/>
+      <c r="G97" s="174"/>
+      <c r="H97" s="174"/>
+      <c r="I97" s="174"/>
+      <c r="J97" s="174"/>
+      <c r="K97" s="174"/>
+      <c r="L97" s="174"/>
+      <c r="M97" s="174"/>
+      <c r="N97" s="174"/>
+      <c r="O97" s="174"/>
+      <c r="P97" s="174"/>
+      <c r="Q97" s="175"/>
     </row>
     <row r="98" spans="2:17">
       <c r="E98" s="80" t="s">
         <v>409</v>
       </c>
-      <c r="F98" s="171" t="s">
+      <c r="F98" s="173" t="s">
         <v>420</v>
       </c>
-      <c r="G98" s="185"/>
-      <c r="H98" s="185"/>
-      <c r="I98" s="185"/>
-      <c r="J98" s="185"/>
-      <c r="K98" s="185"/>
-      <c r="L98" s="185"/>
-      <c r="M98" s="185"/>
-      <c r="N98" s="185"/>
-      <c r="O98" s="185"/>
-      <c r="P98" s="185"/>
-      <c r="Q98" s="179"/>
+      <c r="G98" s="174"/>
+      <c r="H98" s="174"/>
+      <c r="I98" s="174"/>
+      <c r="J98" s="174"/>
+      <c r="K98" s="174"/>
+      <c r="L98" s="174"/>
+      <c r="M98" s="174"/>
+      <c r="N98" s="174"/>
+      <c r="O98" s="174"/>
+      <c r="P98" s="174"/>
+      <c r="Q98" s="175"/>
     </row>
     <row r="99" spans="2:17">
       <c r="E99" s="80" t="s">
         <v>386</v>
       </c>
-      <c r="F99" s="171" t="s">
+      <c r="F99" s="173" t="s">
         <v>411</v>
       </c>
-      <c r="G99" s="185"/>
-      <c r="H99" s="185"/>
-      <c r="I99" s="185"/>
-      <c r="J99" s="185"/>
-      <c r="K99" s="185"/>
-      <c r="L99" s="185"/>
-      <c r="M99" s="185"/>
-      <c r="N99" s="185"/>
-      <c r="O99" s="185"/>
-      <c r="P99" s="185"/>
-      <c r="Q99" s="179"/>
+      <c r="G99" s="174"/>
+      <c r="H99" s="174"/>
+      <c r="I99" s="174"/>
+      <c r="J99" s="174"/>
+      <c r="K99" s="174"/>
+      <c r="L99" s="174"/>
+      <c r="M99" s="174"/>
+      <c r="N99" s="174"/>
+      <c r="O99" s="174"/>
+      <c r="P99" s="174"/>
+      <c r="Q99" s="175"/>
     </row>
     <row r="100" spans="2:17">
       <c r="E100" s="80" t="s">
         <v>389</v>
       </c>
-      <c r="F100" s="171" t="s">
+      <c r="F100" s="173" t="s">
         <v>412</v>
       </c>
-      <c r="G100" s="185"/>
-      <c r="H100" s="185"/>
-      <c r="I100" s="185"/>
-      <c r="J100" s="185"/>
-      <c r="K100" s="185"/>
-      <c r="L100" s="185"/>
-      <c r="M100" s="185"/>
-      <c r="N100" s="185"/>
-      <c r="O100" s="185"/>
-      <c r="P100" s="185"/>
-      <c r="Q100" s="179"/>
+      <c r="G100" s="174"/>
+      <c r="H100" s="174"/>
+      <c r="I100" s="174"/>
+      <c r="J100" s="174"/>
+      <c r="K100" s="174"/>
+      <c r="L100" s="174"/>
+      <c r="M100" s="174"/>
+      <c r="N100" s="174"/>
+      <c r="O100" s="174"/>
+      <c r="P100" s="174"/>
+      <c r="Q100" s="175"/>
     </row>
     <row r="101" spans="2:17">
       <c r="E101" s="80" t="s">
         <v>413</v>
       </c>
-      <c r="F101" s="180" t="s">
+      <c r="F101" s="170" t="s">
         <v>458</v>
       </c>
-      <c r="G101" s="186"/>
-      <c r="H101" s="186"/>
-      <c r="I101" s="186"/>
-      <c r="J101" s="186"/>
-      <c r="K101" s="186"/>
-      <c r="L101" s="186"/>
-      <c r="M101" s="186"/>
-      <c r="N101" s="186"/>
-      <c r="O101" s="186"/>
-      <c r="P101" s="186"/>
-      <c r="Q101" s="187"/>
+      <c r="G101" s="171"/>
+      <c r="H101" s="171"/>
+      <c r="I101" s="171"/>
+      <c r="J101" s="171"/>
+      <c r="K101" s="171"/>
+      <c r="L101" s="171"/>
+      <c r="M101" s="171"/>
+      <c r="N101" s="171"/>
+      <c r="O101" s="171"/>
+      <c r="P101" s="171"/>
+      <c r="Q101" s="172"/>
     </row>
     <row r="103" spans="2:17">
       <c r="B103" s="79" t="s">
@@ -13371,96 +13371,96 @@
       <c r="E104" s="80" t="s">
         <v>408</v>
       </c>
-      <c r="F104" s="171" t="s">
+      <c r="F104" s="173" t="s">
         <v>123</v>
       </c>
-      <c r="G104" s="185"/>
-      <c r="H104" s="185"/>
-      <c r="I104" s="185"/>
-      <c r="J104" s="185"/>
-      <c r="K104" s="185"/>
-      <c r="L104" s="185"/>
-      <c r="M104" s="185"/>
-      <c r="N104" s="185"/>
-      <c r="O104" s="185"/>
-      <c r="P104" s="185"/>
-      <c r="Q104" s="179"/>
+      <c r="G104" s="174"/>
+      <c r="H104" s="174"/>
+      <c r="I104" s="174"/>
+      <c r="J104" s="174"/>
+      <c r="K104" s="174"/>
+      <c r="L104" s="174"/>
+      <c r="M104" s="174"/>
+      <c r="N104" s="174"/>
+      <c r="O104" s="174"/>
+      <c r="P104" s="174"/>
+      <c r="Q104" s="175"/>
     </row>
     <row r="105" spans="2:17">
       <c r="E105" s="80" t="s">
         <v>409</v>
       </c>
-      <c r="F105" s="171" t="s">
+      <c r="F105" s="173" t="s">
         <v>420</v>
       </c>
-      <c r="G105" s="185"/>
-      <c r="H105" s="185"/>
-      <c r="I105" s="185"/>
-      <c r="J105" s="185"/>
-      <c r="K105" s="185"/>
-      <c r="L105" s="185"/>
-      <c r="M105" s="185"/>
-      <c r="N105" s="185"/>
-      <c r="O105" s="185"/>
-      <c r="P105" s="185"/>
-      <c r="Q105" s="179"/>
+      <c r="G105" s="174"/>
+      <c r="H105" s="174"/>
+      <c r="I105" s="174"/>
+      <c r="J105" s="174"/>
+      <c r="K105" s="174"/>
+      <c r="L105" s="174"/>
+      <c r="M105" s="174"/>
+      <c r="N105" s="174"/>
+      <c r="O105" s="174"/>
+      <c r="P105" s="174"/>
+      <c r="Q105" s="175"/>
     </row>
     <row r="106" spans="2:17">
       <c r="E106" s="80" t="s">
         <v>386</v>
       </c>
-      <c r="F106" s="171" t="s">
+      <c r="F106" s="173" t="s">
         <v>411</v>
       </c>
-      <c r="G106" s="185"/>
-      <c r="H106" s="185"/>
-      <c r="I106" s="185"/>
-      <c r="J106" s="185"/>
-      <c r="K106" s="185"/>
-      <c r="L106" s="185"/>
-      <c r="M106" s="185"/>
-      <c r="N106" s="185"/>
-      <c r="O106" s="185"/>
-      <c r="P106" s="185"/>
-      <c r="Q106" s="179"/>
+      <c r="G106" s="174"/>
+      <c r="H106" s="174"/>
+      <c r="I106" s="174"/>
+      <c r="J106" s="174"/>
+      <c r="K106" s="174"/>
+      <c r="L106" s="174"/>
+      <c r="M106" s="174"/>
+      <c r="N106" s="174"/>
+      <c r="O106" s="174"/>
+      <c r="P106" s="174"/>
+      <c r="Q106" s="175"/>
     </row>
     <row r="107" spans="2:17">
       <c r="E107" s="80" t="s">
         <v>389</v>
       </c>
-      <c r="F107" s="171" t="s">
+      <c r="F107" s="173" t="s">
         <v>412</v>
       </c>
-      <c r="G107" s="185"/>
-      <c r="H107" s="185"/>
-      <c r="I107" s="185"/>
-      <c r="J107" s="185"/>
-      <c r="K107" s="185"/>
-      <c r="L107" s="185"/>
-      <c r="M107" s="185"/>
-      <c r="N107" s="185"/>
-      <c r="O107" s="185"/>
-      <c r="P107" s="185"/>
-      <c r="Q107" s="179"/>
+      <c r="G107" s="174"/>
+      <c r="H107" s="174"/>
+      <c r="I107" s="174"/>
+      <c r="J107" s="174"/>
+      <c r="K107" s="174"/>
+      <c r="L107" s="174"/>
+      <c r="M107" s="174"/>
+      <c r="N107" s="174"/>
+      <c r="O107" s="174"/>
+      <c r="P107" s="174"/>
+      <c r="Q107" s="175"/>
     </row>
     <row r="108" spans="2:17">
       <c r="E108" s="80" t="s">
         <v>413</v>
       </c>
-      <c r="F108" s="180" t="s">
+      <c r="F108" s="170" t="s">
         <v>460</v>
       </c>
-      <c r="G108" s="186"/>
-      <c r="H108" s="186"/>
-      <c r="I108" s="186"/>
-      <c r="J108" s="186"/>
-      <c r="K108" s="186"/>
-      <c r="L108" s="186"/>
-      <c r="M108" s="186"/>
-      <c r="N108" s="186"/>
-      <c r="O108" s="186"/>
-      <c r="P108" s="186"/>
-      <c r="Q108" s="187"/>
+      <c r="G108" s="171"/>
+      <c r="H108" s="171"/>
+      <c r="I108" s="171"/>
+      <c r="J108" s="171"/>
+      <c r="K108" s="171"/>
+      <c r="L108" s="171"/>
+      <c r="M108" s="171"/>
+      <c r="N108" s="171"/>
+      <c r="O108" s="171"/>
+      <c r="P108" s="171"/>
+      <c r="Q108" s="172"/>
     </row>
     <row r="110" spans="2:17">
       <c r="B110" s="79" t="s">
@@ -13517,96 +13517,96 @@
       <c r="E111" s="80" t="s">
         <v>408</v>
       </c>
-      <c r="F111" s="171" t="s">
+      <c r="F111" s="173" t="s">
         <v>126</v>
       </c>
-      <c r="G111" s="185"/>
-      <c r="H111" s="185"/>
-      <c r="I111" s="185"/>
-      <c r="J111" s="185"/>
-      <c r="K111" s="185"/>
-      <c r="L111" s="185"/>
-      <c r="M111" s="185"/>
-      <c r="N111" s="185"/>
-      <c r="O111" s="185"/>
-      <c r="P111" s="185"/>
-      <c r="Q111" s="179"/>
+      <c r="G111" s="174"/>
+      <c r="H111" s="174"/>
+      <c r="I111" s="174"/>
+      <c r="J111" s="174"/>
+      <c r="K111" s="174"/>
+      <c r="L111" s="174"/>
+      <c r="M111" s="174"/>
+      <c r="N111" s="174"/>
+      <c r="O111" s="174"/>
+      <c r="P111" s="174"/>
+      <c r="Q111" s="175"/>
     </row>
     <row r="112" spans="2:17">
       <c r="E112" s="80" t="s">
         <v>409</v>
       </c>
-      <c r="F112" s="171" t="s">
+      <c r="F112" s="173" t="s">
         <v>420</v>
       </c>
-      <c r="G112" s="185"/>
-      <c r="H112" s="185"/>
-      <c r="I112" s="185"/>
-      <c r="J112" s="185"/>
-      <c r="K112" s="185"/>
-      <c r="L112" s="185"/>
-      <c r="M112" s="185"/>
-      <c r="N112" s="185"/>
-      <c r="O112" s="185"/>
-      <c r="P112" s="185"/>
-      <c r="Q112" s="179"/>
+      <c r="G112" s="174"/>
+      <c r="H112" s="174"/>
+      <c r="I112" s="174"/>
+      <c r="J112" s="174"/>
+      <c r="K112" s="174"/>
+      <c r="L112" s="174"/>
+      <c r="M112" s="174"/>
+      <c r="N112" s="174"/>
+      <c r="O112" s="174"/>
+      <c r="P112" s="174"/>
+      <c r="Q112" s="175"/>
     </row>
     <row r="113" spans="2:17">
       <c r="E113" s="80" t="s">
         <v>386</v>
       </c>
-      <c r="F113" s="171" t="s">
+      <c r="F113" s="173" t="s">
         <v>411</v>
       </c>
-      <c r="G113" s="185"/>
-      <c r="H113" s="185"/>
-      <c r="I113" s="185"/>
-      <c r="J113" s="185"/>
-      <c r="K113" s="185"/>
-      <c r="L113" s="185"/>
-      <c r="M113" s="185"/>
-      <c r="N113" s="185"/>
-      <c r="O113" s="185"/>
-      <c r="P113" s="185"/>
-      <c r="Q113" s="179"/>
+      <c r="G113" s="174"/>
+      <c r="H113" s="174"/>
+      <c r="I113" s="174"/>
+      <c r="J113" s="174"/>
+      <c r="K113" s="174"/>
+      <c r="L113" s="174"/>
+      <c r="M113" s="174"/>
+      <c r="N113" s="174"/>
+      <c r="O113" s="174"/>
+      <c r="P113" s="174"/>
+      <c r="Q113" s="175"/>
     </row>
     <row r="114" spans="2:17">
       <c r="E114" s="80" t="s">
         <v>389</v>
       </c>
-      <c r="F114" s="171" t="s">
+      <c r="F114" s="173" t="s">
         <v>412</v>
       </c>
-      <c r="G114" s="185"/>
-      <c r="H114" s="185"/>
-      <c r="I114" s="185"/>
-      <c r="J114" s="185"/>
-      <c r="K114" s="185"/>
-      <c r="L114" s="185"/>
-      <c r="M114" s="185"/>
-      <c r="N114" s="185"/>
-      <c r="O114" s="185"/>
-      <c r="P114" s="185"/>
-      <c r="Q114" s="179"/>
+      <c r="G114" s="174"/>
+      <c r="H114" s="174"/>
+      <c r="I114" s="174"/>
+      <c r="J114" s="174"/>
+      <c r="K114" s="174"/>
+      <c r="L114" s="174"/>
+      <c r="M114" s="174"/>
+      <c r="N114" s="174"/>
+      <c r="O114" s="174"/>
+      <c r="P114" s="174"/>
+      <c r="Q114" s="175"/>
     </row>
     <row r="115" spans="2:17">
       <c r="E115" s="80" t="s">
         <v>413</v>
       </c>
-      <c r="F115" s="180" t="s">
+      <c r="F115" s="170" t="s">
         <v>462</v>
       </c>
-      <c r="G115" s="186"/>
-      <c r="H115" s="186"/>
-      <c r="I115" s="186"/>
-      <c r="J115" s="186"/>
-      <c r="K115" s="186"/>
-      <c r="L115" s="186"/>
-      <c r="M115" s="186"/>
-      <c r="N115" s="186"/>
-      <c r="O115" s="186"/>
-      <c r="P115" s="186"/>
-      <c r="Q115" s="187"/>
+      <c r="G115" s="171"/>
+      <c r="H115" s="171"/>
+      <c r="I115" s="171"/>
+      <c r="J115" s="171"/>
+      <c r="K115" s="171"/>
+      <c r="L115" s="171"/>
+      <c r="M115" s="171"/>
+      <c r="N115" s="171"/>
+      <c r="O115" s="171"/>
+      <c r="P115" s="171"/>
+      <c r="Q115" s="172"/>
     </row>
     <row r="117" spans="2:17">
       <c r="B117" s="79" t="s">
@@ -13663,104 +13663,104 @@
       <c r="E118" s="80" t="s">
         <v>408</v>
       </c>
-      <c r="F118" s="172" t="s">
+      <c r="F118" s="179" t="s">
         <v>129</v>
       </c>
-      <c r="G118" s="172"/>
-      <c r="H118" s="172"/>
-      <c r="I118" s="172"/>
-      <c r="J118" s="172" t="s">
+      <c r="G118" s="179"/>
+      <c r="H118" s="179"/>
+      <c r="I118" s="179"/>
+      <c r="J118" s="179" t="s">
         <v>130</v>
       </c>
-      <c r="K118" s="172"/>
-      <c r="L118" s="172"/>
-      <c r="M118" s="172"/>
-      <c r="N118" s="172" t="s">
+      <c r="K118" s="179"/>
+      <c r="L118" s="179"/>
+      <c r="M118" s="179"/>
+      <c r="N118" s="179" t="s">
         <v>131</v>
       </c>
-      <c r="O118" s="172"/>
-      <c r="P118" s="172"/>
-      <c r="Q118" s="172"/>
+      <c r="O118" s="179"/>
+      <c r="P118" s="179"/>
+      <c r="Q118" s="179"/>
     </row>
     <row r="119" spans="2:17">
       <c r="E119" s="80" t="s">
         <v>409</v>
       </c>
-      <c r="F119" s="171" t="s">
+      <c r="F119" s="173" t="s">
         <v>465</v>
       </c>
-      <c r="G119" s="185"/>
-      <c r="H119" s="185"/>
-      <c r="I119" s="185"/>
-      <c r="J119" s="171" t="s">
+      <c r="G119" s="174"/>
+      <c r="H119" s="174"/>
+      <c r="I119" s="174"/>
+      <c r="J119" s="173" t="s">
         <v>465</v>
       </c>
-      <c r="K119" s="185"/>
-      <c r="L119" s="185"/>
-      <c r="M119" s="185"/>
-      <c r="N119" s="171" t="s">
+      <c r="K119" s="174"/>
+      <c r="L119" s="174"/>
+      <c r="M119" s="174"/>
+      <c r="N119" s="173" t="s">
         <v>465</v>
       </c>
-      <c r="O119" s="185"/>
-      <c r="P119" s="185"/>
-      <c r="Q119" s="185"/>
+      <c r="O119" s="174"/>
+      <c r="P119" s="174"/>
+      <c r="Q119" s="174"/>
     </row>
     <row r="120" spans="2:17">
       <c r="E120" s="80" t="s">
         <v>386</v>
       </c>
-      <c r="F120" s="171" t="s">
+      <c r="F120" s="173" t="s">
         <v>411</v>
       </c>
-      <c r="G120" s="185"/>
-      <c r="H120" s="185"/>
-      <c r="I120" s="185"/>
-      <c r="J120" s="185"/>
-      <c r="K120" s="185"/>
-      <c r="L120" s="185"/>
-      <c r="M120" s="185"/>
-      <c r="N120" s="185"/>
-      <c r="O120" s="185"/>
-      <c r="P120" s="185"/>
-      <c r="Q120" s="179"/>
+      <c r="G120" s="174"/>
+      <c r="H120" s="174"/>
+      <c r="I120" s="174"/>
+      <c r="J120" s="174"/>
+      <c r="K120" s="174"/>
+      <c r="L120" s="174"/>
+      <c r="M120" s="174"/>
+      <c r="N120" s="174"/>
+      <c r="O120" s="174"/>
+      <c r="P120" s="174"/>
+      <c r="Q120" s="175"/>
     </row>
     <row r="121" spans="2:17">
       <c r="E121" s="80" t="s">
         <v>389</v>
       </c>
-      <c r="F121" s="171" t="s">
+      <c r="F121" s="173" t="s">
         <v>203</v>
       </c>
-      <c r="G121" s="185"/>
-      <c r="H121" s="185"/>
-      <c r="I121" s="185"/>
-      <c r="J121" s="185"/>
-      <c r="K121" s="185"/>
-      <c r="L121" s="185"/>
-      <c r="M121" s="185"/>
-      <c r="N121" s="185"/>
-      <c r="O121" s="185"/>
-      <c r="P121" s="185"/>
-      <c r="Q121" s="179"/>
+      <c r="G121" s="174"/>
+      <c r="H121" s="174"/>
+      <c r="I121" s="174"/>
+      <c r="J121" s="174"/>
+      <c r="K121" s="174"/>
+      <c r="L121" s="174"/>
+      <c r="M121" s="174"/>
+      <c r="N121" s="174"/>
+      <c r="O121" s="174"/>
+      <c r="P121" s="174"/>
+      <c r="Q121" s="175"/>
     </row>
     <row r="122" spans="2:17" ht="300.39999999999998" customHeight="1">
       <c r="E122" s="80" t="s">
         <v>413</v>
       </c>
-      <c r="F122" s="178" t="s">
+      <c r="F122" s="176" t="s">
         <v>466</v>
       </c>
-      <c r="G122" s="188"/>
-      <c r="H122" s="188"/>
-      <c r="I122" s="188"/>
-      <c r="J122" s="188"/>
-      <c r="K122" s="188"/>
-      <c r="L122" s="188"/>
-      <c r="M122" s="188"/>
-      <c r="N122" s="188"/>
-      <c r="O122" s="188"/>
-      <c r="P122" s="188"/>
-      <c r="Q122" s="189"/>
+      <c r="G122" s="177"/>
+      <c r="H122" s="177"/>
+      <c r="I122" s="177"/>
+      <c r="J122" s="177"/>
+      <c r="K122" s="177"/>
+      <c r="L122" s="177"/>
+      <c r="M122" s="177"/>
+      <c r="N122" s="177"/>
+      <c r="O122" s="177"/>
+      <c r="P122" s="177"/>
+      <c r="Q122" s="178"/>
     </row>
     <row r="124" spans="2:17">
       <c r="B124" s="79" t="s">
@@ -13823,94 +13823,94 @@
       <c r="G125" s="82" t="s">
         <v>244</v>
       </c>
-      <c r="H125" s="171" t="s">
+      <c r="H125" s="173" t="s">
         <v>469</v>
       </c>
-      <c r="I125" s="185"/>
-      <c r="J125" s="185"/>
-      <c r="K125" s="185"/>
-      <c r="L125" s="185"/>
-      <c r="M125" s="185"/>
-      <c r="N125" s="185"/>
-      <c r="O125" s="185"/>
-      <c r="P125" s="185"/>
-      <c r="Q125" s="179"/>
+      <c r="I125" s="174"/>
+      <c r="J125" s="174"/>
+      <c r="K125" s="174"/>
+      <c r="L125" s="174"/>
+      <c r="M125" s="174"/>
+      <c r="N125" s="174"/>
+      <c r="O125" s="174"/>
+      <c r="P125" s="174"/>
+      <c r="Q125" s="175"/>
     </row>
     <row r="126" spans="2:17">
       <c r="E126" s="80" t="s">
         <v>409</v>
       </c>
-      <c r="F126" s="171" t="s">
+      <c r="F126" s="173" t="s">
         <v>470</v>
       </c>
-      <c r="G126" s="185"/>
-      <c r="H126" s="185"/>
-      <c r="I126" s="185"/>
-      <c r="J126" s="185"/>
-      <c r="K126" s="185"/>
-      <c r="L126" s="185"/>
-      <c r="M126" s="185"/>
-      <c r="N126" s="185"/>
-      <c r="O126" s="185"/>
-      <c r="P126" s="185"/>
-      <c r="Q126" s="179"/>
+      <c r="G126" s="174"/>
+      <c r="H126" s="174"/>
+      <c r="I126" s="174"/>
+      <c r="J126" s="174"/>
+      <c r="K126" s="174"/>
+      <c r="L126" s="174"/>
+      <c r="M126" s="174"/>
+      <c r="N126" s="174"/>
+      <c r="O126" s="174"/>
+      <c r="P126" s="174"/>
+      <c r="Q126" s="175"/>
     </row>
     <row r="127" spans="2:17">
       <c r="E127" s="80" t="s">
         <v>386</v>
       </c>
-      <c r="F127" s="171" t="s">
+      <c r="F127" s="173" t="s">
         <v>411</v>
       </c>
-      <c r="G127" s="185"/>
-      <c r="H127" s="185"/>
-      <c r="I127" s="185"/>
-      <c r="J127" s="185"/>
-      <c r="K127" s="185"/>
-      <c r="L127" s="185"/>
-      <c r="M127" s="185"/>
-      <c r="N127" s="185"/>
-      <c r="O127" s="185"/>
-      <c r="P127" s="185"/>
-      <c r="Q127" s="179"/>
+      <c r="G127" s="174"/>
+      <c r="H127" s="174"/>
+      <c r="I127" s="174"/>
+      <c r="J127" s="174"/>
+      <c r="K127" s="174"/>
+      <c r="L127" s="174"/>
+      <c r="M127" s="174"/>
+      <c r="N127" s="174"/>
+      <c r="O127" s="174"/>
+      <c r="P127" s="174"/>
+      <c r="Q127" s="175"/>
     </row>
     <row r="128" spans="2:17">
       <c r="E128" s="80" t="s">
         <v>389</v>
       </c>
-      <c r="F128" s="171" t="s">
+      <c r="F128" s="173" t="s">
         <v>203</v>
       </c>
-      <c r="G128" s="185"/>
-      <c r="H128" s="185"/>
-      <c r="I128" s="185"/>
-      <c r="J128" s="185"/>
-      <c r="K128" s="185"/>
-      <c r="L128" s="185"/>
-      <c r="M128" s="185"/>
-      <c r="N128" s="185"/>
-      <c r="O128" s="185"/>
-      <c r="P128" s="185"/>
-      <c r="Q128" s="179"/>
+      <c r="G128" s="174"/>
+      <c r="H128" s="174"/>
+      <c r="I128" s="174"/>
+      <c r="J128" s="174"/>
+      <c r="K128" s="174"/>
+      <c r="L128" s="174"/>
+      <c r="M128" s="174"/>
+      <c r="N128" s="174"/>
+      <c r="O128" s="174"/>
+      <c r="P128" s="174"/>
+      <c r="Q128" s="175"/>
     </row>
     <row r="129" spans="2:17">
       <c r="E129" s="80" t="s">
         <v>413</v>
       </c>
-      <c r="F129" s="180" t="s">
+      <c r="F129" s="170" t="s">
         <v>471</v>
       </c>
-      <c r="G129" s="186"/>
-      <c r="H129" s="186"/>
-      <c r="I129" s="186"/>
-      <c r="J129" s="186"/>
-      <c r="K129" s="186"/>
-      <c r="L129" s="186"/>
-      <c r="M129" s="186"/>
-      <c r="N129" s="186"/>
-      <c r="O129" s="186"/>
-      <c r="P129" s="186"/>
-      <c r="Q129" s="187"/>
+      <c r="G129" s="171"/>
+      <c r="H129" s="171"/>
+      <c r="I129" s="171"/>
+      <c r="J129" s="171"/>
+      <c r="K129" s="171"/>
+      <c r="L129" s="171"/>
+      <c r="M129" s="171"/>
+      <c r="N129" s="171"/>
+      <c r="O129" s="171"/>
+      <c r="P129" s="171"/>
+      <c r="Q129" s="172"/>
     </row>
     <row r="131" spans="2:17">
       <c r="B131" s="79" t="s">
@@ -13973,94 +13973,94 @@
       <c r="G132" s="82" t="s">
         <v>244</v>
       </c>
-      <c r="H132" s="171" t="s">
+      <c r="H132" s="173" t="s">
         <v>474</v>
       </c>
-      <c r="I132" s="185"/>
-      <c r="J132" s="185"/>
-      <c r="K132" s="185"/>
-      <c r="L132" s="185"/>
-      <c r="M132" s="185"/>
-      <c r="N132" s="185"/>
-      <c r="O132" s="185"/>
-      <c r="P132" s="185"/>
-      <c r="Q132" s="179"/>
+      <c r="I132" s="174"/>
+      <c r="J132" s="174"/>
+      <c r="K132" s="174"/>
+      <c r="L132" s="174"/>
+      <c r="M132" s="174"/>
+      <c r="N132" s="174"/>
+      <c r="O132" s="174"/>
+      <c r="P132" s="174"/>
+      <c r="Q132" s="175"/>
     </row>
     <row r="133" spans="2:17">
       <c r="E133" s="80" t="s">
         <v>409</v>
       </c>
-      <c r="F133" s="171" t="s">
+      <c r="F133" s="173" t="s">
         <v>470</v>
       </c>
-      <c r="G133" s="185"/>
-      <c r="H133" s="185"/>
-      <c r="I133" s="185"/>
-      <c r="J133" s="185"/>
-      <c r="K133" s="185"/>
-      <c r="L133" s="185"/>
-      <c r="M133" s="185"/>
-      <c r="N133" s="185"/>
-      <c r="O133" s="185"/>
-      <c r="P133" s="185"/>
-      <c r="Q133" s="179"/>
+      <c r="G133" s="174"/>
+      <c r="H133" s="174"/>
+      <c r="I133" s="174"/>
+      <c r="J133" s="174"/>
+      <c r="K133" s="174"/>
+      <c r="L133" s="174"/>
+      <c r="M133" s="174"/>
+      <c r="N133" s="174"/>
+      <c r="O133" s="174"/>
+      <c r="P133" s="174"/>
+      <c r="Q133" s="175"/>
     </row>
     <row r="134" spans="2:17">
       <c r="E134" s="80" t="s">
         <v>386</v>
       </c>
-      <c r="F134" s="171" t="s">
+      <c r="F134" s="173" t="s">
         <v>411</v>
       </c>
-      <c r="G134" s="185"/>
-      <c r="H134" s="185"/>
-      <c r="I134" s="185"/>
-      <c r="J134" s="185"/>
-      <c r="K134" s="185"/>
-      <c r="L134" s="185"/>
-      <c r="M134" s="185"/>
-      <c r="N134" s="185"/>
-      <c r="O134" s="185"/>
-      <c r="P134" s="185"/>
-      <c r="Q134" s="179"/>
+      <c r="G134" s="174"/>
+      <c r="H134" s="174"/>
+      <c r="I134" s="174"/>
+      <c r="J134" s="174"/>
+      <c r="K134" s="174"/>
+      <c r="L134" s="174"/>
+      <c r="M134" s="174"/>
+      <c r="N134" s="174"/>
+      <c r="O134" s="174"/>
+      <c r="P134" s="174"/>
+      <c r="Q134" s="175"/>
     </row>
     <row r="135" spans="2:17">
       <c r="E135" s="80" t="s">
         <v>389</v>
       </c>
-      <c r="F135" s="171" t="s">
+      <c r="F135" s="173" t="s">
         <v>203</v>
       </c>
-      <c r="G135" s="185"/>
-      <c r="H135" s="185"/>
-      <c r="I135" s="185"/>
-      <c r="J135" s="185"/>
-      <c r="K135" s="185"/>
-      <c r="L135" s="185"/>
-      <c r="M135" s="185"/>
-      <c r="N135" s="185"/>
-      <c r="O135" s="185"/>
-      <c r="P135" s="185"/>
-      <c r="Q135" s="179"/>
+      <c r="G135" s="174"/>
+      <c r="H135" s="174"/>
+      <c r="I135" s="174"/>
+      <c r="J135" s="174"/>
+      <c r="K135" s="174"/>
+      <c r="L135" s="174"/>
+      <c r="M135" s="174"/>
+      <c r="N135" s="174"/>
+      <c r="O135" s="174"/>
+      <c r="P135" s="174"/>
+      <c r="Q135" s="175"/>
     </row>
     <row r="136" spans="2:17" ht="17.25" customHeight="1">
       <c r="E136" s="80" t="s">
         <v>413</v>
       </c>
-      <c r="F136" s="180" t="s">
+      <c r="F136" s="170" t="s">
         <v>475</v>
       </c>
-      <c r="G136" s="186"/>
-      <c r="H136" s="186"/>
-      <c r="I136" s="186"/>
-      <c r="J136" s="186"/>
-      <c r="K136" s="186"/>
-      <c r="L136" s="186"/>
-      <c r="M136" s="186"/>
-      <c r="N136" s="186"/>
-      <c r="O136" s="186"/>
-      <c r="P136" s="186"/>
-      <c r="Q136" s="187"/>
+      <c r="G136" s="171"/>
+      <c r="H136" s="171"/>
+      <c r="I136" s="171"/>
+      <c r="J136" s="171"/>
+      <c r="K136" s="171"/>
+      <c r="L136" s="171"/>
+      <c r="M136" s="171"/>
+      <c r="N136" s="171"/>
+      <c r="O136" s="171"/>
+      <c r="P136" s="171"/>
+      <c r="Q136" s="172"/>
     </row>
     <row r="138" spans="2:17">
       <c r="B138" s="79" t="s">
@@ -14123,94 +14123,94 @@
       <c r="G139" s="82" t="s">
         <v>244</v>
       </c>
-      <c r="H139" s="171" t="s">
+      <c r="H139" s="173" t="s">
         <v>478</v>
       </c>
-      <c r="I139" s="185"/>
-      <c r="J139" s="185"/>
-      <c r="K139" s="185"/>
-      <c r="L139" s="185"/>
-      <c r="M139" s="185"/>
-      <c r="N139" s="185"/>
-      <c r="O139" s="185"/>
-      <c r="P139" s="185"/>
-      <c r="Q139" s="179"/>
+      <c r="I139" s="174"/>
+      <c r="J139" s="174"/>
+      <c r="K139" s="174"/>
+      <c r="L139" s="174"/>
+      <c r="M139" s="174"/>
+      <c r="N139" s="174"/>
+      <c r="O139" s="174"/>
+      <c r="P139" s="174"/>
+      <c r="Q139" s="175"/>
     </row>
     <row r="140" spans="2:17">
       <c r="E140" s="80" t="s">
         <v>409</v>
       </c>
-      <c r="F140" s="171" t="s">
+      <c r="F140" s="173" t="s">
         <v>479</v>
       </c>
-      <c r="G140" s="185"/>
-      <c r="H140" s="185"/>
-      <c r="I140" s="185"/>
-      <c r="J140" s="185"/>
-      <c r="K140" s="185"/>
-      <c r="L140" s="185"/>
-      <c r="M140" s="185"/>
-      <c r="N140" s="185"/>
-      <c r="O140" s="185"/>
-      <c r="P140" s="185"/>
-      <c r="Q140" s="179"/>
+      <c r="G140" s="174"/>
+      <c r="H140" s="174"/>
+      <c r="I140" s="174"/>
+      <c r="J140" s="174"/>
+      <c r="K140" s="174"/>
+      <c r="L140" s="174"/>
+      <c r="M140" s="174"/>
+      <c r="N140" s="174"/>
+      <c r="O140" s="174"/>
+      <c r="P140" s="174"/>
+      <c r="Q140" s="175"/>
     </row>
     <row r="141" spans="2:17">
       <c r="E141" s="80" t="s">
         <v>386</v>
       </c>
-      <c r="F141" s="171" t="s">
+      <c r="F141" s="173" t="s">
         <v>411</v>
       </c>
-      <c r="G141" s="185"/>
-      <c r="H141" s="185"/>
-      <c r="I141" s="185"/>
-      <c r="J141" s="185"/>
-      <c r="K141" s="185"/>
-      <c r="L141" s="185"/>
-      <c r="M141" s="185"/>
-      <c r="N141" s="185"/>
-      <c r="O141" s="185"/>
-      <c r="P141" s="185"/>
-      <c r="Q141" s="179"/>
+      <c r="G141" s="174"/>
+      <c r="H141" s="174"/>
+      <c r="I141" s="174"/>
+      <c r="J141" s="174"/>
+      <c r="K141" s="174"/>
+      <c r="L141" s="174"/>
+      <c r="M141" s="174"/>
+      <c r="N141" s="174"/>
+      <c r="O141" s="174"/>
+      <c r="P141" s="174"/>
+      <c r="Q141" s="175"/>
     </row>
     <row r="142" spans="2:17">
       <c r="E142" s="80" t="s">
         <v>389</v>
       </c>
-      <c r="F142" s="171" t="s">
+      <c r="F142" s="173" t="s">
         <v>203</v>
       </c>
-      <c r="G142" s="185"/>
-      <c r="H142" s="185"/>
-      <c r="I142" s="185"/>
-      <c r="J142" s="185"/>
-      <c r="K142" s="185"/>
-      <c r="L142" s="185"/>
-      <c r="M142" s="185"/>
-      <c r="N142" s="185"/>
-      <c r="O142" s="185"/>
-      <c r="P142" s="185"/>
-      <c r="Q142" s="179"/>
+      <c r="G142" s="174"/>
+      <c r="H142" s="174"/>
+      <c r="I142" s="174"/>
+      <c r="J142" s="174"/>
+      <c r="K142" s="174"/>
+      <c r="L142" s="174"/>
+      <c r="M142" s="174"/>
+      <c r="N142" s="174"/>
+      <c r="O142" s="174"/>
+      <c r="P142" s="174"/>
+      <c r="Q142" s="175"/>
     </row>
     <row r="143" spans="2:17" ht="16.5" customHeight="1">
       <c r="E143" s="80" t="s">
         <v>413</v>
       </c>
-      <c r="F143" s="180" t="s">
+      <c r="F143" s="170" t="s">
         <v>480</v>
       </c>
-      <c r="G143" s="186"/>
-      <c r="H143" s="186"/>
-      <c r="I143" s="186"/>
-      <c r="J143" s="186"/>
-      <c r="K143" s="186"/>
-      <c r="L143" s="186"/>
-      <c r="M143" s="186"/>
-      <c r="N143" s="186"/>
-      <c r="O143" s="186"/>
-      <c r="P143" s="186"/>
-      <c r="Q143" s="187"/>
+      <c r="G143" s="171"/>
+      <c r="H143" s="171"/>
+      <c r="I143" s="171"/>
+      <c r="J143" s="171"/>
+      <c r="K143" s="171"/>
+      <c r="L143" s="171"/>
+      <c r="M143" s="171"/>
+      <c r="N143" s="171"/>
+      <c r="O143" s="171"/>
+      <c r="P143" s="171"/>
+      <c r="Q143" s="172"/>
     </row>
     <row r="145" spans="2:17">
       <c r="B145" s="79" t="s">
@@ -14273,94 +14273,94 @@
       <c r="G146" s="82" t="s">
         <v>244</v>
       </c>
-      <c r="H146" s="171" t="s">
+      <c r="H146" s="173" t="s">
         <v>483</v>
       </c>
-      <c r="I146" s="185"/>
-      <c r="J146" s="185"/>
-      <c r="K146" s="185"/>
-      <c r="L146" s="185"/>
-      <c r="M146" s="185"/>
-      <c r="N146" s="185"/>
-      <c r="O146" s="185"/>
-      <c r="P146" s="185"/>
-      <c r="Q146" s="179"/>
+      <c r="I146" s="174"/>
+      <c r="J146" s="174"/>
+      <c r="K146" s="174"/>
+      <c r="L146" s="174"/>
+      <c r="M146" s="174"/>
+      <c r="N146" s="174"/>
+      <c r="O146" s="174"/>
+      <c r="P146" s="174"/>
+      <c r="Q146" s="175"/>
     </row>
     <row r="147" spans="2:17">
       <c r="E147" s="80" t="s">
         <v>409</v>
       </c>
-      <c r="F147" s="171" t="s">
+      <c r="F147" s="173" t="s">
         <v>484</v>
       </c>
-      <c r="G147" s="185"/>
-      <c r="H147" s="185"/>
-      <c r="I147" s="185"/>
-      <c r="J147" s="185"/>
-      <c r="K147" s="185"/>
-      <c r="L147" s="185"/>
-      <c r="M147" s="185"/>
-      <c r="N147" s="185"/>
-      <c r="O147" s="185"/>
-      <c r="P147" s="185"/>
-      <c r="Q147" s="179"/>
+      <c r="G147" s="174"/>
+      <c r="H147" s="174"/>
+      <c r="I147" s="174"/>
+      <c r="J147" s="174"/>
+      <c r="K147" s="174"/>
+      <c r="L147" s="174"/>
+      <c r="M147" s="174"/>
+      <c r="N147" s="174"/>
+      <c r="O147" s="174"/>
+      <c r="P147" s="174"/>
+      <c r="Q147" s="175"/>
     </row>
     <row r="148" spans="2:17">
       <c r="E148" s="80" t="s">
         <v>386</v>
       </c>
-      <c r="F148" s="171" t="s">
+      <c r="F148" s="173" t="s">
         <v>411</v>
       </c>
-      <c r="G148" s="185"/>
-      <c r="H148" s="185"/>
-      <c r="I148" s="185"/>
-      <c r="J148" s="185"/>
-      <c r="K148" s="185"/>
-      <c r="L148" s="185"/>
-      <c r="M148" s="185"/>
-      <c r="N148" s="185"/>
-      <c r="O148" s="185"/>
-      <c r="P148" s="185"/>
-      <c r="Q148" s="179"/>
+      <c r="G148" s="174"/>
+      <c r="H148" s="174"/>
+      <c r="I148" s="174"/>
+      <c r="J148" s="174"/>
+      <c r="K148" s="174"/>
+      <c r="L148" s="174"/>
+      <c r="M148" s="174"/>
+      <c r="N148" s="174"/>
+      <c r="O148" s="174"/>
+      <c r="P148" s="174"/>
+      <c r="Q148" s="175"/>
     </row>
     <row r="149" spans="2:17">
       <c r="E149" s="80" t="s">
         <v>389</v>
       </c>
-      <c r="F149" s="171" t="s">
+      <c r="F149" s="173" t="s">
         <v>203</v>
       </c>
-      <c r="G149" s="185"/>
-      <c r="H149" s="185"/>
-      <c r="I149" s="185"/>
-      <c r="J149" s="185"/>
-      <c r="K149" s="185"/>
-      <c r="L149" s="185"/>
-      <c r="M149" s="185"/>
-      <c r="N149" s="185"/>
-      <c r="O149" s="185"/>
-      <c r="P149" s="185"/>
-      <c r="Q149" s="179"/>
+      <c r="G149" s="174"/>
+      <c r="H149" s="174"/>
+      <c r="I149" s="174"/>
+      <c r="J149" s="174"/>
+      <c r="K149" s="174"/>
+      <c r="L149" s="174"/>
+      <c r="M149" s="174"/>
+      <c r="N149" s="174"/>
+      <c r="O149" s="174"/>
+      <c r="P149" s="174"/>
+      <c r="Q149" s="175"/>
     </row>
     <row r="150" spans="2:17" ht="16.5" customHeight="1">
       <c r="E150" s="80" t="s">
         <v>413</v>
       </c>
-      <c r="F150" s="180" t="s">
+      <c r="F150" s="170" t="s">
         <v>485</v>
       </c>
-      <c r="G150" s="186"/>
-      <c r="H150" s="186"/>
-      <c r="I150" s="186"/>
-      <c r="J150" s="186"/>
-      <c r="K150" s="186"/>
-      <c r="L150" s="186"/>
-      <c r="M150" s="186"/>
-      <c r="N150" s="186"/>
-      <c r="O150" s="186"/>
-      <c r="P150" s="186"/>
-      <c r="Q150" s="187"/>
+      <c r="G150" s="171"/>
+      <c r="H150" s="171"/>
+      <c r="I150" s="171"/>
+      <c r="J150" s="171"/>
+      <c r="K150" s="171"/>
+      <c r="L150" s="171"/>
+      <c r="M150" s="171"/>
+      <c r="N150" s="171"/>
+      <c r="O150" s="171"/>
+      <c r="P150" s="171"/>
+      <c r="Q150" s="172"/>
     </row>
     <row r="152" spans="2:17">
       <c r="B152" s="79" t="s">
@@ -14423,94 +14423,94 @@
       <c r="G153" s="82" t="s">
         <v>244</v>
       </c>
-      <c r="H153" s="171" t="s">
+      <c r="H153" s="173" t="s">
         <v>488</v>
       </c>
-      <c r="I153" s="185"/>
-      <c r="J153" s="185"/>
-      <c r="K153" s="185"/>
-      <c r="L153" s="185"/>
-      <c r="M153" s="185"/>
-      <c r="N153" s="185"/>
-      <c r="O153" s="185"/>
-      <c r="P153" s="185"/>
-      <c r="Q153" s="179"/>
+      <c r="I153" s="174"/>
+      <c r="J153" s="174"/>
+      <c r="K153" s="174"/>
+      <c r="L153" s="174"/>
+      <c r="M153" s="174"/>
+      <c r="N153" s="174"/>
+      <c r="O153" s="174"/>
+      <c r="P153" s="174"/>
+      <c r="Q153" s="175"/>
     </row>
     <row r="154" spans="2:17">
       <c r="E154" s="80" t="s">
         <v>409</v>
       </c>
-      <c r="F154" s="171" t="s">
+      <c r="F154" s="173" t="s">
         <v>489</v>
       </c>
-      <c r="G154" s="185"/>
-      <c r="H154" s="185"/>
-      <c r="I154" s="185"/>
-      <c r="J154" s="185"/>
-      <c r="K154" s="185"/>
-      <c r="L154" s="185"/>
-      <c r="M154" s="185"/>
-      <c r="N154" s="185"/>
-      <c r="O154" s="185"/>
-      <c r="P154" s="185"/>
-      <c r="Q154" s="179"/>
+      <c r="G154" s="174"/>
+      <c r="H154" s="174"/>
+      <c r="I154" s="174"/>
+      <c r="J154" s="174"/>
+      <c r="K154" s="174"/>
+      <c r="L154" s="174"/>
+      <c r="M154" s="174"/>
+      <c r="N154" s="174"/>
+      <c r="O154" s="174"/>
+      <c r="P154" s="174"/>
+      <c r="Q154" s="175"/>
     </row>
     <row r="155" spans="2:17">
       <c r="E155" s="80" t="s">
         <v>386</v>
       </c>
-      <c r="F155" s="171" t="s">
+      <c r="F155" s="173" t="s">
         <v>411</v>
       </c>
-      <c r="G155" s="185"/>
-      <c r="H155" s="185"/>
-      <c r="I155" s="185"/>
-      <c r="J155" s="185"/>
-      <c r="K155" s="185"/>
-      <c r="L155" s="185"/>
-      <c r="M155" s="185"/>
-      <c r="N155" s="185"/>
-      <c r="O155" s="185"/>
-      <c r="P155" s="185"/>
-      <c r="Q155" s="179"/>
+      <c r="G155" s="174"/>
+      <c r="H155" s="174"/>
+      <c r="I155" s="174"/>
+      <c r="J155" s="174"/>
+      <c r="K155" s="174"/>
+      <c r="L155" s="174"/>
+      <c r="M155" s="174"/>
+      <c r="N155" s="174"/>
+      <c r="O155" s="174"/>
+      <c r="P155" s="174"/>
+      <c r="Q155" s="175"/>
     </row>
     <row r="156" spans="2:17">
       <c r="E156" s="80" t="s">
         <v>389</v>
       </c>
-      <c r="F156" s="171" t="s">
+      <c r="F156" s="173" t="s">
         <v>203</v>
       </c>
-      <c r="G156" s="185"/>
-      <c r="H156" s="185"/>
-      <c r="I156" s="185"/>
-      <c r="J156" s="185"/>
-      <c r="K156" s="185"/>
-      <c r="L156" s="185"/>
-      <c r="M156" s="185"/>
-      <c r="N156" s="185"/>
-      <c r="O156" s="185"/>
-      <c r="P156" s="185"/>
-      <c r="Q156" s="179"/>
+      <c r="G156" s="174"/>
+      <c r="H156" s="174"/>
+      <c r="I156" s="174"/>
+      <c r="J156" s="174"/>
+      <c r="K156" s="174"/>
+      <c r="L156" s="174"/>
+      <c r="M156" s="174"/>
+      <c r="N156" s="174"/>
+      <c r="O156" s="174"/>
+      <c r="P156" s="174"/>
+      <c r="Q156" s="175"/>
     </row>
     <row r="157" spans="2:17" ht="16.5" customHeight="1">
       <c r="E157" s="80" t="s">
         <v>413</v>
       </c>
-      <c r="F157" s="180" t="s">
+      <c r="F157" s="170" t="s">
         <v>490</v>
       </c>
-      <c r="G157" s="186"/>
-      <c r="H157" s="186"/>
-      <c r="I157" s="186"/>
-      <c r="J157" s="186"/>
-      <c r="K157" s="186"/>
-      <c r="L157" s="186"/>
-      <c r="M157" s="186"/>
-      <c r="N157" s="186"/>
-      <c r="O157" s="186"/>
-      <c r="P157" s="186"/>
-      <c r="Q157" s="187"/>
+      <c r="G157" s="171"/>
+      <c r="H157" s="171"/>
+      <c r="I157" s="171"/>
+      <c r="J157" s="171"/>
+      <c r="K157" s="171"/>
+      <c r="L157" s="171"/>
+      <c r="M157" s="171"/>
+      <c r="N157" s="171"/>
+      <c r="O157" s="171"/>
+      <c r="P157" s="171"/>
+      <c r="Q157" s="172"/>
     </row>
     <row r="159" spans="2:17">
       <c r="B159" s="79" t="s">
@@ -14573,94 +14573,94 @@
       <c r="G160" s="82" t="s">
         <v>244</v>
       </c>
-      <c r="H160" s="171" t="s">
+      <c r="H160" s="173" t="s">
         <v>493</v>
       </c>
-      <c r="I160" s="185"/>
-      <c r="J160" s="185"/>
-      <c r="K160" s="185"/>
-      <c r="L160" s="185"/>
-      <c r="M160" s="185"/>
-      <c r="N160" s="185"/>
-      <c r="O160" s="185"/>
-      <c r="P160" s="185"/>
-      <c r="Q160" s="179"/>
+      <c r="I160" s="174"/>
+      <c r="J160" s="174"/>
+      <c r="K160" s="174"/>
+      <c r="L160" s="174"/>
+      <c r="M160" s="174"/>
+      <c r="N160" s="174"/>
+      <c r="O160" s="174"/>
+      <c r="P160" s="174"/>
+      <c r="Q160" s="175"/>
     </row>
     <row r="161" spans="2:17">
       <c r="E161" s="80" t="s">
         <v>409</v>
       </c>
-      <c r="F161" s="171" t="s">
+      <c r="F161" s="173" t="s">
         <v>494</v>
       </c>
-      <c r="G161" s="185"/>
-      <c r="H161" s="185"/>
-      <c r="I161" s="185"/>
-      <c r="J161" s="185"/>
-      <c r="K161" s="185"/>
-      <c r="L161" s="185"/>
-      <c r="M161" s="185"/>
-      <c r="N161" s="185"/>
-      <c r="O161" s="185"/>
-      <c r="P161" s="185"/>
-      <c r="Q161" s="179"/>
+      <c r="G161" s="174"/>
+      <c r="H161" s="174"/>
+      <c r="I161" s="174"/>
+      <c r="J161" s="174"/>
+      <c r="K161" s="174"/>
+      <c r="L161" s="174"/>
+      <c r="M161" s="174"/>
+      <c r="N161" s="174"/>
+      <c r="O161" s="174"/>
+      <c r="P161" s="174"/>
+      <c r="Q161" s="175"/>
     </row>
     <row r="162" spans="2:17">
       <c r="E162" s="80" t="s">
         <v>386</v>
       </c>
-      <c r="F162" s="171" t="s">
+      <c r="F162" s="173" t="s">
         <v>411</v>
       </c>
-      <c r="G162" s="185"/>
-      <c r="H162" s="185"/>
-      <c r="I162" s="185"/>
-      <c r="J162" s="185"/>
-      <c r="K162" s="185"/>
-      <c r="L162" s="185"/>
-      <c r="M162" s="185"/>
-      <c r="N162" s="185"/>
-      <c r="O162" s="185"/>
-      <c r="P162" s="185"/>
-      <c r="Q162" s="179"/>
+      <c r="G162" s="174"/>
+      <c r="H162" s="174"/>
+      <c r="I162" s="174"/>
+      <c r="J162" s="174"/>
+      <c r="K162" s="174"/>
+      <c r="L162" s="174"/>
+      <c r="M162" s="174"/>
+      <c r="N162" s="174"/>
+      <c r="O162" s="174"/>
+      <c r="P162" s="174"/>
+      <c r="Q162" s="175"/>
     </row>
     <row r="163" spans="2:17">
       <c r="E163" s="80" t="s">
         <v>389</v>
       </c>
-      <c r="F163" s="171" t="s">
+      <c r="F163" s="173" t="s">
         <v>203</v>
       </c>
-      <c r="G163" s="185"/>
-      <c r="H163" s="185"/>
-      <c r="I163" s="185"/>
-      <c r="J163" s="185"/>
-      <c r="K163" s="185"/>
-      <c r="L163" s="185"/>
-      <c r="M163" s="185"/>
-      <c r="N163" s="185"/>
-      <c r="O163" s="185"/>
-      <c r="P163" s="185"/>
-      <c r="Q163" s="179"/>
+      <c r="G163" s="174"/>
+      <c r="H163" s="174"/>
+      <c r="I163" s="174"/>
+      <c r="J163" s="174"/>
+      <c r="K163" s="174"/>
+      <c r="L163" s="174"/>
+      <c r="M163" s="174"/>
+      <c r="N163" s="174"/>
+      <c r="O163" s="174"/>
+      <c r="P163" s="174"/>
+      <c r="Q163" s="175"/>
     </row>
     <row r="164" spans="2:17" ht="16.5" customHeight="1">
       <c r="E164" s="80" t="s">
         <v>413</v>
       </c>
-      <c r="F164" s="180" t="s">
+      <c r="F164" s="170" t="s">
         <v>495</v>
       </c>
-      <c r="G164" s="186"/>
-      <c r="H164" s="186"/>
-      <c r="I164" s="186"/>
-      <c r="J164" s="186"/>
-      <c r="K164" s="186"/>
-      <c r="L164" s="186"/>
-      <c r="M164" s="186"/>
-      <c r="N164" s="186"/>
-      <c r="O164" s="186"/>
-      <c r="P164" s="186"/>
-      <c r="Q164" s="187"/>
+      <c r="G164" s="171"/>
+      <c r="H164" s="171"/>
+      <c r="I164" s="171"/>
+      <c r="J164" s="171"/>
+      <c r="K164" s="171"/>
+      <c r="L164" s="171"/>
+      <c r="M164" s="171"/>
+      <c r="N164" s="171"/>
+      <c r="O164" s="171"/>
+      <c r="P164" s="171"/>
+      <c r="Q164" s="172"/>
     </row>
     <row r="166" spans="2:17">
       <c r="B166" s="79" t="s">
@@ -14723,94 +14723,94 @@
       <c r="G167" s="82" t="s">
         <v>244</v>
       </c>
-      <c r="H167" s="171" t="s">
+      <c r="H167" s="173" t="s">
         <v>498</v>
       </c>
-      <c r="I167" s="185"/>
-      <c r="J167" s="185"/>
-      <c r="K167" s="185"/>
-      <c r="L167" s="185"/>
-      <c r="M167" s="185"/>
-      <c r="N167" s="185"/>
-      <c r="O167" s="185"/>
-      <c r="P167" s="185"/>
-      <c r="Q167" s="179"/>
+      <c r="I167" s="174"/>
+      <c r="J167" s="174"/>
+      <c r="K167" s="174"/>
+      <c r="L167" s="174"/>
+      <c r="M167" s="174"/>
+      <c r="N167" s="174"/>
+      <c r="O167" s="174"/>
+      <c r="P167" s="174"/>
+      <c r="Q167" s="175"/>
     </row>
     <row r="168" spans="2:17">
       <c r="E168" s="80" t="s">
         <v>409</v>
       </c>
-      <c r="F168" s="171" t="s">
+      <c r="F168" s="173" t="s">
         <v>499</v>
       </c>
-      <c r="G168" s="185"/>
-      <c r="H168" s="185"/>
-      <c r="I168" s="185"/>
-      <c r="J168" s="185"/>
-      <c r="K168" s="185"/>
-      <c r="L168" s="185"/>
-      <c r="M168" s="185"/>
-      <c r="N168" s="185"/>
-      <c r="O168" s="185"/>
-      <c r="P168" s="185"/>
-      <c r="Q168" s="179"/>
+      <c r="G168" s="174"/>
+      <c r="H168" s="174"/>
+      <c r="I168" s="174"/>
+      <c r="J168" s="174"/>
+      <c r="K168" s="174"/>
+      <c r="L168" s="174"/>
+      <c r="M168" s="174"/>
+      <c r="N168" s="174"/>
+      <c r="O168" s="174"/>
+      <c r="P168" s="174"/>
+      <c r="Q168" s="175"/>
     </row>
     <row r="169" spans="2:17">
       <c r="E169" s="80" t="s">
         <v>386</v>
       </c>
-      <c r="F169" s="171" t="s">
+      <c r="F169" s="173" t="s">
         <v>411</v>
       </c>
-      <c r="G169" s="185"/>
-      <c r="H169" s="185"/>
-      <c r="I169" s="185"/>
-      <c r="J169" s="185"/>
-      <c r="K169" s="185"/>
-      <c r="L169" s="185"/>
-      <c r="M169" s="185"/>
-      <c r="N169" s="185"/>
-      <c r="O169" s="185"/>
-      <c r="P169" s="185"/>
-      <c r="Q169" s="179"/>
+      <c r="G169" s="174"/>
+      <c r="H169" s="174"/>
+      <c r="I169" s="174"/>
+      <c r="J169" s="174"/>
+      <c r="K169" s="174"/>
+      <c r="L169" s="174"/>
+      <c r="M169" s="174"/>
+      <c r="N169" s="174"/>
+      <c r="O169" s="174"/>
+      <c r="P169" s="174"/>
+      <c r="Q169" s="175"/>
     </row>
     <row r="170" spans="2:17">
       <c r="E170" s="80" t="s">
         <v>389</v>
       </c>
-      <c r="F170" s="171" t="s">
+      <c r="F170" s="173" t="s">
         <v>203</v>
       </c>
-      <c r="G170" s="185"/>
-      <c r="H170" s="185"/>
-      <c r="I170" s="185"/>
-      <c r="J170" s="185"/>
-      <c r="K170" s="185"/>
-      <c r="L170" s="185"/>
-      <c r="M170" s="185"/>
-      <c r="N170" s="185"/>
-      <c r="O170" s="185"/>
-      <c r="P170" s="185"/>
-      <c r="Q170" s="179"/>
+      <c r="G170" s="174"/>
+      <c r="H170" s="174"/>
+      <c r="I170" s="174"/>
+      <c r="J170" s="174"/>
+      <c r="K170" s="174"/>
+      <c r="L170" s="174"/>
+      <c r="M170" s="174"/>
+      <c r="N170" s="174"/>
+      <c r="O170" s="174"/>
+      <c r="P170" s="174"/>
+      <c r="Q170" s="175"/>
     </row>
     <row r="171" spans="2:17" ht="16.5" customHeight="1">
       <c r="E171" s="80" t="s">
         <v>413</v>
       </c>
-      <c r="F171" s="180" t="s">
+      <c r="F171" s="170" t="s">
         <v>500</v>
       </c>
-      <c r="G171" s="186"/>
-      <c r="H171" s="186"/>
-      <c r="I171" s="186"/>
-      <c r="J171" s="186"/>
-      <c r="K171" s="186"/>
-      <c r="L171" s="186"/>
-      <c r="M171" s="186"/>
-      <c r="N171" s="186"/>
-      <c r="O171" s="186"/>
-      <c r="P171" s="186"/>
-      <c r="Q171" s="187"/>
+      <c r="G171" s="171"/>
+      <c r="H171" s="171"/>
+      <c r="I171" s="171"/>
+      <c r="J171" s="171"/>
+      <c r="K171" s="171"/>
+      <c r="L171" s="171"/>
+      <c r="M171" s="171"/>
+      <c r="N171" s="171"/>
+      <c r="O171" s="171"/>
+      <c r="P171" s="171"/>
+      <c r="Q171" s="172"/>
     </row>
     <row r="173" spans="2:17">
       <c r="B173" s="79" t="s">
@@ -14873,94 +14873,94 @@
       <c r="G174" s="82" t="s">
         <v>244</v>
       </c>
-      <c r="H174" s="171" t="s">
+      <c r="H174" s="173" t="s">
         <v>503</v>
       </c>
-      <c r="I174" s="185"/>
-      <c r="J174" s="185"/>
-      <c r="K174" s="185"/>
-      <c r="L174" s="185"/>
-      <c r="M174" s="185"/>
-      <c r="N174" s="185"/>
-      <c r="O174" s="185"/>
-      <c r="P174" s="185"/>
-      <c r="Q174" s="179"/>
+      <c r="I174" s="174"/>
+      <c r="J174" s="174"/>
+      <c r="K174" s="174"/>
+      <c r="L174" s="174"/>
+      <c r="M174" s="174"/>
+      <c r="N174" s="174"/>
+      <c r="O174" s="174"/>
+      <c r="P174" s="174"/>
+      <c r="Q174" s="175"/>
     </row>
     <row r="175" spans="2:17">
       <c r="E175" s="80" t="s">
         <v>409</v>
       </c>
-      <c r="F175" s="171" t="s">
+      <c r="F175" s="173" t="s">
         <v>504</v>
       </c>
-      <c r="G175" s="185"/>
-      <c r="H175" s="185"/>
-      <c r="I175" s="185"/>
-      <c r="J175" s="185"/>
-      <c r="K175" s="185"/>
-      <c r="L175" s="185"/>
-      <c r="M175" s="185"/>
-      <c r="N175" s="185"/>
-      <c r="O175" s="185"/>
-      <c r="P175" s="185"/>
-      <c r="Q175" s="179"/>
+      <c r="G175" s="174"/>
+      <c r="H175" s="174"/>
+      <c r="I175" s="174"/>
+      <c r="J175" s="174"/>
+      <c r="K175" s="174"/>
+      <c r="L175" s="174"/>
+      <c r="M175" s="174"/>
+      <c r="N175" s="174"/>
+      <c r="O175" s="174"/>
+      <c r="P175" s="174"/>
+      <c r="Q175" s="175"/>
     </row>
     <row r="176" spans="2:17">
       <c r="E176" s="80" t="s">
         <v>386</v>
       </c>
-      <c r="F176" s="171" t="s">
+      <c r="F176" s="173" t="s">
         <v>411</v>
       </c>
-      <c r="G176" s="185"/>
-      <c r="H176" s="185"/>
-      <c r="I176" s="185"/>
-      <c r="J176" s="185"/>
-      <c r="K176" s="185"/>
-      <c r="L176" s="185"/>
-      <c r="M176" s="185"/>
-      <c r="N176" s="185"/>
-      <c r="O176" s="185"/>
-      <c r="P176" s="185"/>
-      <c r="Q176" s="179"/>
+      <c r="G176" s="174"/>
+      <c r="H176" s="174"/>
+      <c r="I176" s="174"/>
+      <c r="J176" s="174"/>
+      <c r="K176" s="174"/>
+      <c r="L176" s="174"/>
+      <c r="M176" s="174"/>
+      <c r="N176" s="174"/>
+      <c r="O176" s="174"/>
+      <c r="P176" s="174"/>
+      <c r="Q176" s="175"/>
     </row>
     <row r="177" spans="2:17">
       <c r="E177" s="80" t="s">
         <v>389</v>
       </c>
-      <c r="F177" s="171" t="s">
+      <c r="F177" s="173" t="s">
         <v>203</v>
       </c>
-      <c r="G177" s="185"/>
-      <c r="H177" s="185"/>
-      <c r="I177" s="185"/>
-      <c r="J177" s="185"/>
-      <c r="K177" s="185"/>
-      <c r="L177" s="185"/>
-      <c r="M177" s="185"/>
-      <c r="N177" s="185"/>
-      <c r="O177" s="185"/>
-      <c r="P177" s="185"/>
-      <c r="Q177" s="179"/>
+      <c r="G177" s="174"/>
+      <c r="H177" s="174"/>
+      <c r="I177" s="174"/>
+      <c r="J177" s="174"/>
+      <c r="K177" s="174"/>
+      <c r="L177" s="174"/>
+      <c r="M177" s="174"/>
+      <c r="N177" s="174"/>
+      <c r="O177" s="174"/>
+      <c r="P177" s="174"/>
+      <c r="Q177" s="175"/>
     </row>
     <row r="178" spans="2:17" ht="16.5" customHeight="1">
       <c r="E178" s="80" t="s">
         <v>413</v>
       </c>
-      <c r="F178" s="180" t="s">
+      <c r="F178" s="170" t="s">
         <v>505</v>
       </c>
-      <c r="G178" s="186"/>
-      <c r="H178" s="186"/>
-      <c r="I178" s="186"/>
-      <c r="J178" s="186"/>
-      <c r="K178" s="186"/>
-      <c r="L178" s="186"/>
-      <c r="M178" s="186"/>
-      <c r="N178" s="186"/>
-      <c r="O178" s="186"/>
-      <c r="P178" s="186"/>
-      <c r="Q178" s="187"/>
+      <c r="G178" s="171"/>
+      <c r="H178" s="171"/>
+      <c r="I178" s="171"/>
+      <c r="J178" s="171"/>
+      <c r="K178" s="171"/>
+      <c r="L178" s="171"/>
+      <c r="M178" s="171"/>
+      <c r="N178" s="171"/>
+      <c r="O178" s="171"/>
+      <c r="P178" s="171"/>
+      <c r="Q178" s="172"/>
     </row>
     <row r="180" spans="2:17">
       <c r="B180" s="79" t="s">
@@ -15023,94 +15023,94 @@
       <c r="G181" s="82" t="s">
         <v>244</v>
       </c>
-      <c r="H181" s="171" t="s">
+      <c r="H181" s="173" t="s">
         <v>508</v>
       </c>
-      <c r="I181" s="185"/>
-      <c r="J181" s="185"/>
-      <c r="K181" s="185"/>
-      <c r="L181" s="185"/>
-      <c r="M181" s="185"/>
-      <c r="N181" s="185"/>
-      <c r="O181" s="185"/>
-      <c r="P181" s="185"/>
-      <c r="Q181" s="179"/>
+      <c r="I181" s="174"/>
+      <c r="J181" s="174"/>
+      <c r="K181" s="174"/>
+      <c r="L181" s="174"/>
+      <c r="M181" s="174"/>
+      <c r="N181" s="174"/>
+      <c r="O181" s="174"/>
+      <c r="P181" s="174"/>
+      <c r="Q181" s="175"/>
     </row>
     <row r="182" spans="2:17">
       <c r="E182" s="80" t="s">
         <v>409</v>
       </c>
-      <c r="F182" s="171" t="s">
+      <c r="F182" s="173" t="s">
         <v>509</v>
       </c>
-      <c r="G182" s="185"/>
-      <c r="H182" s="185"/>
-      <c r="I182" s="185"/>
-      <c r="J182" s="185"/>
-      <c r="K182" s="185"/>
-      <c r="L182" s="185"/>
-      <c r="M182" s="185"/>
-      <c r="N182" s="185"/>
-      <c r="O182" s="185"/>
-      <c r="P182" s="185"/>
-      <c r="Q182" s="179"/>
+      <c r="G182" s="174"/>
+      <c r="H182" s="174"/>
+      <c r="I182" s="174"/>
+      <c r="J182" s="174"/>
+      <c r="K182" s="174"/>
+      <c r="L182" s="174"/>
+      <c r="M182" s="174"/>
+      <c r="N182" s="174"/>
+      <c r="O182" s="174"/>
+      <c r="P182" s="174"/>
+      <c r="Q182" s="175"/>
     </row>
     <row r="183" spans="2:17">
       <c r="E183" s="80" t="s">
         <v>386</v>
       </c>
-      <c r="F183" s="171" t="s">
+      <c r="F183" s="173" t="s">
         <v>411</v>
       </c>
-      <c r="G183" s="185"/>
-      <c r="H183" s="185"/>
-      <c r="I183" s="185"/>
-      <c r="J183" s="185"/>
-      <c r="K183" s="185"/>
-      <c r="L183" s="185"/>
-      <c r="M183" s="185"/>
-      <c r="N183" s="185"/>
-      <c r="O183" s="185"/>
-      <c r="P183" s="185"/>
-      <c r="Q183" s="179"/>
+      <c r="G183" s="174"/>
+      <c r="H183" s="174"/>
+      <c r="I183" s="174"/>
+      <c r="J183" s="174"/>
+      <c r="K183" s="174"/>
+      <c r="L183" s="174"/>
+      <c r="M183" s="174"/>
+      <c r="N183" s="174"/>
+      <c r="O183" s="174"/>
+      <c r="P183" s="174"/>
+      <c r="Q183" s="175"/>
     </row>
     <row r="184" spans="2:17">
       <c r="E184" s="80" t="s">
         <v>389</v>
       </c>
-      <c r="F184" s="171" t="s">
+      <c r="F184" s="173" t="s">
         <v>203</v>
       </c>
-      <c r="G184" s="185"/>
-      <c r="H184" s="185"/>
-      <c r="I184" s="185"/>
-      <c r="J184" s="185"/>
-      <c r="K184" s="185"/>
-      <c r="L184" s="185"/>
-      <c r="M184" s="185"/>
-      <c r="N184" s="185"/>
-      <c r="O184" s="185"/>
-      <c r="P184" s="185"/>
-      <c r="Q184" s="179"/>
+      <c r="G184" s="174"/>
+      <c r="H184" s="174"/>
+      <c r="I184" s="174"/>
+      <c r="J184" s="174"/>
+      <c r="K184" s="174"/>
+      <c r="L184" s="174"/>
+      <c r="M184" s="174"/>
+      <c r="N184" s="174"/>
+      <c r="O184" s="174"/>
+      <c r="P184" s="174"/>
+      <c r="Q184" s="175"/>
     </row>
     <row r="185" spans="2:17" ht="16.5" customHeight="1">
       <c r="E185" s="80" t="s">
         <v>413</v>
       </c>
-      <c r="F185" s="180" t="s">
+      <c r="F185" s="170" t="s">
         <v>510</v>
       </c>
-      <c r="G185" s="186"/>
-      <c r="H185" s="186"/>
-      <c r="I185" s="186"/>
-      <c r="J185" s="186"/>
-      <c r="K185" s="186"/>
-      <c r="L185" s="186"/>
-      <c r="M185" s="186"/>
-      <c r="N185" s="186"/>
-      <c r="O185" s="186"/>
-      <c r="P185" s="186"/>
-      <c r="Q185" s="187"/>
+      <c r="G185" s="171"/>
+      <c r="H185" s="171"/>
+      <c r="I185" s="171"/>
+      <c r="J185" s="171"/>
+      <c r="K185" s="171"/>
+      <c r="L185" s="171"/>
+      <c r="M185" s="171"/>
+      <c r="N185" s="171"/>
+      <c r="O185" s="171"/>
+      <c r="P185" s="171"/>
+      <c r="Q185" s="172"/>
     </row>
     <row r="187" spans="2:17">
       <c r="B187" s="79" t="s">
@@ -15173,94 +15173,94 @@
       <c r="G188" s="82" t="s">
         <v>244</v>
       </c>
-      <c r="H188" s="171" t="s">
+      <c r="H188" s="173" t="s">
         <v>513</v>
       </c>
-      <c r="I188" s="185"/>
-      <c r="J188" s="185"/>
-      <c r="K188" s="185"/>
-      <c r="L188" s="185"/>
-      <c r="M188" s="185"/>
-      <c r="N188" s="185"/>
-      <c r="O188" s="185"/>
-      <c r="P188" s="185"/>
-      <c r="Q188" s="179"/>
+      <c r="I188" s="174"/>
+      <c r="J188" s="174"/>
+      <c r="K188" s="174"/>
+      <c r="L188" s="174"/>
+      <c r="M188" s="174"/>
+      <c r="N188" s="174"/>
+      <c r="O188" s="174"/>
+      <c r="P188" s="174"/>
+      <c r="Q188" s="175"/>
     </row>
     <row r="189" spans="2:17">
       <c r="E189" s="80" t="s">
         <v>409</v>
       </c>
-      <c r="F189" s="171" t="s">
+      <c r="F189" s="173" t="s">
         <v>514</v>
       </c>
-      <c r="G189" s="185"/>
-      <c r="H189" s="185"/>
-      <c r="I189" s="185"/>
-      <c r="J189" s="185"/>
-      <c r="K189" s="185"/>
-      <c r="L189" s="185"/>
-      <c r="M189" s="185"/>
-      <c r="N189" s="185"/>
-      <c r="O189" s="185"/>
-      <c r="P189" s="185"/>
-      <c r="Q189" s="179"/>
+      <c r="G189" s="174"/>
+      <c r="H189" s="174"/>
+      <c r="I189" s="174"/>
+      <c r="J189" s="174"/>
+      <c r="K189" s="174"/>
+      <c r="L189" s="174"/>
+      <c r="M189" s="174"/>
+      <c r="N189" s="174"/>
+      <c r="O189" s="174"/>
+      <c r="P189" s="174"/>
+      <c r="Q189" s="175"/>
     </row>
     <row r="190" spans="2:17">
       <c r="E190" s="80" t="s">
         <v>386</v>
       </c>
-      <c r="F190" s="171" t="s">
+      <c r="F190" s="173" t="s">
         <v>411</v>
       </c>
-      <c r="G190" s="185"/>
-      <c r="H190" s="185"/>
-      <c r="I190" s="185"/>
-      <c r="J190" s="185"/>
-      <c r="K190" s="185"/>
-      <c r="L190" s="185"/>
-      <c r="M190" s="185"/>
-      <c r="N190" s="185"/>
-      <c r="O190" s="185"/>
-      <c r="P190" s="185"/>
-      <c r="Q190" s="179"/>
+      <c r="G190" s="174"/>
+      <c r="H190" s="174"/>
+      <c r="I190" s="174"/>
+      <c r="J190" s="174"/>
+      <c r="K190" s="174"/>
+      <c r="L190" s="174"/>
+      <c r="M190" s="174"/>
+      <c r="N190" s="174"/>
+      <c r="O190" s="174"/>
+      <c r="P190" s="174"/>
+      <c r="Q190" s="175"/>
     </row>
     <row r="191" spans="2:17">
       <c r="E191" s="80" t="s">
         <v>389</v>
       </c>
-      <c r="F191" s="171" t="s">
+      <c r="F191" s="173" t="s">
         <v>203</v>
       </c>
-      <c r="G191" s="185"/>
-      <c r="H191" s="185"/>
-      <c r="I191" s="185"/>
-      <c r="J191" s="185"/>
-      <c r="K191" s="185"/>
-      <c r="L191" s="185"/>
-      <c r="M191" s="185"/>
-      <c r="N191" s="185"/>
-      <c r="O191" s="185"/>
-      <c r="P191" s="185"/>
-      <c r="Q191" s="179"/>
+      <c r="G191" s="174"/>
+      <c r="H191" s="174"/>
+      <c r="I191" s="174"/>
+      <c r="J191" s="174"/>
+      <c r="K191" s="174"/>
+      <c r="L191" s="174"/>
+      <c r="M191" s="174"/>
+      <c r="N191" s="174"/>
+      <c r="O191" s="174"/>
+      <c r="P191" s="174"/>
+      <c r="Q191" s="175"/>
     </row>
     <row r="192" spans="2:17" ht="16.5" customHeight="1">
       <c r="E192" s="80" t="s">
         <v>413</v>
       </c>
-      <c r="F192" s="180" t="s">
+      <c r="F192" s="170" t="s">
         <v>515</v>
       </c>
-      <c r="G192" s="186"/>
-      <c r="H192" s="186"/>
-      <c r="I192" s="186"/>
-      <c r="J192" s="186"/>
-      <c r="K192" s="186"/>
-      <c r="L192" s="186"/>
-      <c r="M192" s="186"/>
-      <c r="N192" s="186"/>
-      <c r="O192" s="186"/>
-      <c r="P192" s="186"/>
-      <c r="Q192" s="187"/>
+      <c r="G192" s="171"/>
+      <c r="H192" s="171"/>
+      <c r="I192" s="171"/>
+      <c r="J192" s="171"/>
+      <c r="K192" s="171"/>
+      <c r="L192" s="171"/>
+      <c r="M192" s="171"/>
+      <c r="N192" s="171"/>
+      <c r="O192" s="171"/>
+      <c r="P192" s="171"/>
+      <c r="Q192" s="172"/>
     </row>
     <row r="194" spans="2:17">
       <c r="B194" s="79" t="s">
@@ -15317,99 +15317,246 @@
       <c r="E195" s="80" t="s">
         <v>408</v>
       </c>
-      <c r="F195" s="171" t="s">
+      <c r="F195" s="173" t="s">
         <v>518</v>
       </c>
-      <c r="G195" s="185"/>
-      <c r="H195" s="185"/>
-      <c r="I195" s="185"/>
-      <c r="J195" s="185"/>
-      <c r="K195" s="185"/>
-      <c r="L195" s="185"/>
-      <c r="M195" s="185"/>
-      <c r="N195" s="185"/>
-      <c r="O195" s="185"/>
-      <c r="P195" s="185"/>
-      <c r="Q195" s="179"/>
+      <c r="G195" s="174"/>
+      <c r="H195" s="174"/>
+      <c r="I195" s="174"/>
+      <c r="J195" s="174"/>
+      <c r="K195" s="174"/>
+      <c r="L195" s="174"/>
+      <c r="M195" s="174"/>
+      <c r="N195" s="174"/>
+      <c r="O195" s="174"/>
+      <c r="P195" s="174"/>
+      <c r="Q195" s="175"/>
     </row>
     <row r="196" spans="2:17">
       <c r="E196" s="80" t="s">
         <v>409</v>
       </c>
-      <c r="F196" s="171" t="s">
+      <c r="F196" s="173" t="s">
         <v>519</v>
       </c>
-      <c r="G196" s="185"/>
-      <c r="H196" s="185"/>
-      <c r="I196" s="185"/>
-      <c r="J196" s="185"/>
-      <c r="K196" s="185"/>
-      <c r="L196" s="185"/>
-      <c r="M196" s="185"/>
-      <c r="N196" s="185"/>
-      <c r="O196" s="185"/>
-      <c r="P196" s="185"/>
-      <c r="Q196" s="179"/>
+      <c r="G196" s="174"/>
+      <c r="H196" s="174"/>
+      <c r="I196" s="174"/>
+      <c r="J196" s="174"/>
+      <c r="K196" s="174"/>
+      <c r="L196" s="174"/>
+      <c r="M196" s="174"/>
+      <c r="N196" s="174"/>
+      <c r="O196" s="174"/>
+      <c r="P196" s="174"/>
+      <c r="Q196" s="175"/>
     </row>
     <row r="197" spans="2:17">
       <c r="E197" s="80" t="s">
         <v>386</v>
       </c>
-      <c r="F197" s="171" t="s">
+      <c r="F197" s="173" t="s">
         <v>411</v>
       </c>
-      <c r="G197" s="185"/>
-      <c r="H197" s="185"/>
-      <c r="I197" s="185"/>
-      <c r="J197" s="185"/>
-      <c r="K197" s="185"/>
-      <c r="L197" s="185"/>
-      <c r="M197" s="185"/>
-      <c r="N197" s="185"/>
-      <c r="O197" s="185"/>
-      <c r="P197" s="185"/>
-      <c r="Q197" s="179"/>
+      <c r="G197" s="174"/>
+      <c r="H197" s="174"/>
+      <c r="I197" s="174"/>
+      <c r="J197" s="174"/>
+      <c r="K197" s="174"/>
+      <c r="L197" s="174"/>
+      <c r="M197" s="174"/>
+      <c r="N197" s="174"/>
+      <c r="O197" s="174"/>
+      <c r="P197" s="174"/>
+      <c r="Q197" s="175"/>
     </row>
     <row r="198" spans="2:17">
       <c r="E198" s="80" t="s">
         <v>389</v>
       </c>
-      <c r="F198" s="171" t="s">
+      <c r="F198" s="173" t="s">
         <v>203</v>
       </c>
-      <c r="G198" s="185"/>
-      <c r="H198" s="185"/>
-      <c r="I198" s="185"/>
-      <c r="J198" s="185"/>
-      <c r="K198" s="185"/>
-      <c r="L198" s="185"/>
-      <c r="M198" s="185"/>
-      <c r="N198" s="185"/>
-      <c r="O198" s="185"/>
-      <c r="P198" s="185"/>
-      <c r="Q198" s="179"/>
+      <c r="G198" s="174"/>
+      <c r="H198" s="174"/>
+      <c r="I198" s="174"/>
+      <c r="J198" s="174"/>
+      <c r="K198" s="174"/>
+      <c r="L198" s="174"/>
+      <c r="M198" s="174"/>
+      <c r="N198" s="174"/>
+      <c r="O198" s="174"/>
+      <c r="P198" s="174"/>
+      <c r="Q198" s="175"/>
     </row>
     <row r="199" spans="2:17" ht="16.5" customHeight="1">
       <c r="E199" s="80" t="s">
         <v>413</v>
       </c>
-      <c r="F199" s="180" t="s">
+      <c r="F199" s="170" t="s">
         <v>520</v>
       </c>
-      <c r="G199" s="186"/>
-      <c r="H199" s="186"/>
-      <c r="I199" s="186"/>
-      <c r="J199" s="186"/>
-      <c r="K199" s="186"/>
-      <c r="L199" s="186"/>
-      <c r="M199" s="186"/>
-      <c r="N199" s="186"/>
-      <c r="O199" s="186"/>
-      <c r="P199" s="186"/>
-      <c r="Q199" s="187"/>
+      <c r="G199" s="171"/>
+      <c r="H199" s="171"/>
+      <c r="I199" s="171"/>
+      <c r="J199" s="171"/>
+      <c r="K199" s="171"/>
+      <c r="L199" s="171"/>
+      <c r="M199" s="171"/>
+      <c r="N199" s="171"/>
+      <c r="O199" s="171"/>
+      <c r="P199" s="171"/>
+      <c r="Q199" s="172"/>
     </row>
   </sheetData>
   <mergeCells count="160">
+    <mergeCell ref="E12:Q12"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="E4:Q4"/>
+    <mergeCell ref="E5:Q5"/>
+    <mergeCell ref="E6:Q6"/>
+    <mergeCell ref="E9:Q9"/>
+    <mergeCell ref="E10:Q10"/>
+    <mergeCell ref="E11:Q11"/>
+    <mergeCell ref="F21:Q21"/>
+    <mergeCell ref="F28:Q28"/>
+    <mergeCell ref="H31:Q31"/>
+    <mergeCell ref="H32:Q32"/>
+    <mergeCell ref="H33:Q33"/>
+    <mergeCell ref="H34:Q34"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="P20:Q20"/>
+    <mergeCell ref="N45:Q45"/>
+    <mergeCell ref="N46:Q46"/>
+    <mergeCell ref="N47:Q47"/>
+    <mergeCell ref="N48:Q48"/>
+    <mergeCell ref="F49:Q49"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="P52:Q52"/>
+    <mergeCell ref="F35:Q35"/>
+    <mergeCell ref="H38:Q38"/>
+    <mergeCell ref="H39:Q39"/>
+    <mergeCell ref="H40:Q40"/>
+    <mergeCell ref="H41:Q41"/>
+    <mergeCell ref="F42:Q42"/>
+    <mergeCell ref="F56:Q56"/>
+    <mergeCell ref="N59:Q59"/>
+    <mergeCell ref="N60:Q60"/>
+    <mergeCell ref="N61:Q61"/>
+    <mergeCell ref="N62:Q62"/>
+    <mergeCell ref="F64:Q64"/>
+    <mergeCell ref="N53:O53"/>
+    <mergeCell ref="P53:Q53"/>
+    <mergeCell ref="N54:O54"/>
+    <mergeCell ref="P54:Q54"/>
+    <mergeCell ref="N55:O55"/>
+    <mergeCell ref="P55:Q55"/>
+    <mergeCell ref="F72:M72"/>
+    <mergeCell ref="N72:Q72"/>
+    <mergeCell ref="F73:M73"/>
+    <mergeCell ref="N73:Q73"/>
+    <mergeCell ref="F74:M74"/>
+    <mergeCell ref="N74:Q74"/>
+    <mergeCell ref="F65:Q65"/>
+    <mergeCell ref="F66:Q66"/>
+    <mergeCell ref="F67:Q67"/>
+    <mergeCell ref="F68:Q68"/>
+    <mergeCell ref="F71:M71"/>
+    <mergeCell ref="N71:Q71"/>
+    <mergeCell ref="F79:I79"/>
+    <mergeCell ref="J79:Q79"/>
+    <mergeCell ref="F80:Q80"/>
+    <mergeCell ref="H83:Q83"/>
+    <mergeCell ref="H84:Q84"/>
+    <mergeCell ref="H85:Q85"/>
+    <mergeCell ref="F76:I76"/>
+    <mergeCell ref="J76:Q76"/>
+    <mergeCell ref="F77:I77"/>
+    <mergeCell ref="J77:Q77"/>
+    <mergeCell ref="F78:I78"/>
+    <mergeCell ref="J78:Q78"/>
+    <mergeCell ref="F94:Q94"/>
+    <mergeCell ref="F97:Q97"/>
+    <mergeCell ref="F98:Q98"/>
+    <mergeCell ref="F99:Q99"/>
+    <mergeCell ref="F100:Q100"/>
+    <mergeCell ref="F101:Q101"/>
+    <mergeCell ref="H86:Q86"/>
+    <mergeCell ref="F87:Q87"/>
+    <mergeCell ref="H90:Q90"/>
+    <mergeCell ref="H91:Q91"/>
+    <mergeCell ref="H92:Q92"/>
+    <mergeCell ref="H93:Q93"/>
+    <mergeCell ref="F112:Q112"/>
+    <mergeCell ref="F113:Q113"/>
+    <mergeCell ref="F114:Q114"/>
+    <mergeCell ref="F115:Q115"/>
+    <mergeCell ref="F118:I118"/>
+    <mergeCell ref="J118:M118"/>
+    <mergeCell ref="N118:Q118"/>
+    <mergeCell ref="F104:Q104"/>
+    <mergeCell ref="F105:Q105"/>
+    <mergeCell ref="F106:Q106"/>
+    <mergeCell ref="F107:Q107"/>
+    <mergeCell ref="F108:Q108"/>
+    <mergeCell ref="F111:Q111"/>
+    <mergeCell ref="H125:Q125"/>
+    <mergeCell ref="F126:Q126"/>
+    <mergeCell ref="F127:Q127"/>
+    <mergeCell ref="F128:Q128"/>
+    <mergeCell ref="F129:Q129"/>
+    <mergeCell ref="H132:Q132"/>
+    <mergeCell ref="F119:I119"/>
+    <mergeCell ref="J119:M119"/>
+    <mergeCell ref="N119:Q119"/>
+    <mergeCell ref="F120:Q120"/>
+    <mergeCell ref="F121:Q121"/>
+    <mergeCell ref="F122:Q122"/>
+    <mergeCell ref="F141:Q141"/>
+    <mergeCell ref="F142:Q142"/>
+    <mergeCell ref="F143:Q143"/>
+    <mergeCell ref="H146:Q146"/>
+    <mergeCell ref="F147:Q147"/>
+    <mergeCell ref="F148:Q148"/>
+    <mergeCell ref="F133:Q133"/>
+    <mergeCell ref="F134:Q134"/>
+    <mergeCell ref="F135:Q135"/>
+    <mergeCell ref="F136:Q136"/>
+    <mergeCell ref="H139:Q139"/>
+    <mergeCell ref="F140:Q140"/>
+    <mergeCell ref="F157:Q157"/>
+    <mergeCell ref="H160:Q160"/>
+    <mergeCell ref="F161:Q161"/>
+    <mergeCell ref="F162:Q162"/>
+    <mergeCell ref="F163:Q163"/>
+    <mergeCell ref="F164:Q164"/>
+    <mergeCell ref="F149:Q149"/>
+    <mergeCell ref="F150:Q150"/>
+    <mergeCell ref="H153:Q153"/>
+    <mergeCell ref="F154:Q154"/>
+    <mergeCell ref="F155:Q155"/>
+    <mergeCell ref="F156:Q156"/>
+    <mergeCell ref="F175:Q175"/>
+    <mergeCell ref="F176:Q176"/>
+    <mergeCell ref="F177:Q177"/>
+    <mergeCell ref="F178:Q178"/>
+    <mergeCell ref="H181:Q181"/>
+    <mergeCell ref="F182:Q182"/>
+    <mergeCell ref="H167:Q167"/>
+    <mergeCell ref="F168:Q168"/>
+    <mergeCell ref="F169:Q169"/>
+    <mergeCell ref="F170:Q170"/>
+    <mergeCell ref="F171:Q171"/>
+    <mergeCell ref="H174:Q174"/>
     <mergeCell ref="F199:Q199"/>
     <mergeCell ref="F191:Q191"/>
     <mergeCell ref="F192:Q192"/>
@@ -15423,153 +15570,6 @@
     <mergeCell ref="H188:Q188"/>
     <mergeCell ref="F189:Q189"/>
     <mergeCell ref="F190:Q190"/>
-    <mergeCell ref="F175:Q175"/>
-    <mergeCell ref="F176:Q176"/>
-    <mergeCell ref="F177:Q177"/>
-    <mergeCell ref="F178:Q178"/>
-    <mergeCell ref="H181:Q181"/>
-    <mergeCell ref="F182:Q182"/>
-    <mergeCell ref="H167:Q167"/>
-    <mergeCell ref="F168:Q168"/>
-    <mergeCell ref="F169:Q169"/>
-    <mergeCell ref="F170:Q170"/>
-    <mergeCell ref="F171:Q171"/>
-    <mergeCell ref="H174:Q174"/>
-    <mergeCell ref="F157:Q157"/>
-    <mergeCell ref="H160:Q160"/>
-    <mergeCell ref="F161:Q161"/>
-    <mergeCell ref="F162:Q162"/>
-    <mergeCell ref="F163:Q163"/>
-    <mergeCell ref="F164:Q164"/>
-    <mergeCell ref="F149:Q149"/>
-    <mergeCell ref="F150:Q150"/>
-    <mergeCell ref="H153:Q153"/>
-    <mergeCell ref="F154:Q154"/>
-    <mergeCell ref="F155:Q155"/>
-    <mergeCell ref="F156:Q156"/>
-    <mergeCell ref="F141:Q141"/>
-    <mergeCell ref="F142:Q142"/>
-    <mergeCell ref="F143:Q143"/>
-    <mergeCell ref="H146:Q146"/>
-    <mergeCell ref="F147:Q147"/>
-    <mergeCell ref="F148:Q148"/>
-    <mergeCell ref="F133:Q133"/>
-    <mergeCell ref="F134:Q134"/>
-    <mergeCell ref="F135:Q135"/>
-    <mergeCell ref="F136:Q136"/>
-    <mergeCell ref="H139:Q139"/>
-    <mergeCell ref="F140:Q140"/>
-    <mergeCell ref="H125:Q125"/>
-    <mergeCell ref="F126:Q126"/>
-    <mergeCell ref="F127:Q127"/>
-    <mergeCell ref="F128:Q128"/>
-    <mergeCell ref="F129:Q129"/>
-    <mergeCell ref="H132:Q132"/>
-    <mergeCell ref="F119:I119"/>
-    <mergeCell ref="J119:M119"/>
-    <mergeCell ref="N119:Q119"/>
-    <mergeCell ref="F120:Q120"/>
-    <mergeCell ref="F121:Q121"/>
-    <mergeCell ref="F122:Q122"/>
-    <mergeCell ref="F112:Q112"/>
-    <mergeCell ref="F113:Q113"/>
-    <mergeCell ref="F114:Q114"/>
-    <mergeCell ref="F115:Q115"/>
-    <mergeCell ref="F118:I118"/>
-    <mergeCell ref="J118:M118"/>
-    <mergeCell ref="N118:Q118"/>
-    <mergeCell ref="F104:Q104"/>
-    <mergeCell ref="F105:Q105"/>
-    <mergeCell ref="F106:Q106"/>
-    <mergeCell ref="F107:Q107"/>
-    <mergeCell ref="F108:Q108"/>
-    <mergeCell ref="F111:Q111"/>
-    <mergeCell ref="F94:Q94"/>
-    <mergeCell ref="F97:Q97"/>
-    <mergeCell ref="F98:Q98"/>
-    <mergeCell ref="F99:Q99"/>
-    <mergeCell ref="F100:Q100"/>
-    <mergeCell ref="F101:Q101"/>
-    <mergeCell ref="H86:Q86"/>
-    <mergeCell ref="F87:Q87"/>
-    <mergeCell ref="H90:Q90"/>
-    <mergeCell ref="H91:Q91"/>
-    <mergeCell ref="H92:Q92"/>
-    <mergeCell ref="H93:Q93"/>
-    <mergeCell ref="F79:I79"/>
-    <mergeCell ref="J79:Q79"/>
-    <mergeCell ref="F80:Q80"/>
-    <mergeCell ref="H83:Q83"/>
-    <mergeCell ref="H84:Q84"/>
-    <mergeCell ref="H85:Q85"/>
-    <mergeCell ref="F76:I76"/>
-    <mergeCell ref="J76:Q76"/>
-    <mergeCell ref="F77:I77"/>
-    <mergeCell ref="J77:Q77"/>
-    <mergeCell ref="F78:I78"/>
-    <mergeCell ref="J78:Q78"/>
-    <mergeCell ref="F72:M72"/>
-    <mergeCell ref="N72:Q72"/>
-    <mergeCell ref="F73:M73"/>
-    <mergeCell ref="N73:Q73"/>
-    <mergeCell ref="F74:M74"/>
-    <mergeCell ref="N74:Q74"/>
-    <mergeCell ref="F65:Q65"/>
-    <mergeCell ref="F66:Q66"/>
-    <mergeCell ref="F67:Q67"/>
-    <mergeCell ref="F68:Q68"/>
-    <mergeCell ref="F71:M71"/>
-    <mergeCell ref="N71:Q71"/>
-    <mergeCell ref="F56:Q56"/>
-    <mergeCell ref="N59:Q59"/>
-    <mergeCell ref="N60:Q60"/>
-    <mergeCell ref="N61:Q61"/>
-    <mergeCell ref="N62:Q62"/>
-    <mergeCell ref="F64:Q64"/>
-    <mergeCell ref="N53:O53"/>
-    <mergeCell ref="P53:Q53"/>
-    <mergeCell ref="N54:O54"/>
-    <mergeCell ref="P54:Q54"/>
-    <mergeCell ref="N55:O55"/>
-    <mergeCell ref="P55:Q55"/>
-    <mergeCell ref="N45:Q45"/>
-    <mergeCell ref="N46:Q46"/>
-    <mergeCell ref="N47:Q47"/>
-    <mergeCell ref="N48:Q48"/>
-    <mergeCell ref="F49:Q49"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="P52:Q52"/>
-    <mergeCell ref="F35:Q35"/>
-    <mergeCell ref="H38:Q38"/>
-    <mergeCell ref="H39:Q39"/>
-    <mergeCell ref="H40:Q40"/>
-    <mergeCell ref="H41:Q41"/>
-    <mergeCell ref="F42:Q42"/>
-    <mergeCell ref="F21:Q21"/>
-    <mergeCell ref="F28:Q28"/>
-    <mergeCell ref="H31:Q31"/>
-    <mergeCell ref="H32:Q32"/>
-    <mergeCell ref="H33:Q33"/>
-    <mergeCell ref="H34:Q34"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="P20:Q20"/>
-    <mergeCell ref="E12:Q12"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="P18:Q18"/>
-    <mergeCell ref="E4:Q4"/>
-    <mergeCell ref="E5:Q5"/>
-    <mergeCell ref="E6:Q6"/>
-    <mergeCell ref="E9:Q9"/>
-    <mergeCell ref="E10:Q10"/>
-    <mergeCell ref="E11:Q11"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15682,12 +15682,12 @@
       <c r="D3" s="13"/>
       <c r="E3" s="14"/>
       <c r="F3" s="14"/>
-      <c r="G3" s="164" t="s">
+      <c r="G3" s="168" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="164"/>
-      <c r="I3" s="164"/>
-      <c r="J3" s="164"/>
+      <c r="H3" s="168"/>
+      <c r="I3" s="168"/>
+      <c r="J3" s="168"/>
       <c r="K3" s="14"/>
       <c r="L3" s="14"/>
       <c r="M3" s="14"/>
@@ -15746,16 +15746,16 @@
       <c r="M5" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="N5" s="190" t="s">
+      <c r="N5" s="197" t="s">
         <v>207</v>
       </c>
-      <c r="O5" s="191"/>
-      <c r="P5" s="192"/>
-      <c r="Q5" s="190" t="s">
+      <c r="O5" s="198"/>
+      <c r="P5" s="199"/>
+      <c r="Q5" s="197" t="s">
         <v>208</v>
       </c>
-      <c r="R5" s="191"/>
-      <c r="S5" s="192"/>
+      <c r="R5" s="198"/>
+      <c r="S5" s="199"/>
       <c r="T5" s="8" t="s">
         <v>209</v>
       </c>
@@ -15813,18 +15813,18 @@
       <c r="N6" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="O6" s="160" t="s">
+      <c r="O6" s="163" t="s">
         <v>218</v>
       </c>
-      <c r="P6" s="160"/>
-      <c r="Q6" s="160"/>
-      <c r="R6" s="160"/>
-      <c r="S6" s="193" t="s">
+      <c r="P6" s="163"/>
+      <c r="Q6" s="163"/>
+      <c r="R6" s="163"/>
+      <c r="S6" s="200" t="s">
         <v>700</v>
       </c>
-      <c r="T6" s="193"/>
-      <c r="U6" s="193"/>
-      <c r="V6" s="193"/>
+      <c r="T6" s="200"/>
+      <c r="U6" s="200"/>
+      <c r="V6" s="200"/>
       <c r="W6" s="9" t="s">
         <v>219</v>
       </c>
@@ -15861,20 +15861,20 @@
       <c r="J7" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="K7" s="160" t="s">
+      <c r="K7" s="163" t="s">
         <v>222</v>
       </c>
-      <c r="L7" s="160"/>
-      <c r="M7" s="160"/>
-      <c r="N7" s="160"/>
-      <c r="O7" s="160"/>
-      <c r="P7" s="160"/>
-      <c r="Q7" s="160"/>
-      <c r="R7" s="160"/>
-      <c r="S7" s="160"/>
-      <c r="T7" s="160"/>
-      <c r="U7" s="160"/>
-      <c r="V7" s="160"/>
+      <c r="L7" s="163"/>
+      <c r="M7" s="163"/>
+      <c r="N7" s="163"/>
+      <c r="O7" s="163"/>
+      <c r="P7" s="163"/>
+      <c r="Q7" s="163"/>
+      <c r="R7" s="163"/>
+      <c r="S7" s="163"/>
+      <c r="T7" s="163"/>
+      <c r="U7" s="163"/>
+      <c r="V7" s="163"/>
       <c r="W7" s="9" t="s">
         <v>223</v>
       </c>
@@ -15911,20 +15911,20 @@
       <c r="J8" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="K8" s="160" t="s">
+      <c r="K8" s="163" t="s">
         <v>226</v>
       </c>
-      <c r="L8" s="160"/>
-      <c r="M8" s="160"/>
-      <c r="N8" s="160"/>
-      <c r="O8" s="160"/>
-      <c r="P8" s="160"/>
-      <c r="Q8" s="160"/>
-      <c r="R8" s="160"/>
-      <c r="S8" s="160"/>
-      <c r="T8" s="160"/>
-      <c r="U8" s="160"/>
-      <c r="V8" s="160"/>
+      <c r="L8" s="163"/>
+      <c r="M8" s="163"/>
+      <c r="N8" s="163"/>
+      <c r="O8" s="163"/>
+      <c r="P8" s="163"/>
+      <c r="Q8" s="163"/>
+      <c r="R8" s="163"/>
+      <c r="S8" s="163"/>
+      <c r="T8" s="163"/>
+      <c r="U8" s="163"/>
+      <c r="V8" s="163"/>
       <c r="W8" s="9" t="s">
         <v>227</v>
       </c>
@@ -15967,24 +15967,24 @@
       <c r="J10" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="K10" s="194" t="s">
+      <c r="K10" s="191" t="s">
         <v>231</v>
       </c>
-      <c r="L10" s="194"/>
-      <c r="M10" s="194"/>
-      <c r="N10" s="194" t="s">
+      <c r="L10" s="191"/>
+      <c r="M10" s="191"/>
+      <c r="N10" s="191" t="s">
         <v>232</v>
       </c>
-      <c r="O10" s="194"/>
-      <c r="P10" s="194"/>
-      <c r="Q10" s="194" t="s">
+      <c r="O10" s="191"/>
+      <c r="P10" s="191"/>
+      <c r="Q10" s="191" t="s">
         <v>233</v>
       </c>
-      <c r="R10" s="194"/>
-      <c r="S10" s="194"/>
-      <c r="T10" s="194"/>
-      <c r="U10" s="194"/>
-      <c r="V10" s="194"/>
+      <c r="R10" s="191"/>
+      <c r="S10" s="191"/>
+      <c r="T10" s="191"/>
+      <c r="U10" s="191"/>
+      <c r="V10" s="191"/>
       <c r="W10" s="9" t="s">
         <v>234</v>
       </c>
@@ -16021,26 +16021,26 @@
       <c r="J11" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="K11" s="194" t="s">
+      <c r="K11" s="191" t="s">
         <v>237</v>
       </c>
-      <c r="L11" s="194"/>
-      <c r="M11" s="195" t="s">
+      <c r="L11" s="191"/>
+      <c r="M11" s="192" t="s">
         <v>238</v>
       </c>
-      <c r="N11" s="196"/>
-      <c r="O11" s="194" t="s">
+      <c r="N11" s="193"/>
+      <c r="O11" s="191" t="s">
         <v>239</v>
       </c>
-      <c r="P11" s="194"/>
-      <c r="Q11" s="194"/>
-      <c r="R11" s="194" t="s">
+      <c r="P11" s="191"/>
+      <c r="Q11" s="191"/>
+      <c r="R11" s="191" t="s">
         <v>240</v>
       </c>
-      <c r="S11" s="194"/>
-      <c r="T11" s="194"/>
-      <c r="U11" s="194"/>
-      <c r="V11" s="194"/>
+      <c r="S11" s="191"/>
+      <c r="T11" s="191"/>
+      <c r="U11" s="191"/>
+      <c r="V11" s="191"/>
       <c r="W11" s="9" t="s">
         <v>241</v>
       </c>
@@ -16083,20 +16083,20 @@
       <c r="L12" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="M12" s="197" t="s">
+      <c r="M12" s="194" t="s">
         <v>245</v>
       </c>
-      <c r="N12" s="198"/>
-      <c r="O12" s="198"/>
-      <c r="P12" s="198"/>
-      <c r="Q12" s="198"/>
-      <c r="R12" s="199"/>
-      <c r="S12" s="197" t="s">
+      <c r="N12" s="195"/>
+      <c r="O12" s="195"/>
+      <c r="P12" s="195"/>
+      <c r="Q12" s="195"/>
+      <c r="R12" s="196"/>
+      <c r="S12" s="194" t="s">
         <v>246</v>
       </c>
-      <c r="T12" s="198"/>
-      <c r="U12" s="198"/>
-      <c r="V12" s="199"/>
+      <c r="T12" s="195"/>
+      <c r="U12" s="195"/>
+      <c r="V12" s="196"/>
       <c r="W12" s="9" t="s">
         <v>247</v>
       </c>
@@ -16133,22 +16133,22 @@
       <c r="J13" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="K13" s="194" t="s">
+      <c r="K13" s="191" t="s">
         <v>250</v>
       </c>
-      <c r="L13" s="194"/>
-      <c r="M13" s="194"/>
-      <c r="N13" s="194"/>
-      <c r="O13" s="194"/>
-      <c r="P13" s="194"/>
-      <c r="Q13" s="194"/>
-      <c r="R13" s="194"/>
-      <c r="S13" s="197" t="s">
+      <c r="L13" s="191"/>
+      <c r="M13" s="191"/>
+      <c r="N13" s="191"/>
+      <c r="O13" s="191"/>
+      <c r="P13" s="191"/>
+      <c r="Q13" s="191"/>
+      <c r="R13" s="191"/>
+      <c r="S13" s="194" t="s">
         <v>251</v>
       </c>
-      <c r="T13" s="198"/>
-      <c r="U13" s="198"/>
-      <c r="V13" s="199"/>
+      <c r="T13" s="195"/>
+      <c r="U13" s="195"/>
+      <c r="V13" s="196"/>
       <c r="W13" s="9" t="s">
         <v>252</v>
       </c>
@@ -16338,17 +16338,17 @@
       <c r="M16" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="N16" s="197" t="s">
+      <c r="N16" s="194" t="s">
         <v>261</v>
       </c>
-      <c r="O16" s="198"/>
-      <c r="P16" s="198"/>
-      <c r="Q16" s="198"/>
-      <c r="R16" s="198"/>
-      <c r="S16" s="198"/>
-      <c r="T16" s="198"/>
-      <c r="U16" s="198"/>
-      <c r="V16" s="199"/>
+      <c r="O16" s="195"/>
+      <c r="P16" s="195"/>
+      <c r="Q16" s="195"/>
+      <c r="R16" s="195"/>
+      <c r="S16" s="195"/>
+      <c r="T16" s="195"/>
+      <c r="U16" s="195"/>
+      <c r="V16" s="196"/>
       <c r="W16" s="9" t="s">
         <v>256</v>
       </c>
@@ -16406,13 +16406,13 @@
       <c r="Q17" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="R17" s="194" t="s">
+      <c r="R17" s="191" t="s">
         <v>264</v>
       </c>
-      <c r="S17" s="194"/>
-      <c r="T17" s="194"/>
-      <c r="U17" s="194"/>
-      <c r="V17" s="194"/>
+      <c r="S17" s="191"/>
+      <c r="T17" s="191"/>
+      <c r="U17" s="191"/>
+      <c r="V17" s="191"/>
       <c r="W17" s="9" t="s">
         <v>265</v>
       </c>
@@ -16461,16 +16461,16 @@
       <c r="N18" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="O18" s="194" t="s">
+      <c r="O18" s="191" t="s">
         <v>268</v>
       </c>
-      <c r="P18" s="194"/>
-      <c r="Q18" s="194"/>
-      <c r="R18" s="194"/>
-      <c r="S18" s="194"/>
-      <c r="T18" s="194"/>
-      <c r="U18" s="194"/>
-      <c r="V18" s="194"/>
+      <c r="P18" s="191"/>
+      <c r="Q18" s="191"/>
+      <c r="R18" s="191"/>
+      <c r="S18" s="191"/>
+      <c r="T18" s="191"/>
+      <c r="U18" s="191"/>
+      <c r="V18" s="191"/>
       <c r="W18" s="9" t="s">
         <v>269</v>
       </c>
@@ -16519,16 +16519,16 @@
       <c r="N19" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="O19" s="194" t="s">
+      <c r="O19" s="191" t="s">
         <v>272</v>
       </c>
-      <c r="P19" s="194"/>
-      <c r="Q19" s="194"/>
-      <c r="R19" s="194"/>
-      <c r="S19" s="194"/>
-      <c r="T19" s="194"/>
-      <c r="U19" s="194"/>
-      <c r="V19" s="194"/>
+      <c r="P19" s="191"/>
+      <c r="Q19" s="191"/>
+      <c r="R19" s="191"/>
+      <c r="S19" s="191"/>
+      <c r="T19" s="191"/>
+      <c r="U19" s="191"/>
+      <c r="V19" s="191"/>
       <c r="W19" s="9" t="s">
         <v>269</v>
       </c>
@@ -16577,16 +16577,16 @@
       <c r="N20" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="O20" s="194" t="s">
+      <c r="O20" s="191" t="s">
         <v>275</v>
       </c>
-      <c r="P20" s="194"/>
-      <c r="Q20" s="194"/>
-      <c r="R20" s="194"/>
-      <c r="S20" s="194"/>
-      <c r="T20" s="194"/>
-      <c r="U20" s="194"/>
-      <c r="V20" s="194"/>
+      <c r="P20" s="191"/>
+      <c r="Q20" s="191"/>
+      <c r="R20" s="191"/>
+      <c r="S20" s="191"/>
+      <c r="T20" s="191"/>
+      <c r="U20" s="191"/>
+      <c r="V20" s="191"/>
       <c r="W20" s="9" t="s">
         <v>269</v>
       </c>
@@ -16629,18 +16629,18 @@
       <c r="L21" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="M21" s="194" t="s">
+      <c r="M21" s="191" t="s">
         <v>278</v>
       </c>
-      <c r="N21" s="194"/>
-      <c r="O21" s="194"/>
-      <c r="P21" s="194"/>
-      <c r="Q21" s="194"/>
-      <c r="R21" s="194"/>
-      <c r="S21" s="194"/>
-      <c r="T21" s="194"/>
-      <c r="U21" s="194"/>
-      <c r="V21" s="194"/>
+      <c r="N21" s="191"/>
+      <c r="O21" s="191"/>
+      <c r="P21" s="191"/>
+      <c r="Q21" s="191"/>
+      <c r="R21" s="191"/>
+      <c r="S21" s="191"/>
+      <c r="T21" s="191"/>
+      <c r="U21" s="191"/>
+      <c r="V21" s="191"/>
       <c r="W21" s="9" t="s">
         <v>255</v>
       </c>
@@ -16683,18 +16683,18 @@
       <c r="L22" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="M22" s="194" t="s">
+      <c r="M22" s="191" t="s">
         <v>281</v>
       </c>
-      <c r="N22" s="194"/>
-      <c r="O22" s="194"/>
-      <c r="P22" s="194"/>
-      <c r="Q22" s="194"/>
-      <c r="R22" s="194"/>
-      <c r="S22" s="194"/>
-      <c r="T22" s="194"/>
-      <c r="U22" s="194"/>
-      <c r="V22" s="194"/>
+      <c r="N22" s="191"/>
+      <c r="O22" s="191"/>
+      <c r="P22" s="191"/>
+      <c r="Q22" s="191"/>
+      <c r="R22" s="191"/>
+      <c r="S22" s="191"/>
+      <c r="T22" s="191"/>
+      <c r="U22" s="191"/>
+      <c r="V22" s="191"/>
       <c r="W22" s="9" t="s">
         <v>282</v>
       </c>
@@ -16737,20 +16737,20 @@
       <c r="J24" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="K24" s="194" t="s">
+      <c r="K24" s="191" t="s">
         <v>286</v>
       </c>
-      <c r="L24" s="194"/>
-      <c r="M24" s="194"/>
-      <c r="N24" s="194"/>
-      <c r="O24" s="194"/>
-      <c r="P24" s="194"/>
-      <c r="Q24" s="194"/>
-      <c r="R24" s="194"/>
-      <c r="S24" s="194"/>
-      <c r="T24" s="194"/>
-      <c r="U24" s="194"/>
-      <c r="V24" s="194"/>
+      <c r="L24" s="191"/>
+      <c r="M24" s="191"/>
+      <c r="N24" s="191"/>
+      <c r="O24" s="191"/>
+      <c r="P24" s="191"/>
+      <c r="Q24" s="191"/>
+      <c r="R24" s="191"/>
+      <c r="S24" s="191"/>
+      <c r="T24" s="191"/>
+      <c r="U24" s="191"/>
+      <c r="V24" s="191"/>
       <c r="W24" s="9" t="s">
         <v>255</v>
       </c>
@@ -16787,20 +16787,20 @@
       <c r="J25" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="K25" s="194" t="s">
+      <c r="K25" s="191" t="s">
         <v>289</v>
       </c>
-      <c r="L25" s="194"/>
-      <c r="M25" s="194"/>
-      <c r="N25" s="194"/>
-      <c r="O25" s="194"/>
-      <c r="P25" s="194"/>
-      <c r="Q25" s="194"/>
-      <c r="R25" s="194"/>
-      <c r="S25" s="194"/>
-      <c r="T25" s="194"/>
-      <c r="U25" s="194"/>
-      <c r="V25" s="194"/>
+      <c r="L25" s="191"/>
+      <c r="M25" s="191"/>
+      <c r="N25" s="191"/>
+      <c r="O25" s="191"/>
+      <c r="P25" s="191"/>
+      <c r="Q25" s="191"/>
+      <c r="R25" s="191"/>
+      <c r="S25" s="191"/>
+      <c r="T25" s="191"/>
+      <c r="U25" s="191"/>
+      <c r="V25" s="191"/>
       <c r="W25" s="9" t="s">
         <v>255</v>
       </c>
@@ -16837,20 +16837,20 @@
       <c r="J26" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="K26" s="194" t="s">
+      <c r="K26" s="191" t="s">
         <v>292</v>
       </c>
-      <c r="L26" s="194"/>
-      <c r="M26" s="194"/>
-      <c r="N26" s="194"/>
-      <c r="O26" s="194"/>
-      <c r="P26" s="194"/>
-      <c r="Q26" s="194"/>
-      <c r="R26" s="194"/>
-      <c r="S26" s="194"/>
-      <c r="T26" s="194"/>
-      <c r="U26" s="194"/>
-      <c r="V26" s="194"/>
+      <c r="L26" s="191"/>
+      <c r="M26" s="191"/>
+      <c r="N26" s="191"/>
+      <c r="O26" s="191"/>
+      <c r="P26" s="191"/>
+      <c r="Q26" s="191"/>
+      <c r="R26" s="191"/>
+      <c r="S26" s="191"/>
+      <c r="T26" s="191"/>
+      <c r="U26" s="191"/>
+      <c r="V26" s="191"/>
       <c r="W26" s="9" t="s">
         <v>282</v>
       </c>
@@ -16899,16 +16899,16 @@
       <c r="N27" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="O27" s="194" t="s">
+      <c r="O27" s="191" t="s">
         <v>295</v>
       </c>
-      <c r="P27" s="194"/>
-      <c r="Q27" s="194"/>
-      <c r="R27" s="194"/>
-      <c r="S27" s="194"/>
-      <c r="T27" s="194"/>
-      <c r="U27" s="194"/>
-      <c r="V27" s="194"/>
+      <c r="P27" s="191"/>
+      <c r="Q27" s="191"/>
+      <c r="R27" s="191"/>
+      <c r="S27" s="191"/>
+      <c r="T27" s="191"/>
+      <c r="U27" s="191"/>
+      <c r="V27" s="191"/>
       <c r="W27" s="9" t="s">
         <v>282</v>
       </c>
@@ -17063,15 +17063,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="K25:V25"/>
-    <mergeCell ref="K26:V26"/>
-    <mergeCell ref="O27:V27"/>
-    <mergeCell ref="O18:V18"/>
-    <mergeCell ref="O19:V19"/>
-    <mergeCell ref="O20:V20"/>
-    <mergeCell ref="M21:V21"/>
-    <mergeCell ref="M22:V22"/>
-    <mergeCell ref="K24:V24"/>
+    <mergeCell ref="K7:V7"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="O6:R6"/>
+    <mergeCell ref="S6:V6"/>
     <mergeCell ref="R17:V17"/>
     <mergeCell ref="K8:V8"/>
     <mergeCell ref="K10:M10"/>
@@ -17086,12 +17083,15 @@
     <mergeCell ref="K13:R13"/>
     <mergeCell ref="S13:V13"/>
     <mergeCell ref="N16:V16"/>
-    <mergeCell ref="K7:V7"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="O6:R6"/>
-    <mergeCell ref="S6:V6"/>
+    <mergeCell ref="K25:V25"/>
+    <mergeCell ref="K26:V26"/>
+    <mergeCell ref="O27:V27"/>
+    <mergeCell ref="O18:V18"/>
+    <mergeCell ref="O19:V19"/>
+    <mergeCell ref="O20:V20"/>
+    <mergeCell ref="M21:V21"/>
+    <mergeCell ref="M22:V22"/>
+    <mergeCell ref="K24:V24"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="S22">
@@ -17119,55 +17119,55 @@
   <sheetData>
     <row r="2" spans="2:17" ht="17.25" thickBot="1"/>
     <row r="3" spans="2:17">
-      <c r="E3" s="206" t="s">
+      <c r="E3" s="224" t="s">
         <v>386</v>
       </c>
-      <c r="F3" s="207"/>
-      <c r="G3" s="207"/>
-      <c r="H3" s="207"/>
-      <c r="I3" s="207"/>
-      <c r="J3" s="207"/>
-      <c r="K3" s="207"/>
-      <c r="L3" s="207"/>
-      <c r="M3" s="207"/>
-      <c r="N3" s="207"/>
-      <c r="O3" s="207"/>
-      <c r="P3" s="207"/>
-      <c r="Q3" s="208"/>
+      <c r="F3" s="225"/>
+      <c r="G3" s="225"/>
+      <c r="H3" s="225"/>
+      <c r="I3" s="225"/>
+      <c r="J3" s="225"/>
+      <c r="K3" s="225"/>
+      <c r="L3" s="225"/>
+      <c r="M3" s="225"/>
+      <c r="N3" s="225"/>
+      <c r="O3" s="225"/>
+      <c r="P3" s="225"/>
+      <c r="Q3" s="226"/>
     </row>
     <row r="4" spans="2:17">
-      <c r="E4" s="209" t="s">
+      <c r="E4" s="227" t="s">
         <v>387</v>
       </c>
-      <c r="F4" s="210"/>
-      <c r="G4" s="210"/>
-      <c r="H4" s="210"/>
-      <c r="I4" s="210"/>
-      <c r="J4" s="210"/>
-      <c r="K4" s="210"/>
-      <c r="L4" s="210"/>
-      <c r="M4" s="210"/>
-      <c r="N4" s="210"/>
-      <c r="O4" s="210"/>
-      <c r="P4" s="210"/>
-      <c r="Q4" s="211"/>
+      <c r="F4" s="208"/>
+      <c r="G4" s="208"/>
+      <c r="H4" s="208"/>
+      <c r="I4" s="208"/>
+      <c r="J4" s="208"/>
+      <c r="K4" s="208"/>
+      <c r="L4" s="208"/>
+      <c r="M4" s="208"/>
+      <c r="N4" s="208"/>
+      <c r="O4" s="208"/>
+      <c r="P4" s="208"/>
+      <c r="Q4" s="228"/>
     </row>
     <row r="5" spans="2:17" ht="17.25" thickBot="1">
-      <c r="E5" s="200" t="s">
+      <c r="E5" s="221" t="s">
         <v>388</v>
       </c>
-      <c r="F5" s="201"/>
-      <c r="G5" s="201"/>
-      <c r="H5" s="201"/>
-      <c r="I5" s="201"/>
-      <c r="J5" s="201"/>
-      <c r="K5" s="201"/>
-      <c r="L5" s="201"/>
-      <c r="M5" s="201"/>
-      <c r="N5" s="201"/>
-      <c r="O5" s="201"/>
-      <c r="P5" s="201"/>
-      <c r="Q5" s="202"/>
+      <c r="F5" s="222"/>
+      <c r="G5" s="222"/>
+      <c r="H5" s="222"/>
+      <c r="I5" s="222"/>
+      <c r="J5" s="222"/>
+      <c r="K5" s="222"/>
+      <c r="L5" s="222"/>
+      <c r="M5" s="222"/>
+      <c r="N5" s="222"/>
+      <c r="O5" s="222"/>
+      <c r="P5" s="222"/>
+      <c r="Q5" s="223"/>
     </row>
     <row r="6" spans="2:17">
       <c r="E6" s="89"/>
@@ -17186,72 +17186,72 @@
     </row>
     <row r="7" spans="2:17" ht="17.25" thickBot="1"/>
     <row r="8" spans="2:17">
-      <c r="E8" s="206" t="s">
+      <c r="E8" s="224" t="s">
         <v>389</v>
       </c>
-      <c r="F8" s="207"/>
-      <c r="G8" s="207"/>
-      <c r="H8" s="207"/>
-      <c r="I8" s="207"/>
-      <c r="J8" s="207"/>
-      <c r="K8" s="207"/>
-      <c r="L8" s="207"/>
-      <c r="M8" s="207"/>
-      <c r="N8" s="207"/>
-      <c r="O8" s="207"/>
-      <c r="P8" s="207"/>
-      <c r="Q8" s="208"/>
+      <c r="F8" s="225"/>
+      <c r="G8" s="225"/>
+      <c r="H8" s="225"/>
+      <c r="I8" s="225"/>
+      <c r="J8" s="225"/>
+      <c r="K8" s="225"/>
+      <c r="L8" s="225"/>
+      <c r="M8" s="225"/>
+      <c r="N8" s="225"/>
+      <c r="O8" s="225"/>
+      <c r="P8" s="225"/>
+      <c r="Q8" s="226"/>
     </row>
     <row r="9" spans="2:17">
-      <c r="E9" s="209" t="s">
+      <c r="E9" s="227" t="s">
         <v>390</v>
       </c>
-      <c r="F9" s="210"/>
-      <c r="G9" s="210"/>
-      <c r="H9" s="210"/>
-      <c r="I9" s="210"/>
-      <c r="J9" s="210"/>
-      <c r="K9" s="210"/>
-      <c r="L9" s="210"/>
-      <c r="M9" s="210"/>
-      <c r="N9" s="210"/>
-      <c r="O9" s="210"/>
-      <c r="P9" s="210"/>
-      <c r="Q9" s="211"/>
+      <c r="F9" s="208"/>
+      <c r="G9" s="208"/>
+      <c r="H9" s="208"/>
+      <c r="I9" s="208"/>
+      <c r="J9" s="208"/>
+      <c r="K9" s="208"/>
+      <c r="L9" s="208"/>
+      <c r="M9" s="208"/>
+      <c r="N9" s="208"/>
+      <c r="O9" s="208"/>
+      <c r="P9" s="208"/>
+      <c r="Q9" s="228"/>
     </row>
     <row r="10" spans="2:17">
-      <c r="E10" s="209" t="s">
+      <c r="E10" s="227" t="s">
         <v>391</v>
       </c>
-      <c r="F10" s="210"/>
-      <c r="G10" s="210"/>
-      <c r="H10" s="210"/>
-      <c r="I10" s="210"/>
-      <c r="J10" s="210"/>
-      <c r="K10" s="210"/>
-      <c r="L10" s="210"/>
-      <c r="M10" s="210"/>
-      <c r="N10" s="210"/>
-      <c r="O10" s="210"/>
-      <c r="P10" s="210"/>
-      <c r="Q10" s="211"/>
+      <c r="F10" s="208"/>
+      <c r="G10" s="208"/>
+      <c r="H10" s="208"/>
+      <c r="I10" s="208"/>
+      <c r="J10" s="208"/>
+      <c r="K10" s="208"/>
+      <c r="L10" s="208"/>
+      <c r="M10" s="208"/>
+      <c r="N10" s="208"/>
+      <c r="O10" s="208"/>
+      <c r="P10" s="208"/>
+      <c r="Q10" s="228"/>
     </row>
     <row r="11" spans="2:17" ht="17.25" thickBot="1">
-      <c r="E11" s="200" t="s">
+      <c r="E11" s="221" t="s">
         <v>392</v>
       </c>
-      <c r="F11" s="201"/>
-      <c r="G11" s="201"/>
-      <c r="H11" s="201"/>
-      <c r="I11" s="201"/>
-      <c r="J11" s="201"/>
-      <c r="K11" s="201"/>
-      <c r="L11" s="201"/>
-      <c r="M11" s="201"/>
-      <c r="N11" s="201"/>
-      <c r="O11" s="201"/>
-      <c r="P11" s="201"/>
-      <c r="Q11" s="202"/>
+      <c r="F11" s="222"/>
+      <c r="G11" s="222"/>
+      <c r="H11" s="222"/>
+      <c r="I11" s="222"/>
+      <c r="J11" s="222"/>
+      <c r="K11" s="222"/>
+      <c r="L11" s="222"/>
+      <c r="M11" s="222"/>
+      <c r="N11" s="222"/>
+      <c r="O11" s="222"/>
+      <c r="P11" s="222"/>
+      <c r="Q11" s="223"/>
     </row>
     <row r="12" spans="2:17">
       <c r="E12" s="89"/>
@@ -17455,20 +17455,20 @@
       <c r="E19" s="91" t="s">
         <v>413</v>
       </c>
-      <c r="F19" s="215" t="s">
+      <c r="F19" s="218" t="s">
         <v>521</v>
       </c>
-      <c r="G19" s="216"/>
-      <c r="H19" s="216"/>
-      <c r="I19" s="216"/>
-      <c r="J19" s="216"/>
-      <c r="K19" s="216"/>
-      <c r="L19" s="216"/>
-      <c r="M19" s="216"/>
-      <c r="N19" s="216"/>
-      <c r="O19" s="216"/>
-      <c r="P19" s="216"/>
-      <c r="Q19" s="217"/>
+      <c r="G19" s="219"/>
+      <c r="H19" s="219"/>
+      <c r="I19" s="219"/>
+      <c r="J19" s="219"/>
+      <c r="K19" s="219"/>
+      <c r="L19" s="219"/>
+      <c r="M19" s="219"/>
+      <c r="N19" s="219"/>
+      <c r="O19" s="219"/>
+      <c r="P19" s="219"/>
+      <c r="Q19" s="220"/>
     </row>
     <row r="21" spans="2:17">
       <c r="B21" s="90" t="s">
@@ -17537,18 +17537,18 @@
       <c r="I22" s="93" t="s">
         <v>217</v>
       </c>
-      <c r="J22" s="212" t="s">
+      <c r="J22" s="202" t="s">
         <v>524</v>
       </c>
-      <c r="K22" s="212"/>
-      <c r="L22" s="212"/>
-      <c r="M22" s="212"/>
-      <c r="N22" s="212" t="s">
+      <c r="K22" s="202"/>
+      <c r="L22" s="202"/>
+      <c r="M22" s="202"/>
+      <c r="N22" s="202" t="s">
         <v>525</v>
       </c>
-      <c r="O22" s="212"/>
-      <c r="P22" s="212"/>
-      <c r="Q22" s="212"/>
+      <c r="O22" s="202"/>
+      <c r="P22" s="202"/>
+      <c r="Q22" s="202"/>
     </row>
     <row r="23" spans="2:17">
       <c r="E23" s="91" t="s">
@@ -17566,18 +17566,18 @@
       <c r="I23" s="93">
         <v>0</v>
       </c>
-      <c r="J23" s="212" t="s">
+      <c r="J23" s="202" t="s">
         <v>526</v>
       </c>
-      <c r="K23" s="212"/>
-      <c r="L23" s="212"/>
-      <c r="M23" s="212"/>
-      <c r="N23" s="212" t="s">
+      <c r="K23" s="202"/>
+      <c r="L23" s="202"/>
+      <c r="M23" s="202"/>
+      <c r="N23" s="202" t="s">
         <v>410</v>
       </c>
-      <c r="O23" s="212"/>
-      <c r="P23" s="212"/>
-      <c r="Q23" s="212"/>
+      <c r="O23" s="202"/>
+      <c r="P23" s="202"/>
+      <c r="Q23" s="202"/>
     </row>
     <row r="24" spans="2:17">
       <c r="E24" s="91" t="s">
@@ -17595,18 +17595,18 @@
       <c r="I24" s="93" t="s">
         <v>202</v>
       </c>
-      <c r="J24" s="212" t="s">
+      <c r="J24" s="202" t="s">
         <v>202</v>
       </c>
-      <c r="K24" s="212"/>
-      <c r="L24" s="212"/>
-      <c r="M24" s="212"/>
-      <c r="N24" s="212" t="s">
+      <c r="K24" s="202"/>
+      <c r="L24" s="202"/>
+      <c r="M24" s="202"/>
+      <c r="N24" s="202" t="s">
         <v>202</v>
       </c>
-      <c r="O24" s="212"/>
-      <c r="P24" s="212"/>
-      <c r="Q24" s="212"/>
+      <c r="O24" s="202"/>
+      <c r="P24" s="202"/>
+      <c r="Q24" s="202"/>
     </row>
     <row r="25" spans="2:17">
       <c r="E25" s="91" t="s">
@@ -17624,37 +17624,37 @@
       <c r="I25" s="93" t="s">
         <v>203</v>
       </c>
-      <c r="J25" s="212" t="s">
+      <c r="J25" s="202" t="s">
         <v>203</v>
       </c>
-      <c r="K25" s="212"/>
-      <c r="L25" s="212"/>
-      <c r="M25" s="212"/>
-      <c r="N25" s="212" t="s">
+      <c r="K25" s="202"/>
+      <c r="L25" s="202"/>
+      <c r="M25" s="202"/>
+      <c r="N25" s="202" t="s">
         <v>203</v>
       </c>
-      <c r="O25" s="212"/>
-      <c r="P25" s="212"/>
-      <c r="Q25" s="212"/>
+      <c r="O25" s="202"/>
+      <c r="P25" s="202"/>
+      <c r="Q25" s="202"/>
     </row>
     <row r="26" spans="2:17" ht="70.5" customHeight="1">
       <c r="E26" s="91" t="s">
         <v>413</v>
       </c>
-      <c r="F26" s="213" t="s">
+      <c r="F26" s="207" t="s">
         <v>527</v>
       </c>
-      <c r="G26" s="210"/>
-      <c r="H26" s="210"/>
-      <c r="I26" s="210"/>
-      <c r="J26" s="210"/>
-      <c r="K26" s="210"/>
-      <c r="L26" s="210"/>
-      <c r="M26" s="210"/>
-      <c r="N26" s="210"/>
-      <c r="O26" s="210"/>
-      <c r="P26" s="210"/>
-      <c r="Q26" s="214"/>
+      <c r="G26" s="208"/>
+      <c r="H26" s="208"/>
+      <c r="I26" s="208"/>
+      <c r="J26" s="208"/>
+      <c r="K26" s="208"/>
+      <c r="L26" s="208"/>
+      <c r="M26" s="208"/>
+      <c r="N26" s="208"/>
+      <c r="O26" s="208"/>
+      <c r="P26" s="208"/>
+      <c r="Q26" s="209"/>
     </row>
     <row r="28" spans="2:17">
       <c r="B28" s="90" t="s">
@@ -17787,18 +17787,18 @@
       <c r="E33" s="91" t="s">
         <v>413</v>
       </c>
-      <c r="F33" s="213"/>
-      <c r="G33" s="210"/>
-      <c r="H33" s="210"/>
-      <c r="I33" s="210"/>
-      <c r="J33" s="210"/>
-      <c r="K33" s="210"/>
-      <c r="L33" s="210"/>
-      <c r="M33" s="210"/>
-      <c r="N33" s="210"/>
-      <c r="O33" s="210"/>
-      <c r="P33" s="210"/>
-      <c r="Q33" s="214"/>
+      <c r="F33" s="207"/>
+      <c r="G33" s="208"/>
+      <c r="H33" s="208"/>
+      <c r="I33" s="208"/>
+      <c r="J33" s="208"/>
+      <c r="K33" s="208"/>
+      <c r="L33" s="208"/>
+      <c r="M33" s="208"/>
+      <c r="N33" s="208"/>
+      <c r="O33" s="208"/>
+      <c r="P33" s="208"/>
+      <c r="Q33" s="209"/>
     </row>
     <row r="35" spans="2:17">
       <c r="B35" s="90" t="s">
@@ -17931,20 +17931,20 @@
       <c r="E40" s="91" t="s">
         <v>413</v>
       </c>
-      <c r="F40" s="213" t="s">
+      <c r="F40" s="207" t="s">
         <v>536</v>
       </c>
-      <c r="G40" s="210"/>
-      <c r="H40" s="210"/>
-      <c r="I40" s="210"/>
-      <c r="J40" s="210"/>
-      <c r="K40" s="210"/>
-      <c r="L40" s="210"/>
-      <c r="M40" s="210"/>
-      <c r="N40" s="210"/>
-      <c r="O40" s="210"/>
-      <c r="P40" s="210"/>
-      <c r="Q40" s="214"/>
+      <c r="G40" s="208"/>
+      <c r="H40" s="208"/>
+      <c r="I40" s="208"/>
+      <c r="J40" s="208"/>
+      <c r="K40" s="208"/>
+      <c r="L40" s="208"/>
+      <c r="M40" s="208"/>
+      <c r="N40" s="208"/>
+      <c r="O40" s="208"/>
+      <c r="P40" s="208"/>
+      <c r="Q40" s="209"/>
     </row>
     <row r="42" spans="2:17" ht="17.25" customHeight="1">
       <c r="B42" s="97" t="s">
@@ -18021,39 +18021,39 @@
       <c r="E44" s="91" t="s">
         <v>408</v>
       </c>
-      <c r="F44" s="218" t="s">
+      <c r="F44" s="206" t="s">
         <v>231</v>
       </c>
-      <c r="G44" s="218"/>
-      <c r="H44" s="218"/>
-      <c r="I44" s="218" t="s">
+      <c r="G44" s="206"/>
+      <c r="H44" s="206"/>
+      <c r="I44" s="206" t="s">
         <v>232</v>
       </c>
-      <c r="J44" s="218"/>
-      <c r="K44" s="218"/>
-      <c r="L44" s="218" t="s">
+      <c r="J44" s="206"/>
+      <c r="K44" s="206"/>
+      <c r="L44" s="206" t="s">
         <v>233</v>
       </c>
-      <c r="M44" s="218"/>
-      <c r="N44" s="218"/>
-      <c r="O44" s="218"/>
-      <c r="P44" s="218"/>
-      <c r="Q44" s="218"/>
+      <c r="M44" s="206"/>
+      <c r="N44" s="206"/>
+      <c r="O44" s="206"/>
+      <c r="P44" s="206"/>
+      <c r="Q44" s="206"/>
     </row>
     <row r="45" spans="2:17">
       <c r="E45" s="91" t="s">
         <v>409</v>
       </c>
-      <c r="F45" s="212" t="s">
+      <c r="F45" s="202" t="s">
         <v>410</v>
       </c>
-      <c r="G45" s="212"/>
-      <c r="H45" s="212"/>
-      <c r="I45" s="212" t="s">
+      <c r="G45" s="202"/>
+      <c r="H45" s="202"/>
+      <c r="I45" s="202" t="s">
         <v>410</v>
       </c>
-      <c r="J45" s="212"/>
-      <c r="K45" s="212"/>
+      <c r="J45" s="202"/>
+      <c r="K45" s="202"/>
       <c r="L45" s="203" t="s">
         <v>193</v>
       </c>
@@ -18105,20 +18105,20 @@
       <c r="E48" s="91" t="s">
         <v>413</v>
       </c>
-      <c r="F48" s="213" t="s">
+      <c r="F48" s="207" t="s">
         <v>540</v>
       </c>
-      <c r="G48" s="210"/>
-      <c r="H48" s="210"/>
-      <c r="I48" s="210"/>
-      <c r="J48" s="210"/>
-      <c r="K48" s="210"/>
-      <c r="L48" s="210"/>
-      <c r="M48" s="210"/>
-      <c r="N48" s="210"/>
-      <c r="O48" s="210"/>
-      <c r="P48" s="210"/>
-      <c r="Q48" s="214"/>
+      <c r="G48" s="208"/>
+      <c r="H48" s="208"/>
+      <c r="I48" s="208"/>
+      <c r="J48" s="208"/>
+      <c r="K48" s="208"/>
+      <c r="L48" s="208"/>
+      <c r="M48" s="208"/>
+      <c r="N48" s="208"/>
+      <c r="O48" s="208"/>
+      <c r="P48" s="208"/>
+      <c r="Q48" s="209"/>
     </row>
     <row r="50" spans="2:17">
       <c r="B50" s="90" t="s">
@@ -18175,26 +18175,26 @@
       <c r="E51" s="91" t="s">
         <v>408</v>
       </c>
-      <c r="F51" s="218" t="s">
+      <c r="F51" s="206" t="s">
         <v>237</v>
       </c>
-      <c r="G51" s="218"/>
-      <c r="H51" s="219" t="s">
+      <c r="G51" s="206"/>
+      <c r="H51" s="216" t="s">
         <v>238</v>
       </c>
-      <c r="I51" s="220"/>
-      <c r="J51" s="218" t="s">
+      <c r="I51" s="217"/>
+      <c r="J51" s="206" t="s">
         <v>239</v>
       </c>
-      <c r="K51" s="218"/>
-      <c r="L51" s="218"/>
-      <c r="M51" s="218" t="s">
+      <c r="K51" s="206"/>
+      <c r="L51" s="206"/>
+      <c r="M51" s="206" t="s">
         <v>240</v>
       </c>
-      <c r="N51" s="218"/>
-      <c r="O51" s="218"/>
-      <c r="P51" s="218"/>
-      <c r="Q51" s="218"/>
+      <c r="N51" s="206"/>
+      <c r="O51" s="206"/>
+      <c r="P51" s="206"/>
+      <c r="Q51" s="206"/>
     </row>
     <row r="52" spans="2:17">
       <c r="E52" s="91" t="s">
@@ -18208,75 +18208,75 @@
         <v>410</v>
       </c>
       <c r="I52" s="205"/>
-      <c r="J52" s="212" t="s">
+      <c r="J52" s="202" t="s">
         <v>410</v>
       </c>
-      <c r="K52" s="212"/>
-      <c r="L52" s="212"/>
-      <c r="M52" s="212" t="s">
+      <c r="K52" s="202"/>
+      <c r="L52" s="202"/>
+      <c r="M52" s="202" t="s">
         <v>468</v>
       </c>
-      <c r="N52" s="212"/>
-      <c r="O52" s="212"/>
-      <c r="P52" s="212"/>
-      <c r="Q52" s="212"/>
+      <c r="N52" s="202"/>
+      <c r="O52" s="202"/>
+      <c r="P52" s="202"/>
+      <c r="Q52" s="202"/>
     </row>
     <row r="53" spans="2:17">
       <c r="E53" s="91" t="s">
         <v>386</v>
       </c>
-      <c r="F53" s="212" t="s">
+      <c r="F53" s="202" t="s">
         <v>202</v>
       </c>
-      <c r="G53" s="212"/>
-      <c r="H53" s="212"/>
-      <c r="I53" s="212"/>
-      <c r="J53" s="212"/>
-      <c r="K53" s="212"/>
-      <c r="L53" s="212"/>
-      <c r="M53" s="212"/>
-      <c r="N53" s="212"/>
-      <c r="O53" s="212"/>
-      <c r="P53" s="212"/>
-      <c r="Q53" s="212"/>
+      <c r="G53" s="202"/>
+      <c r="H53" s="202"/>
+      <c r="I53" s="202"/>
+      <c r="J53" s="202"/>
+      <c r="K53" s="202"/>
+      <c r="L53" s="202"/>
+      <c r="M53" s="202"/>
+      <c r="N53" s="202"/>
+      <c r="O53" s="202"/>
+      <c r="P53" s="202"/>
+      <c r="Q53" s="202"/>
     </row>
     <row r="54" spans="2:17">
       <c r="E54" s="91" t="s">
         <v>389</v>
       </c>
-      <c r="F54" s="212" t="s">
+      <c r="F54" s="202" t="s">
         <v>203</v>
       </c>
-      <c r="G54" s="212"/>
-      <c r="H54" s="212"/>
-      <c r="I54" s="212"/>
-      <c r="J54" s="212"/>
-      <c r="K54" s="212"/>
-      <c r="L54" s="212"/>
-      <c r="M54" s="212"/>
-      <c r="N54" s="212"/>
-      <c r="O54" s="212"/>
-      <c r="P54" s="212"/>
-      <c r="Q54" s="212"/>
+      <c r="G54" s="202"/>
+      <c r="H54" s="202"/>
+      <c r="I54" s="202"/>
+      <c r="J54" s="202"/>
+      <c r="K54" s="202"/>
+      <c r="L54" s="202"/>
+      <c r="M54" s="202"/>
+      <c r="N54" s="202"/>
+      <c r="O54" s="202"/>
+      <c r="P54" s="202"/>
+      <c r="Q54" s="202"/>
     </row>
     <row r="55" spans="2:17" ht="17.25" customHeight="1">
       <c r="E55" s="91" t="s">
         <v>413</v>
       </c>
-      <c r="F55" s="213" t="s">
+      <c r="F55" s="207" t="s">
         <v>540</v>
       </c>
-      <c r="G55" s="210"/>
-      <c r="H55" s="210"/>
-      <c r="I55" s="210"/>
-      <c r="J55" s="210"/>
-      <c r="K55" s="210"/>
-      <c r="L55" s="210"/>
-      <c r="M55" s="210"/>
-      <c r="N55" s="210"/>
-      <c r="O55" s="210"/>
-      <c r="P55" s="210"/>
-      <c r="Q55" s="214"/>
+      <c r="G55" s="208"/>
+      <c r="H55" s="208"/>
+      <c r="I55" s="208"/>
+      <c r="J55" s="208"/>
+      <c r="K55" s="208"/>
+      <c r="L55" s="208"/>
+      <c r="M55" s="208"/>
+      <c r="N55" s="208"/>
+      <c r="O55" s="208"/>
+      <c r="P55" s="208"/>
+      <c r="Q55" s="209"/>
     </row>
     <row r="57" spans="2:17">
       <c r="B57" s="90" t="s">
@@ -18339,20 +18339,20 @@
       <c r="G58" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="H58" s="224" t="s">
+      <c r="H58" s="210" t="s">
         <v>245</v>
       </c>
-      <c r="I58" s="225"/>
-      <c r="J58" s="225"/>
-      <c r="K58" s="225"/>
-      <c r="L58" s="225"/>
-      <c r="M58" s="226"/>
-      <c r="N58" s="221" t="s">
+      <c r="I58" s="211"/>
+      <c r="J58" s="211"/>
+      <c r="K58" s="211"/>
+      <c r="L58" s="211"/>
+      <c r="M58" s="212"/>
+      <c r="N58" s="213" t="s">
         <v>246</v>
       </c>
-      <c r="O58" s="222"/>
-      <c r="P58" s="222"/>
-      <c r="Q58" s="223"/>
+      <c r="O58" s="214"/>
+      <c r="P58" s="214"/>
+      <c r="Q58" s="215"/>
     </row>
     <row r="59" spans="2:17" ht="17" customHeight="1">
       <c r="E59" s="91" t="s">
@@ -18400,39 +18400,39 @@
       <c r="E61" s="91" t="s">
         <v>389</v>
       </c>
-      <c r="F61" s="212" t="s">
+      <c r="F61" s="202" t="s">
         <v>203</v>
       </c>
-      <c r="G61" s="212"/>
-      <c r="H61" s="212"/>
-      <c r="I61" s="212"/>
-      <c r="J61" s="212"/>
-      <c r="K61" s="212"/>
-      <c r="L61" s="212"/>
-      <c r="M61" s="212"/>
-      <c r="N61" s="212"/>
-      <c r="O61" s="212"/>
-      <c r="P61" s="212"/>
-      <c r="Q61" s="212"/>
+      <c r="G61" s="202"/>
+      <c r="H61" s="202"/>
+      <c r="I61" s="202"/>
+      <c r="J61" s="202"/>
+      <c r="K61" s="202"/>
+      <c r="L61" s="202"/>
+      <c r="M61" s="202"/>
+      <c r="N61" s="202"/>
+      <c r="O61" s="202"/>
+      <c r="P61" s="202"/>
+      <c r="Q61" s="202"/>
     </row>
     <row r="62" spans="2:17" ht="17.25" customHeight="1">
       <c r="E62" s="91" t="s">
         <v>413</v>
       </c>
-      <c r="F62" s="213" t="s">
+      <c r="F62" s="207" t="s">
         <v>540</v>
       </c>
-      <c r="G62" s="210"/>
-      <c r="H62" s="210"/>
-      <c r="I62" s="210"/>
-      <c r="J62" s="210"/>
-      <c r="K62" s="210"/>
-      <c r="L62" s="210"/>
-      <c r="M62" s="210"/>
-      <c r="N62" s="210"/>
-      <c r="O62" s="210"/>
-      <c r="P62" s="210"/>
-      <c r="Q62" s="214"/>
+      <c r="G62" s="208"/>
+      <c r="H62" s="208"/>
+      <c r="I62" s="208"/>
+      <c r="J62" s="208"/>
+      <c r="K62" s="208"/>
+      <c r="L62" s="208"/>
+      <c r="M62" s="208"/>
+      <c r="N62" s="208"/>
+      <c r="O62" s="208"/>
+      <c r="P62" s="208"/>
+      <c r="Q62" s="209"/>
     </row>
     <row r="64" spans="2:17">
       <c r="B64" s="90" t="s">
@@ -18489,100 +18489,100 @@
       <c r="E65" s="91" t="s">
         <v>408</v>
       </c>
-      <c r="F65" s="218" t="s">
+      <c r="F65" s="206" t="s">
         <v>250</v>
       </c>
-      <c r="G65" s="218"/>
-      <c r="H65" s="218"/>
-      <c r="I65" s="218"/>
-      <c r="J65" s="218"/>
-      <c r="K65" s="218"/>
-      <c r="L65" s="218"/>
-      <c r="M65" s="218"/>
-      <c r="N65" s="221" t="s">
+      <c r="G65" s="206"/>
+      <c r="H65" s="206"/>
+      <c r="I65" s="206"/>
+      <c r="J65" s="206"/>
+      <c r="K65" s="206"/>
+      <c r="L65" s="206"/>
+      <c r="M65" s="206"/>
+      <c r="N65" s="213" t="s">
         <v>251</v>
       </c>
-      <c r="O65" s="222"/>
-      <c r="P65" s="222"/>
-      <c r="Q65" s="223"/>
+      <c r="O65" s="214"/>
+      <c r="P65" s="214"/>
+      <c r="Q65" s="215"/>
     </row>
     <row r="66" spans="2:17">
       <c r="E66" s="91" t="s">
         <v>409</v>
       </c>
-      <c r="F66" s="212" t="s">
+      <c r="F66" s="202" t="s">
         <v>410</v>
       </c>
-      <c r="G66" s="212"/>
-      <c r="H66" s="212"/>
-      <c r="I66" s="212"/>
-      <c r="J66" s="212"/>
-      <c r="K66" s="212"/>
-      <c r="L66" s="212"/>
-      <c r="M66" s="212"/>
-      <c r="N66" s="212" t="s">
+      <c r="G66" s="202"/>
+      <c r="H66" s="202"/>
+      <c r="I66" s="202"/>
+      <c r="J66" s="202"/>
+      <c r="K66" s="202"/>
+      <c r="L66" s="202"/>
+      <c r="M66" s="202"/>
+      <c r="N66" s="202" t="s">
         <v>549</v>
       </c>
-      <c r="O66" s="212"/>
-      <c r="P66" s="212"/>
-      <c r="Q66" s="212"/>
+      <c r="O66" s="202"/>
+      <c r="P66" s="202"/>
+      <c r="Q66" s="202"/>
     </row>
     <row r="67" spans="2:17">
       <c r="E67" s="91" t="s">
         <v>386</v>
       </c>
-      <c r="F67" s="212" t="s">
+      <c r="F67" s="202" t="s">
         <v>202</v>
       </c>
-      <c r="G67" s="212"/>
-      <c r="H67" s="212"/>
-      <c r="I67" s="212"/>
-      <c r="J67" s="212"/>
-      <c r="K67" s="212"/>
-      <c r="L67" s="212"/>
-      <c r="M67" s="212"/>
-      <c r="N67" s="212"/>
-      <c r="O67" s="212"/>
-      <c r="P67" s="212"/>
-      <c r="Q67" s="212"/>
+      <c r="G67" s="202"/>
+      <c r="H67" s="202"/>
+      <c r="I67" s="202"/>
+      <c r="J67" s="202"/>
+      <c r="K67" s="202"/>
+      <c r="L67" s="202"/>
+      <c r="M67" s="202"/>
+      <c r="N67" s="202"/>
+      <c r="O67" s="202"/>
+      <c r="P67" s="202"/>
+      <c r="Q67" s="202"/>
     </row>
     <row r="68" spans="2:17">
       <c r="E68" s="91" t="s">
         <v>389</v>
       </c>
-      <c r="F68" s="212" t="s">
+      <c r="F68" s="202" t="s">
         <v>203</v>
       </c>
-      <c r="G68" s="212"/>
-      <c r="H68" s="212"/>
-      <c r="I68" s="212"/>
-      <c r="J68" s="212"/>
-      <c r="K68" s="212"/>
-      <c r="L68" s="212"/>
-      <c r="M68" s="212"/>
-      <c r="N68" s="212"/>
-      <c r="O68" s="212"/>
-      <c r="P68" s="212"/>
-      <c r="Q68" s="212"/>
+      <c r="G68" s="202"/>
+      <c r="H68" s="202"/>
+      <c r="I68" s="202"/>
+      <c r="J68" s="202"/>
+      <c r="K68" s="202"/>
+      <c r="L68" s="202"/>
+      <c r="M68" s="202"/>
+      <c r="N68" s="202"/>
+      <c r="O68" s="202"/>
+      <c r="P68" s="202"/>
+      <c r="Q68" s="202"/>
     </row>
     <row r="69" spans="2:17" ht="17.25" customHeight="1">
       <c r="E69" s="91" t="s">
         <v>413</v>
       </c>
-      <c r="F69" s="213" t="s">
+      <c r="F69" s="207" t="s">
         <v>540</v>
       </c>
-      <c r="G69" s="210"/>
-      <c r="H69" s="210"/>
-      <c r="I69" s="210"/>
-      <c r="J69" s="210"/>
-      <c r="K69" s="210"/>
-      <c r="L69" s="210"/>
-      <c r="M69" s="210"/>
-      <c r="N69" s="210"/>
-      <c r="O69" s="210"/>
-      <c r="P69" s="210"/>
-      <c r="Q69" s="214"/>
+      <c r="G69" s="208"/>
+      <c r="H69" s="208"/>
+      <c r="I69" s="208"/>
+      <c r="J69" s="208"/>
+      <c r="K69" s="208"/>
+      <c r="L69" s="208"/>
+      <c r="M69" s="208"/>
+      <c r="N69" s="208"/>
+      <c r="O69" s="208"/>
+      <c r="P69" s="208"/>
+      <c r="Q69" s="209"/>
     </row>
     <row r="71" spans="2:17">
       <c r="B71" s="90" t="s">
@@ -18721,58 +18721,58 @@
       <c r="E74" s="91" t="s">
         <v>386</v>
       </c>
-      <c r="F74" s="212" t="s">
+      <c r="F74" s="202" t="s">
         <v>202</v>
       </c>
-      <c r="G74" s="212"/>
-      <c r="H74" s="212"/>
-      <c r="I74" s="212"/>
-      <c r="J74" s="212"/>
-      <c r="K74" s="212"/>
-      <c r="L74" s="212"/>
-      <c r="M74" s="212"/>
-      <c r="N74" s="212"/>
-      <c r="O74" s="212"/>
-      <c r="P74" s="212"/>
-      <c r="Q74" s="212"/>
+      <c r="G74" s="202"/>
+      <c r="H74" s="202"/>
+      <c r="I74" s="202"/>
+      <c r="J74" s="202"/>
+      <c r="K74" s="202"/>
+      <c r="L74" s="202"/>
+      <c r="M74" s="202"/>
+      <c r="N74" s="202"/>
+      <c r="O74" s="202"/>
+      <c r="P74" s="202"/>
+      <c r="Q74" s="202"/>
     </row>
     <row r="75" spans="2:17">
       <c r="E75" s="91" t="s">
         <v>389</v>
       </c>
-      <c r="F75" s="212" t="s">
+      <c r="F75" s="202" t="s">
         <v>203</v>
       </c>
-      <c r="G75" s="212"/>
-      <c r="H75" s="212"/>
-      <c r="I75" s="212"/>
-      <c r="J75" s="212"/>
-      <c r="K75" s="212"/>
-      <c r="L75" s="212"/>
-      <c r="M75" s="212"/>
-      <c r="N75" s="212"/>
-      <c r="O75" s="212"/>
-      <c r="P75" s="212"/>
-      <c r="Q75" s="212"/>
+      <c r="G75" s="202"/>
+      <c r="H75" s="202"/>
+      <c r="I75" s="202"/>
+      <c r="J75" s="202"/>
+      <c r="K75" s="202"/>
+      <c r="L75" s="202"/>
+      <c r="M75" s="202"/>
+      <c r="N75" s="202"/>
+      <c r="O75" s="202"/>
+      <c r="P75" s="202"/>
+      <c r="Q75" s="202"/>
     </row>
     <row r="76" spans="2:17" ht="17.25" customHeight="1">
       <c r="E76" s="91" t="s">
         <v>413</v>
       </c>
-      <c r="F76" s="213" t="s">
+      <c r="F76" s="207" t="s">
         <v>540</v>
       </c>
-      <c r="G76" s="210"/>
-      <c r="H76" s="210"/>
-      <c r="I76" s="210"/>
-      <c r="J76" s="210"/>
-      <c r="K76" s="210"/>
-      <c r="L76" s="210"/>
-      <c r="M76" s="210"/>
-      <c r="N76" s="210"/>
-      <c r="O76" s="210"/>
-      <c r="P76" s="210"/>
-      <c r="Q76" s="214"/>
+      <c r="G76" s="208"/>
+      <c r="H76" s="208"/>
+      <c r="I76" s="208"/>
+      <c r="J76" s="208"/>
+      <c r="K76" s="208"/>
+      <c r="L76" s="208"/>
+      <c r="M76" s="208"/>
+      <c r="N76" s="208"/>
+      <c r="O76" s="208"/>
+      <c r="P76" s="208"/>
+      <c r="Q76" s="209"/>
     </row>
     <row r="77" spans="2:17" ht="17.25" customHeight="1">
       <c r="F77" s="89"/>
@@ -18909,60 +18909,60 @@
       <c r="E81" s="91" t="s">
         <v>386</v>
       </c>
-      <c r="F81" s="212" t="s">
+      <c r="F81" s="202" t="s">
         <v>202</v>
       </c>
-      <c r="G81" s="212"/>
-      <c r="H81" s="212"/>
-      <c r="I81" s="212"/>
-      <c r="J81" s="212"/>
-      <c r="K81" s="212"/>
-      <c r="L81" s="212"/>
-      <c r="M81" s="212"/>
-      <c r="N81" s="212"/>
-      <c r="O81" s="212"/>
-      <c r="P81" s="212"/>
-      <c r="Q81" s="212"/>
+      <c r="G81" s="202"/>
+      <c r="H81" s="202"/>
+      <c r="I81" s="202"/>
+      <c r="J81" s="202"/>
+      <c r="K81" s="202"/>
+      <c r="L81" s="202"/>
+      <c r="M81" s="202"/>
+      <c r="N81" s="202"/>
+      <c r="O81" s="202"/>
+      <c r="P81" s="202"/>
+      <c r="Q81" s="202"/>
     </row>
     <row r="82" spans="2:17">
       <c r="B82" s="87"/>
       <c r="E82" s="91" t="s">
         <v>389</v>
       </c>
-      <c r="F82" s="212" t="s">
+      <c r="F82" s="202" t="s">
         <v>203</v>
       </c>
-      <c r="G82" s="212"/>
-      <c r="H82" s="212"/>
-      <c r="I82" s="212"/>
-      <c r="J82" s="212"/>
-      <c r="K82" s="212"/>
-      <c r="L82" s="212"/>
-      <c r="M82" s="212"/>
-      <c r="N82" s="212"/>
-      <c r="O82" s="212"/>
-      <c r="P82" s="212"/>
-      <c r="Q82" s="212"/>
+      <c r="G82" s="202"/>
+      <c r="H82" s="202"/>
+      <c r="I82" s="202"/>
+      <c r="J82" s="202"/>
+      <c r="K82" s="202"/>
+      <c r="L82" s="202"/>
+      <c r="M82" s="202"/>
+      <c r="N82" s="202"/>
+      <c r="O82" s="202"/>
+      <c r="P82" s="202"/>
+      <c r="Q82" s="202"/>
     </row>
     <row r="83" spans="2:17" ht="17.25" customHeight="1">
       <c r="B83" s="87"/>
       <c r="E83" s="91" t="s">
         <v>413</v>
       </c>
-      <c r="F83" s="213" t="s">
+      <c r="F83" s="207" t="s">
         <v>540</v>
       </c>
-      <c r="G83" s="210"/>
-      <c r="H83" s="210"/>
-      <c r="I83" s="210"/>
-      <c r="J83" s="210"/>
-      <c r="K83" s="210"/>
-      <c r="L83" s="210"/>
-      <c r="M83" s="210"/>
-      <c r="N83" s="210"/>
-      <c r="O83" s="210"/>
-      <c r="P83" s="210"/>
-      <c r="Q83" s="214"/>
+      <c r="G83" s="208"/>
+      <c r="H83" s="208"/>
+      <c r="I83" s="208"/>
+      <c r="J83" s="208"/>
+      <c r="K83" s="208"/>
+      <c r="L83" s="208"/>
+      <c r="M83" s="208"/>
+      <c r="N83" s="208"/>
+      <c r="O83" s="208"/>
+      <c r="P83" s="208"/>
+      <c r="Q83" s="209"/>
     </row>
     <row r="84" spans="2:17" ht="17.25" customHeight="1">
       <c r="B84" s="87"/>
@@ -19043,17 +19043,17 @@
       <c r="H86" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="I86" s="224" t="s">
+      <c r="I86" s="210" t="s">
         <v>261</v>
       </c>
-      <c r="J86" s="225"/>
-      <c r="K86" s="225"/>
-      <c r="L86" s="225"/>
-      <c r="M86" s="225"/>
-      <c r="N86" s="225"/>
-      <c r="O86" s="225"/>
-      <c r="P86" s="225"/>
-      <c r="Q86" s="226"/>
+      <c r="J86" s="211"/>
+      <c r="K86" s="211"/>
+      <c r="L86" s="211"/>
+      <c r="M86" s="211"/>
+      <c r="N86" s="211"/>
+      <c r="O86" s="211"/>
+      <c r="P86" s="211"/>
+      <c r="Q86" s="212"/>
     </row>
     <row r="87" spans="2:17">
       <c r="B87" s="87"/>
@@ -19080,60 +19080,60 @@
       <c r="E88" s="91" t="s">
         <v>386</v>
       </c>
-      <c r="F88" s="212" t="s">
+      <c r="F88" s="202" t="s">
         <v>202</v>
       </c>
-      <c r="G88" s="212"/>
-      <c r="H88" s="212"/>
-      <c r="I88" s="212"/>
-      <c r="J88" s="212"/>
-      <c r="K88" s="212"/>
-      <c r="L88" s="212"/>
-      <c r="M88" s="212"/>
-      <c r="N88" s="212"/>
-      <c r="O88" s="212"/>
-      <c r="P88" s="212"/>
-      <c r="Q88" s="212"/>
+      <c r="G88" s="202"/>
+      <c r="H88" s="202"/>
+      <c r="I88" s="202"/>
+      <c r="J88" s="202"/>
+      <c r="K88" s="202"/>
+      <c r="L88" s="202"/>
+      <c r="M88" s="202"/>
+      <c r="N88" s="202"/>
+      <c r="O88" s="202"/>
+      <c r="P88" s="202"/>
+      <c r="Q88" s="202"/>
     </row>
     <row r="89" spans="2:17">
       <c r="B89" s="87"/>
       <c r="E89" s="91" t="s">
         <v>389</v>
       </c>
-      <c r="F89" s="212" t="s">
+      <c r="F89" s="202" t="s">
         <v>203</v>
       </c>
-      <c r="G89" s="212"/>
-      <c r="H89" s="212"/>
-      <c r="I89" s="212"/>
-      <c r="J89" s="212"/>
-      <c r="K89" s="212"/>
-      <c r="L89" s="212"/>
-      <c r="M89" s="212"/>
-      <c r="N89" s="212"/>
-      <c r="O89" s="212"/>
-      <c r="P89" s="212"/>
-      <c r="Q89" s="212"/>
+      <c r="G89" s="202"/>
+      <c r="H89" s="202"/>
+      <c r="I89" s="202"/>
+      <c r="J89" s="202"/>
+      <c r="K89" s="202"/>
+      <c r="L89" s="202"/>
+      <c r="M89" s="202"/>
+      <c r="N89" s="202"/>
+      <c r="O89" s="202"/>
+      <c r="P89" s="202"/>
+      <c r="Q89" s="202"/>
     </row>
     <row r="90" spans="2:17" ht="17.25" customHeight="1">
       <c r="B90" s="87"/>
       <c r="E90" s="91" t="s">
         <v>413</v>
       </c>
-      <c r="F90" s="213" t="s">
+      <c r="F90" s="207" t="s">
         <v>540</v>
       </c>
-      <c r="G90" s="210"/>
-      <c r="H90" s="210"/>
-      <c r="I90" s="210"/>
-      <c r="J90" s="210"/>
-      <c r="K90" s="210"/>
-      <c r="L90" s="210"/>
-      <c r="M90" s="210"/>
-      <c r="N90" s="210"/>
-      <c r="O90" s="210"/>
-      <c r="P90" s="210"/>
-      <c r="Q90" s="214"/>
+      <c r="G90" s="208"/>
+      <c r="H90" s="208"/>
+      <c r="I90" s="208"/>
+      <c r="J90" s="208"/>
+      <c r="K90" s="208"/>
+      <c r="L90" s="208"/>
+      <c r="M90" s="208"/>
+      <c r="N90" s="208"/>
+      <c r="O90" s="208"/>
+      <c r="P90" s="208"/>
+      <c r="Q90" s="209"/>
     </row>
     <row r="92" spans="2:17">
       <c r="B92" s="90" t="s">
@@ -19211,13 +19211,13 @@
       <c r="L93" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="M93" s="224" t="s">
+      <c r="M93" s="210" t="s">
         <v>264</v>
       </c>
-      <c r="N93" s="225"/>
-      <c r="O93" s="225"/>
-      <c r="P93" s="225"/>
-      <c r="Q93" s="226"/>
+      <c r="N93" s="211"/>
+      <c r="O93" s="211"/>
+      <c r="P93" s="211"/>
+      <c r="Q93" s="212"/>
     </row>
     <row r="94" spans="2:17">
       <c r="B94" s="87"/>
@@ -19240,60 +19240,60 @@
       <c r="E95" s="91" t="s">
         <v>386</v>
       </c>
-      <c r="F95" s="212" t="s">
+      <c r="F95" s="202" t="s">
         <v>202</v>
       </c>
-      <c r="G95" s="212"/>
-      <c r="H95" s="212"/>
-      <c r="I95" s="212"/>
-      <c r="J95" s="212"/>
-      <c r="K95" s="212"/>
-      <c r="L95" s="212"/>
-      <c r="M95" s="212"/>
-      <c r="N95" s="212"/>
-      <c r="O95" s="212"/>
-      <c r="P95" s="212"/>
-      <c r="Q95" s="212"/>
+      <c r="G95" s="202"/>
+      <c r="H95" s="202"/>
+      <c r="I95" s="202"/>
+      <c r="J95" s="202"/>
+      <c r="K95" s="202"/>
+      <c r="L95" s="202"/>
+      <c r="M95" s="202"/>
+      <c r="N95" s="202"/>
+      <c r="O95" s="202"/>
+      <c r="P95" s="202"/>
+      <c r="Q95" s="202"/>
     </row>
     <row r="96" spans="2:17">
       <c r="B96" s="87"/>
       <c r="E96" s="91" t="s">
         <v>389</v>
       </c>
-      <c r="F96" s="212" t="s">
+      <c r="F96" s="202" t="s">
         <v>203</v>
       </c>
-      <c r="G96" s="212"/>
-      <c r="H96" s="212"/>
-      <c r="I96" s="212"/>
-      <c r="J96" s="212"/>
-      <c r="K96" s="212"/>
-      <c r="L96" s="212"/>
-      <c r="M96" s="212"/>
-      <c r="N96" s="212"/>
-      <c r="O96" s="212"/>
-      <c r="P96" s="212"/>
-      <c r="Q96" s="212"/>
+      <c r="G96" s="202"/>
+      <c r="H96" s="202"/>
+      <c r="I96" s="202"/>
+      <c r="J96" s="202"/>
+      <c r="K96" s="202"/>
+      <c r="L96" s="202"/>
+      <c r="M96" s="202"/>
+      <c r="N96" s="202"/>
+      <c r="O96" s="202"/>
+      <c r="P96" s="202"/>
+      <c r="Q96" s="202"/>
     </row>
     <row r="97" spans="2:17" ht="17.25" customHeight="1">
       <c r="B97" s="87"/>
       <c r="E97" s="91" t="s">
         <v>413</v>
       </c>
-      <c r="F97" s="213" t="s">
+      <c r="F97" s="207" t="s">
         <v>540</v>
       </c>
-      <c r="G97" s="210"/>
-      <c r="H97" s="210"/>
-      <c r="I97" s="210"/>
-      <c r="J97" s="210"/>
-      <c r="K97" s="210"/>
-      <c r="L97" s="210"/>
-      <c r="M97" s="210"/>
-      <c r="N97" s="210"/>
-      <c r="O97" s="210"/>
-      <c r="P97" s="210"/>
-      <c r="Q97" s="214"/>
+      <c r="G97" s="208"/>
+      <c r="H97" s="208"/>
+      <c r="I97" s="208"/>
+      <c r="J97" s="208"/>
+      <c r="K97" s="208"/>
+      <c r="L97" s="208"/>
+      <c r="M97" s="208"/>
+      <c r="N97" s="208"/>
+      <c r="O97" s="208"/>
+      <c r="P97" s="208"/>
+      <c r="Q97" s="209"/>
     </row>
     <row r="98" spans="2:17" ht="17.25" customHeight="1">
       <c r="B98" s="87"/>
@@ -19377,16 +19377,16 @@
       <c r="I100" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="J100" s="218" t="s">
+      <c r="J100" s="206" t="s">
         <v>268</v>
       </c>
-      <c r="K100" s="218"/>
-      <c r="L100" s="218"/>
-      <c r="M100" s="218"/>
-      <c r="N100" s="218"/>
-      <c r="O100" s="218"/>
-      <c r="P100" s="218"/>
-      <c r="Q100" s="218"/>
+      <c r="K100" s="206"/>
+      <c r="L100" s="206"/>
+      <c r="M100" s="206"/>
+      <c r="N100" s="206"/>
+      <c r="O100" s="206"/>
+      <c r="P100" s="206"/>
+      <c r="Q100" s="206"/>
     </row>
     <row r="101" spans="2:17">
       <c r="E101" s="91" t="s">
@@ -19416,58 +19416,58 @@
       <c r="E102" s="91" t="s">
         <v>386</v>
       </c>
-      <c r="F102" s="212" t="s">
+      <c r="F102" s="202" t="s">
         <v>202</v>
       </c>
-      <c r="G102" s="212"/>
-      <c r="H102" s="212"/>
-      <c r="I102" s="212"/>
-      <c r="J102" s="212"/>
-      <c r="K102" s="212"/>
-      <c r="L102" s="212"/>
-      <c r="M102" s="212"/>
-      <c r="N102" s="212"/>
-      <c r="O102" s="212"/>
-      <c r="P102" s="212"/>
-      <c r="Q102" s="212"/>
+      <c r="G102" s="202"/>
+      <c r="H102" s="202"/>
+      <c r="I102" s="202"/>
+      <c r="J102" s="202"/>
+      <c r="K102" s="202"/>
+      <c r="L102" s="202"/>
+      <c r="M102" s="202"/>
+      <c r="N102" s="202"/>
+      <c r="O102" s="202"/>
+      <c r="P102" s="202"/>
+      <c r="Q102" s="202"/>
     </row>
     <row r="103" spans="2:17">
       <c r="E103" s="91" t="s">
         <v>389</v>
       </c>
-      <c r="F103" s="212" t="s">
+      <c r="F103" s="202" t="s">
         <v>203</v>
       </c>
-      <c r="G103" s="212"/>
-      <c r="H103" s="212"/>
-      <c r="I103" s="212"/>
-      <c r="J103" s="212"/>
-      <c r="K103" s="212"/>
-      <c r="L103" s="212"/>
-      <c r="M103" s="212"/>
-      <c r="N103" s="212"/>
-      <c r="O103" s="212"/>
-      <c r="P103" s="212"/>
-      <c r="Q103" s="212"/>
+      <c r="G103" s="202"/>
+      <c r="H103" s="202"/>
+      <c r="I103" s="202"/>
+      <c r="J103" s="202"/>
+      <c r="K103" s="202"/>
+      <c r="L103" s="202"/>
+      <c r="M103" s="202"/>
+      <c r="N103" s="202"/>
+      <c r="O103" s="202"/>
+      <c r="P103" s="202"/>
+      <c r="Q103" s="202"/>
     </row>
     <row r="104" spans="2:17" ht="27" customHeight="1">
       <c r="E104" s="91" t="s">
         <v>413</v>
       </c>
-      <c r="F104" s="227" t="s">
+      <c r="F104" s="201" t="s">
         <v>559</v>
       </c>
-      <c r="G104" s="227"/>
-      <c r="H104" s="227"/>
-      <c r="I104" s="227"/>
-      <c r="J104" s="227"/>
-      <c r="K104" s="227"/>
-      <c r="L104" s="227"/>
-      <c r="M104" s="227"/>
-      <c r="N104" s="227"/>
-      <c r="O104" s="227"/>
-      <c r="P104" s="227"/>
-      <c r="Q104" s="227"/>
+      <c r="G104" s="201"/>
+      <c r="H104" s="201"/>
+      <c r="I104" s="201"/>
+      <c r="J104" s="201"/>
+      <c r="K104" s="201"/>
+      <c r="L104" s="201"/>
+      <c r="M104" s="201"/>
+      <c r="N104" s="201"/>
+      <c r="O104" s="201"/>
+      <c r="P104" s="201"/>
+      <c r="Q104" s="201"/>
     </row>
     <row r="106" spans="2:17">
       <c r="B106" s="90" t="s">
@@ -19536,16 +19536,16 @@
       <c r="I107" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="J107" s="218" t="s">
+      <c r="J107" s="206" t="s">
         <v>268</v>
       </c>
-      <c r="K107" s="218"/>
-      <c r="L107" s="218"/>
-      <c r="M107" s="218"/>
-      <c r="N107" s="218"/>
-      <c r="O107" s="218"/>
-      <c r="P107" s="218"/>
-      <c r="Q107" s="218"/>
+      <c r="K107" s="206"/>
+      <c r="L107" s="206"/>
+      <c r="M107" s="206"/>
+      <c r="N107" s="206"/>
+      <c r="O107" s="206"/>
+      <c r="P107" s="206"/>
+      <c r="Q107" s="206"/>
     </row>
     <row r="108" spans="2:17">
       <c r="E108" s="91" t="s">
@@ -19575,59 +19575,59 @@
       <c r="E109" s="91" t="s">
         <v>386</v>
       </c>
-      <c r="F109" s="212" t="s">
+      <c r="F109" s="202" t="s">
         <v>202</v>
       </c>
-      <c r="G109" s="212"/>
-      <c r="H109" s="212"/>
-      <c r="I109" s="212"/>
-      <c r="J109" s="212"/>
-      <c r="K109" s="212"/>
-      <c r="L109" s="212"/>
-      <c r="M109" s="212"/>
-      <c r="N109" s="212"/>
-      <c r="O109" s="212"/>
-      <c r="P109" s="212"/>
-      <c r="Q109" s="212"/>
+      <c r="G109" s="202"/>
+      <c r="H109" s="202"/>
+      <c r="I109" s="202"/>
+      <c r="J109" s="202"/>
+      <c r="K109" s="202"/>
+      <c r="L109" s="202"/>
+      <c r="M109" s="202"/>
+      <c r="N109" s="202"/>
+      <c r="O109" s="202"/>
+      <c r="P109" s="202"/>
+      <c r="Q109" s="202"/>
     </row>
     <row r="110" spans="2:17">
       <c r="E110" s="91" t="s">
         <v>389</v>
       </c>
-      <c r="F110" s="212" t="s">
+      <c r="F110" s="202" t="s">
         <v>203</v>
       </c>
-      <c r="G110" s="212"/>
-      <c r="H110" s="212"/>
-      <c r="I110" s="212"/>
-      <c r="J110" s="212"/>
-      <c r="K110" s="212"/>
-      <c r="L110" s="212"/>
-      <c r="M110" s="212"/>
-      <c r="N110" s="212"/>
-      <c r="O110" s="212"/>
-      <c r="P110" s="212"/>
-      <c r="Q110" s="212"/>
+      <c r="G110" s="202"/>
+      <c r="H110" s="202"/>
+      <c r="I110" s="202"/>
+      <c r="J110" s="202"/>
+      <c r="K110" s="202"/>
+      <c r="L110" s="202"/>
+      <c r="M110" s="202"/>
+      <c r="N110" s="202"/>
+      <c r="O110" s="202"/>
+      <c r="P110" s="202"/>
+      <c r="Q110" s="202"/>
     </row>
     <row r="111" spans="2:17">
       <c r="B111" s="87"/>
       <c r="E111" s="91" t="s">
         <v>413</v>
       </c>
-      <c r="F111" s="227" t="s">
+      <c r="F111" s="201" t="s">
         <v>561</v>
       </c>
-      <c r="G111" s="227"/>
-      <c r="H111" s="227"/>
-      <c r="I111" s="227"/>
-      <c r="J111" s="227"/>
-      <c r="K111" s="227"/>
-      <c r="L111" s="227"/>
-      <c r="M111" s="227"/>
-      <c r="N111" s="227"/>
-      <c r="O111" s="227"/>
-      <c r="P111" s="227"/>
-      <c r="Q111" s="227"/>
+      <c r="G111" s="201"/>
+      <c r="H111" s="201"/>
+      <c r="I111" s="201"/>
+      <c r="J111" s="201"/>
+      <c r="K111" s="201"/>
+      <c r="L111" s="201"/>
+      <c r="M111" s="201"/>
+      <c r="N111" s="201"/>
+      <c r="O111" s="201"/>
+      <c r="P111" s="201"/>
+      <c r="Q111" s="201"/>
     </row>
     <row r="113" spans="2:17">
       <c r="B113" s="90" t="s">
@@ -19696,16 +19696,16 @@
       <c r="I114" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="J114" s="218" t="s">
+      <c r="J114" s="206" t="s">
         <v>268</v>
       </c>
-      <c r="K114" s="218"/>
-      <c r="L114" s="218"/>
-      <c r="M114" s="218"/>
-      <c r="N114" s="218"/>
-      <c r="O114" s="218"/>
-      <c r="P114" s="218"/>
-      <c r="Q114" s="218"/>
+      <c r="K114" s="206"/>
+      <c r="L114" s="206"/>
+      <c r="M114" s="206"/>
+      <c r="N114" s="206"/>
+      <c r="O114" s="206"/>
+      <c r="P114" s="206"/>
+      <c r="Q114" s="206"/>
     </row>
     <row r="115" spans="2:17">
       <c r="E115" s="91" t="s">
@@ -19735,58 +19735,58 @@
       <c r="E116" s="91" t="s">
         <v>386</v>
       </c>
-      <c r="F116" s="212" t="s">
+      <c r="F116" s="202" t="s">
         <v>202</v>
       </c>
-      <c r="G116" s="212"/>
-      <c r="H116" s="212"/>
-      <c r="I116" s="212"/>
-      <c r="J116" s="212"/>
-      <c r="K116" s="212"/>
-      <c r="L116" s="212"/>
-      <c r="M116" s="212"/>
-      <c r="N116" s="212"/>
-      <c r="O116" s="212"/>
-      <c r="P116" s="212"/>
-      <c r="Q116" s="212"/>
+      <c r="G116" s="202"/>
+      <c r="H116" s="202"/>
+      <c r="I116" s="202"/>
+      <c r="J116" s="202"/>
+      <c r="K116" s="202"/>
+      <c r="L116" s="202"/>
+      <c r="M116" s="202"/>
+      <c r="N116" s="202"/>
+      <c r="O116" s="202"/>
+      <c r="P116" s="202"/>
+      <c r="Q116" s="202"/>
     </row>
     <row r="117" spans="2:17">
       <c r="E117" s="91" t="s">
         <v>389</v>
       </c>
-      <c r="F117" s="212" t="s">
+      <c r="F117" s="202" t="s">
         <v>203</v>
       </c>
-      <c r="G117" s="212"/>
-      <c r="H117" s="212"/>
-      <c r="I117" s="212"/>
-      <c r="J117" s="212"/>
-      <c r="K117" s="212"/>
-      <c r="L117" s="212"/>
-      <c r="M117" s="212"/>
-      <c r="N117" s="212"/>
-      <c r="O117" s="212"/>
-      <c r="P117" s="212"/>
-      <c r="Q117" s="212"/>
+      <c r="G117" s="202"/>
+      <c r="H117" s="202"/>
+      <c r="I117" s="202"/>
+      <c r="J117" s="202"/>
+      <c r="K117" s="202"/>
+      <c r="L117" s="202"/>
+      <c r="M117" s="202"/>
+      <c r="N117" s="202"/>
+      <c r="O117" s="202"/>
+      <c r="P117" s="202"/>
+      <c r="Q117" s="202"/>
     </row>
     <row r="118" spans="2:17" ht="17.25" customHeight="1">
       <c r="E118" s="91" t="s">
         <v>413</v>
       </c>
-      <c r="F118" s="227" t="s">
+      <c r="F118" s="201" t="s">
         <v>561</v>
       </c>
-      <c r="G118" s="227"/>
-      <c r="H118" s="227"/>
-      <c r="I118" s="227"/>
-      <c r="J118" s="227"/>
-      <c r="K118" s="227"/>
-      <c r="L118" s="227"/>
-      <c r="M118" s="227"/>
-      <c r="N118" s="227"/>
-      <c r="O118" s="227"/>
-      <c r="P118" s="227"/>
-      <c r="Q118" s="227"/>
+      <c r="G118" s="201"/>
+      <c r="H118" s="201"/>
+      <c r="I118" s="201"/>
+      <c r="J118" s="201"/>
+      <c r="K118" s="201"/>
+      <c r="L118" s="201"/>
+      <c r="M118" s="201"/>
+      <c r="N118" s="201"/>
+      <c r="O118" s="201"/>
+      <c r="P118" s="201"/>
+      <c r="Q118" s="201"/>
     </row>
     <row r="120" spans="2:17">
       <c r="B120" s="90" t="s">
@@ -19849,18 +19849,18 @@
       <c r="G121" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="H121" s="218" t="s">
+      <c r="H121" s="206" t="s">
         <v>278</v>
       </c>
-      <c r="I121" s="218"/>
-      <c r="J121" s="218"/>
-      <c r="K121" s="218"/>
-      <c r="L121" s="218"/>
-      <c r="M121" s="218"/>
-      <c r="N121" s="218"/>
-      <c r="O121" s="218"/>
-      <c r="P121" s="218"/>
-      <c r="Q121" s="218"/>
+      <c r="I121" s="206"/>
+      <c r="J121" s="206"/>
+      <c r="K121" s="206"/>
+      <c r="L121" s="206"/>
+      <c r="M121" s="206"/>
+      <c r="N121" s="206"/>
+      <c r="O121" s="206"/>
+      <c r="P121" s="206"/>
+      <c r="Q121" s="206"/>
     </row>
     <row r="122" spans="2:17">
       <c r="B122" s="87"/>
@@ -19888,60 +19888,60 @@
       <c r="E123" s="91" t="s">
         <v>386</v>
       </c>
-      <c r="F123" s="212" t="s">
+      <c r="F123" s="202" t="s">
         <v>202</v>
       </c>
-      <c r="G123" s="212"/>
-      <c r="H123" s="212"/>
-      <c r="I123" s="212"/>
-      <c r="J123" s="212"/>
-      <c r="K123" s="212"/>
-      <c r="L123" s="212"/>
-      <c r="M123" s="212"/>
-      <c r="N123" s="212"/>
-      <c r="O123" s="212"/>
-      <c r="P123" s="212"/>
-      <c r="Q123" s="212"/>
+      <c r="G123" s="202"/>
+      <c r="H123" s="202"/>
+      <c r="I123" s="202"/>
+      <c r="J123" s="202"/>
+      <c r="K123" s="202"/>
+      <c r="L123" s="202"/>
+      <c r="M123" s="202"/>
+      <c r="N123" s="202"/>
+      <c r="O123" s="202"/>
+      <c r="P123" s="202"/>
+      <c r="Q123" s="202"/>
     </row>
     <row r="124" spans="2:17">
       <c r="B124" s="87"/>
       <c r="E124" s="91" t="s">
         <v>389</v>
       </c>
-      <c r="F124" s="212" t="s">
+      <c r="F124" s="202" t="s">
         <v>203</v>
       </c>
-      <c r="G124" s="212"/>
-      <c r="H124" s="212"/>
-      <c r="I124" s="212"/>
-      <c r="J124" s="212"/>
-      <c r="K124" s="212"/>
-      <c r="L124" s="212"/>
-      <c r="M124" s="212"/>
-      <c r="N124" s="212"/>
-      <c r="O124" s="212"/>
-      <c r="P124" s="212"/>
-      <c r="Q124" s="212"/>
+      <c r="G124" s="202"/>
+      <c r="H124" s="202"/>
+      <c r="I124" s="202"/>
+      <c r="J124" s="202"/>
+      <c r="K124" s="202"/>
+      <c r="L124" s="202"/>
+      <c r="M124" s="202"/>
+      <c r="N124" s="202"/>
+      <c r="O124" s="202"/>
+      <c r="P124" s="202"/>
+      <c r="Q124" s="202"/>
     </row>
     <row r="125" spans="2:17" ht="17.25" customHeight="1">
       <c r="B125" s="87"/>
       <c r="E125" s="91" t="s">
         <v>413</v>
       </c>
-      <c r="F125" s="227" t="s">
+      <c r="F125" s="201" t="s">
         <v>561</v>
       </c>
-      <c r="G125" s="227"/>
-      <c r="H125" s="227"/>
-      <c r="I125" s="227"/>
-      <c r="J125" s="227"/>
-      <c r="K125" s="227"/>
-      <c r="L125" s="227"/>
-      <c r="M125" s="227"/>
-      <c r="N125" s="227"/>
-      <c r="O125" s="227"/>
-      <c r="P125" s="227"/>
-      <c r="Q125" s="227"/>
+      <c r="G125" s="201"/>
+      <c r="H125" s="201"/>
+      <c r="I125" s="201"/>
+      <c r="J125" s="201"/>
+      <c r="K125" s="201"/>
+      <c r="L125" s="201"/>
+      <c r="M125" s="201"/>
+      <c r="N125" s="201"/>
+      <c r="O125" s="201"/>
+      <c r="P125" s="201"/>
+      <c r="Q125" s="201"/>
     </row>
     <row r="127" spans="2:17">
       <c r="B127" s="90" t="s">
@@ -20004,18 +20004,18 @@
       <c r="G128" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="H128" s="218" t="s">
+      <c r="H128" s="206" t="s">
         <v>281</v>
       </c>
-      <c r="I128" s="218"/>
-      <c r="J128" s="218"/>
-      <c r="K128" s="218"/>
-      <c r="L128" s="218"/>
-      <c r="M128" s="218"/>
-      <c r="N128" s="218"/>
-      <c r="O128" s="218"/>
-      <c r="P128" s="218"/>
-      <c r="Q128" s="218"/>
+      <c r="I128" s="206"/>
+      <c r="J128" s="206"/>
+      <c r="K128" s="206"/>
+      <c r="L128" s="206"/>
+      <c r="M128" s="206"/>
+      <c r="N128" s="206"/>
+      <c r="O128" s="206"/>
+      <c r="P128" s="206"/>
+      <c r="Q128" s="206"/>
     </row>
     <row r="129" spans="2:17">
       <c r="E129" s="91" t="s">
@@ -20041,58 +20041,58 @@
       <c r="E130" s="91" t="s">
         <v>386</v>
       </c>
-      <c r="F130" s="212" t="s">
+      <c r="F130" s="202" t="s">
         <v>202</v>
       </c>
-      <c r="G130" s="212"/>
-      <c r="H130" s="212"/>
-      <c r="I130" s="212"/>
-      <c r="J130" s="212"/>
-      <c r="K130" s="212"/>
-      <c r="L130" s="212"/>
-      <c r="M130" s="212"/>
-      <c r="N130" s="212"/>
-      <c r="O130" s="212"/>
-      <c r="P130" s="212"/>
-      <c r="Q130" s="212"/>
+      <c r="G130" s="202"/>
+      <c r="H130" s="202"/>
+      <c r="I130" s="202"/>
+      <c r="J130" s="202"/>
+      <c r="K130" s="202"/>
+      <c r="L130" s="202"/>
+      <c r="M130" s="202"/>
+      <c r="N130" s="202"/>
+      <c r="O130" s="202"/>
+      <c r="P130" s="202"/>
+      <c r="Q130" s="202"/>
     </row>
     <row r="131" spans="2:17">
       <c r="E131" s="91" t="s">
         <v>389</v>
       </c>
-      <c r="F131" s="212" t="s">
+      <c r="F131" s="202" t="s">
         <v>203</v>
       </c>
-      <c r="G131" s="212"/>
-      <c r="H131" s="212"/>
-      <c r="I131" s="212"/>
-      <c r="J131" s="212"/>
-      <c r="K131" s="212"/>
-      <c r="L131" s="212"/>
-      <c r="M131" s="212"/>
-      <c r="N131" s="212"/>
-      <c r="O131" s="212"/>
-      <c r="P131" s="212"/>
-      <c r="Q131" s="212"/>
+      <c r="G131" s="202"/>
+      <c r="H131" s="202"/>
+      <c r="I131" s="202"/>
+      <c r="J131" s="202"/>
+      <c r="K131" s="202"/>
+      <c r="L131" s="202"/>
+      <c r="M131" s="202"/>
+      <c r="N131" s="202"/>
+      <c r="O131" s="202"/>
+      <c r="P131" s="202"/>
+      <c r="Q131" s="202"/>
     </row>
     <row r="132" spans="2:17" ht="17.25" customHeight="1">
       <c r="E132" s="91" t="s">
         <v>413</v>
       </c>
-      <c r="F132" s="227" t="s">
+      <c r="F132" s="201" t="s">
         <v>561</v>
       </c>
-      <c r="G132" s="227"/>
-      <c r="H132" s="227"/>
-      <c r="I132" s="227"/>
-      <c r="J132" s="227"/>
-      <c r="K132" s="227"/>
-      <c r="L132" s="227"/>
-      <c r="M132" s="227"/>
-      <c r="N132" s="227"/>
-      <c r="O132" s="227"/>
-      <c r="P132" s="227"/>
-      <c r="Q132" s="227"/>
+      <c r="G132" s="201"/>
+      <c r="H132" s="201"/>
+      <c r="I132" s="201"/>
+      <c r="J132" s="201"/>
+      <c r="K132" s="201"/>
+      <c r="L132" s="201"/>
+      <c r="M132" s="201"/>
+      <c r="N132" s="201"/>
+      <c r="O132" s="201"/>
+      <c r="P132" s="201"/>
+      <c r="Q132" s="201"/>
     </row>
     <row r="133" spans="2:17" ht="17.25" customHeight="1">
       <c r="D133" s="89"/>
@@ -20185,20 +20185,20 @@
       <c r="E136" s="91" t="s">
         <v>408</v>
       </c>
-      <c r="F136" s="218" t="s">
+      <c r="F136" s="206" t="s">
         <v>286</v>
       </c>
-      <c r="G136" s="218"/>
-      <c r="H136" s="218"/>
-      <c r="I136" s="218"/>
-      <c r="J136" s="218"/>
-      <c r="K136" s="218"/>
-      <c r="L136" s="218"/>
-      <c r="M136" s="218"/>
-      <c r="N136" s="218"/>
-      <c r="O136" s="218"/>
-      <c r="P136" s="218"/>
-      <c r="Q136" s="218"/>
+      <c r="G136" s="206"/>
+      <c r="H136" s="206"/>
+      <c r="I136" s="206"/>
+      <c r="J136" s="206"/>
+      <c r="K136" s="206"/>
+      <c r="L136" s="206"/>
+      <c r="M136" s="206"/>
+      <c r="N136" s="206"/>
+      <c r="O136" s="206"/>
+      <c r="P136" s="206"/>
+      <c r="Q136" s="206"/>
     </row>
     <row r="137" spans="2:17">
       <c r="E137" s="91" t="s">
@@ -20223,58 +20223,58 @@
       <c r="E138" s="91" t="s">
         <v>386</v>
       </c>
-      <c r="F138" s="212" t="s">
+      <c r="F138" s="202" t="s">
         <v>202</v>
       </c>
-      <c r="G138" s="212"/>
-      <c r="H138" s="212"/>
-      <c r="I138" s="212"/>
-      <c r="J138" s="212"/>
-      <c r="K138" s="212"/>
-      <c r="L138" s="212"/>
-      <c r="M138" s="212"/>
-      <c r="N138" s="212"/>
-      <c r="O138" s="212"/>
-      <c r="P138" s="212"/>
-      <c r="Q138" s="212"/>
+      <c r="G138" s="202"/>
+      <c r="H138" s="202"/>
+      <c r="I138" s="202"/>
+      <c r="J138" s="202"/>
+      <c r="K138" s="202"/>
+      <c r="L138" s="202"/>
+      <c r="M138" s="202"/>
+      <c r="N138" s="202"/>
+      <c r="O138" s="202"/>
+      <c r="P138" s="202"/>
+      <c r="Q138" s="202"/>
     </row>
     <row r="139" spans="2:17">
       <c r="E139" s="91" t="s">
         <v>389</v>
       </c>
-      <c r="F139" s="212" t="s">
+      <c r="F139" s="202" t="s">
         <v>203</v>
       </c>
-      <c r="G139" s="212"/>
-      <c r="H139" s="212"/>
-      <c r="I139" s="212"/>
-      <c r="J139" s="212"/>
-      <c r="K139" s="212"/>
-      <c r="L139" s="212"/>
-      <c r="M139" s="212"/>
-      <c r="N139" s="212"/>
-      <c r="O139" s="212"/>
-      <c r="P139" s="212"/>
-      <c r="Q139" s="212"/>
+      <c r="G139" s="202"/>
+      <c r="H139" s="202"/>
+      <c r="I139" s="202"/>
+      <c r="J139" s="202"/>
+      <c r="K139" s="202"/>
+      <c r="L139" s="202"/>
+      <c r="M139" s="202"/>
+      <c r="N139" s="202"/>
+      <c r="O139" s="202"/>
+      <c r="P139" s="202"/>
+      <c r="Q139" s="202"/>
     </row>
     <row r="140" spans="2:17">
       <c r="E140" s="91" t="s">
         <v>413</v>
       </c>
-      <c r="F140" s="227" t="s">
+      <c r="F140" s="201" t="s">
         <v>561</v>
       </c>
-      <c r="G140" s="227"/>
-      <c r="H140" s="227"/>
-      <c r="I140" s="227"/>
-      <c r="J140" s="227"/>
-      <c r="K140" s="227"/>
-      <c r="L140" s="227"/>
-      <c r="M140" s="227"/>
-      <c r="N140" s="227"/>
-      <c r="O140" s="227"/>
-      <c r="P140" s="227"/>
-      <c r="Q140" s="227"/>
+      <c r="G140" s="201"/>
+      <c r="H140" s="201"/>
+      <c r="I140" s="201"/>
+      <c r="J140" s="201"/>
+      <c r="K140" s="201"/>
+      <c r="L140" s="201"/>
+      <c r="M140" s="201"/>
+      <c r="N140" s="201"/>
+      <c r="O140" s="201"/>
+      <c r="P140" s="201"/>
+      <c r="Q140" s="201"/>
     </row>
     <row r="142" spans="2:17">
       <c r="B142" s="90" t="s">
@@ -20331,20 +20331,20 @@
       <c r="E143" s="91" t="s">
         <v>408</v>
       </c>
-      <c r="F143" s="218" t="s">
+      <c r="F143" s="206" t="s">
         <v>289</v>
       </c>
-      <c r="G143" s="218"/>
-      <c r="H143" s="218"/>
-      <c r="I143" s="218"/>
-      <c r="J143" s="218"/>
-      <c r="K143" s="218"/>
-      <c r="L143" s="218"/>
-      <c r="M143" s="218"/>
-      <c r="N143" s="218"/>
-      <c r="O143" s="218"/>
-      <c r="P143" s="218"/>
-      <c r="Q143" s="218"/>
+      <c r="G143" s="206"/>
+      <c r="H143" s="206"/>
+      <c r="I143" s="206"/>
+      <c r="J143" s="206"/>
+      <c r="K143" s="206"/>
+      <c r="L143" s="206"/>
+      <c r="M143" s="206"/>
+      <c r="N143" s="206"/>
+      <c r="O143" s="206"/>
+      <c r="P143" s="206"/>
+      <c r="Q143" s="206"/>
     </row>
     <row r="144" spans="2:17">
       <c r="E144" s="91" t="s">
@@ -20369,58 +20369,58 @@
       <c r="E145" s="91" t="s">
         <v>386</v>
       </c>
-      <c r="F145" s="212" t="s">
+      <c r="F145" s="202" t="s">
         <v>202</v>
       </c>
-      <c r="G145" s="212"/>
-      <c r="H145" s="212"/>
-      <c r="I145" s="212"/>
-      <c r="J145" s="212"/>
-      <c r="K145" s="212"/>
-      <c r="L145" s="212"/>
-      <c r="M145" s="212"/>
-      <c r="N145" s="212"/>
-      <c r="O145" s="212"/>
-      <c r="P145" s="212"/>
-      <c r="Q145" s="212"/>
+      <c r="G145" s="202"/>
+      <c r="H145" s="202"/>
+      <c r="I145" s="202"/>
+      <c r="J145" s="202"/>
+      <c r="K145" s="202"/>
+      <c r="L145" s="202"/>
+      <c r="M145" s="202"/>
+      <c r="N145" s="202"/>
+      <c r="O145" s="202"/>
+      <c r="P145" s="202"/>
+      <c r="Q145" s="202"/>
     </row>
     <row r="146" spans="2:17">
       <c r="E146" s="91" t="s">
         <v>389</v>
       </c>
-      <c r="F146" s="212" t="s">
+      <c r="F146" s="202" t="s">
         <v>203</v>
       </c>
-      <c r="G146" s="212"/>
-      <c r="H146" s="212"/>
-      <c r="I146" s="212"/>
-      <c r="J146" s="212"/>
-      <c r="K146" s="212"/>
-      <c r="L146" s="212"/>
-      <c r="M146" s="212"/>
-      <c r="N146" s="212"/>
-      <c r="O146" s="212"/>
-      <c r="P146" s="212"/>
-      <c r="Q146" s="212"/>
+      <c r="G146" s="202"/>
+      <c r="H146" s="202"/>
+      <c r="I146" s="202"/>
+      <c r="J146" s="202"/>
+      <c r="K146" s="202"/>
+      <c r="L146" s="202"/>
+      <c r="M146" s="202"/>
+      <c r="N146" s="202"/>
+      <c r="O146" s="202"/>
+      <c r="P146" s="202"/>
+      <c r="Q146" s="202"/>
     </row>
     <row r="147" spans="2:17" ht="17.25" customHeight="1">
       <c r="E147" s="91" t="s">
         <v>413</v>
       </c>
-      <c r="F147" s="227" t="s">
+      <c r="F147" s="201" t="s">
         <v>561</v>
       </c>
-      <c r="G147" s="227"/>
-      <c r="H147" s="227"/>
-      <c r="I147" s="227"/>
-      <c r="J147" s="227"/>
-      <c r="K147" s="227"/>
-      <c r="L147" s="227"/>
-      <c r="M147" s="227"/>
-      <c r="N147" s="227"/>
-      <c r="O147" s="227"/>
-      <c r="P147" s="227"/>
-      <c r="Q147" s="227"/>
+      <c r="G147" s="201"/>
+      <c r="H147" s="201"/>
+      <c r="I147" s="201"/>
+      <c r="J147" s="201"/>
+      <c r="K147" s="201"/>
+      <c r="L147" s="201"/>
+      <c r="M147" s="201"/>
+      <c r="N147" s="201"/>
+      <c r="O147" s="201"/>
+      <c r="P147" s="201"/>
+      <c r="Q147" s="201"/>
     </row>
     <row r="149" spans="2:17">
       <c r="B149" s="90" t="s">
@@ -20477,20 +20477,20 @@
       <c r="E150" s="91" t="s">
         <v>408</v>
       </c>
-      <c r="F150" s="218" t="s">
+      <c r="F150" s="206" t="s">
         <v>292</v>
       </c>
-      <c r="G150" s="218"/>
-      <c r="H150" s="218"/>
-      <c r="I150" s="218"/>
-      <c r="J150" s="218"/>
-      <c r="K150" s="218"/>
-      <c r="L150" s="218"/>
-      <c r="M150" s="218"/>
-      <c r="N150" s="218"/>
-      <c r="O150" s="218"/>
-      <c r="P150" s="218"/>
-      <c r="Q150" s="218"/>
+      <c r="G150" s="206"/>
+      <c r="H150" s="206"/>
+      <c r="I150" s="206"/>
+      <c r="J150" s="206"/>
+      <c r="K150" s="206"/>
+      <c r="L150" s="206"/>
+      <c r="M150" s="206"/>
+      <c r="N150" s="206"/>
+      <c r="O150" s="206"/>
+      <c r="P150" s="206"/>
+      <c r="Q150" s="206"/>
     </row>
     <row r="151" spans="2:17">
       <c r="B151" s="87"/>
@@ -20517,60 +20517,60 @@
       <c r="E152" s="91" t="s">
         <v>386</v>
       </c>
-      <c r="F152" s="212" t="s">
+      <c r="F152" s="202" t="s">
         <v>202</v>
       </c>
-      <c r="G152" s="212"/>
-      <c r="H152" s="212"/>
-      <c r="I152" s="212"/>
-      <c r="J152" s="212"/>
-      <c r="K152" s="212"/>
-      <c r="L152" s="212"/>
-      <c r="M152" s="212"/>
-      <c r="N152" s="212"/>
-      <c r="O152" s="212"/>
-      <c r="P152" s="212"/>
-      <c r="Q152" s="212"/>
+      <c r="G152" s="202"/>
+      <c r="H152" s="202"/>
+      <c r="I152" s="202"/>
+      <c r="J152" s="202"/>
+      <c r="K152" s="202"/>
+      <c r="L152" s="202"/>
+      <c r="M152" s="202"/>
+      <c r="N152" s="202"/>
+      <c r="O152" s="202"/>
+      <c r="P152" s="202"/>
+      <c r="Q152" s="202"/>
     </row>
     <row r="153" spans="2:17">
       <c r="B153" s="87"/>
       <c r="E153" s="91" t="s">
         <v>389</v>
       </c>
-      <c r="F153" s="212" t="s">
+      <c r="F153" s="202" t="s">
         <v>203</v>
       </c>
-      <c r="G153" s="212"/>
-      <c r="H153" s="212"/>
-      <c r="I153" s="212"/>
-      <c r="J153" s="212"/>
-      <c r="K153" s="212"/>
-      <c r="L153" s="212"/>
-      <c r="M153" s="212"/>
-      <c r="N153" s="212"/>
-      <c r="O153" s="212"/>
-      <c r="P153" s="212"/>
-      <c r="Q153" s="212"/>
+      <c r="G153" s="202"/>
+      <c r="H153" s="202"/>
+      <c r="I153" s="202"/>
+      <c r="J153" s="202"/>
+      <c r="K153" s="202"/>
+      <c r="L153" s="202"/>
+      <c r="M153" s="202"/>
+      <c r="N153" s="202"/>
+      <c r="O153" s="202"/>
+      <c r="P153" s="202"/>
+      <c r="Q153" s="202"/>
     </row>
     <row r="154" spans="2:17">
       <c r="B154" s="87"/>
       <c r="E154" s="91" t="s">
         <v>413</v>
       </c>
-      <c r="F154" s="227" t="s">
+      <c r="F154" s="201" t="s">
         <v>561</v>
       </c>
-      <c r="G154" s="227"/>
-      <c r="H154" s="227"/>
-      <c r="I154" s="227"/>
-      <c r="J154" s="227"/>
-      <c r="K154" s="227"/>
-      <c r="L154" s="227"/>
-      <c r="M154" s="227"/>
-      <c r="N154" s="227"/>
-      <c r="O154" s="227"/>
-      <c r="P154" s="227"/>
-      <c r="Q154" s="227"/>
+      <c r="G154" s="201"/>
+      <c r="H154" s="201"/>
+      <c r="I154" s="201"/>
+      <c r="J154" s="201"/>
+      <c r="K154" s="201"/>
+      <c r="L154" s="201"/>
+      <c r="M154" s="201"/>
+      <c r="N154" s="201"/>
+      <c r="O154" s="201"/>
+      <c r="P154" s="201"/>
+      <c r="Q154" s="201"/>
     </row>
     <row r="156" spans="2:17">
       <c r="B156" s="90" t="s">
@@ -20639,16 +20639,16 @@
       <c r="I157" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="J157" s="218" t="s">
+      <c r="J157" s="206" t="s">
         <v>295</v>
       </c>
-      <c r="K157" s="218"/>
-      <c r="L157" s="218"/>
-      <c r="M157" s="218"/>
-      <c r="N157" s="218"/>
-      <c r="O157" s="218"/>
-      <c r="P157" s="218"/>
-      <c r="Q157" s="218"/>
+      <c r="K157" s="206"/>
+      <c r="L157" s="206"/>
+      <c r="M157" s="206"/>
+      <c r="N157" s="206"/>
+      <c r="O157" s="206"/>
+      <c r="P157" s="206"/>
+      <c r="Q157" s="206"/>
     </row>
     <row r="158" spans="2:17">
       <c r="E158" s="91" t="s">
@@ -20681,58 +20681,58 @@
       <c r="E159" s="91" t="s">
         <v>386</v>
       </c>
-      <c r="F159" s="212" t="s">
+      <c r="F159" s="202" t="s">
         <v>202</v>
       </c>
-      <c r="G159" s="212"/>
-      <c r="H159" s="212"/>
-      <c r="I159" s="212"/>
-      <c r="J159" s="212"/>
-      <c r="K159" s="212"/>
-      <c r="L159" s="212"/>
-      <c r="M159" s="212"/>
-      <c r="N159" s="212"/>
-      <c r="O159" s="212"/>
-      <c r="P159" s="212"/>
-      <c r="Q159" s="212"/>
+      <c r="G159" s="202"/>
+      <c r="H159" s="202"/>
+      <c r="I159" s="202"/>
+      <c r="J159" s="202"/>
+      <c r="K159" s="202"/>
+      <c r="L159" s="202"/>
+      <c r="M159" s="202"/>
+      <c r="N159" s="202"/>
+      <c r="O159" s="202"/>
+      <c r="P159" s="202"/>
+      <c r="Q159" s="202"/>
     </row>
     <row r="160" spans="2:17">
       <c r="E160" s="91" t="s">
         <v>389</v>
       </c>
-      <c r="F160" s="212" t="s">
+      <c r="F160" s="202" t="s">
         <v>203</v>
       </c>
-      <c r="G160" s="212"/>
-      <c r="H160" s="212"/>
-      <c r="I160" s="212"/>
-      <c r="J160" s="212"/>
-      <c r="K160" s="212"/>
-      <c r="L160" s="212"/>
-      <c r="M160" s="212"/>
-      <c r="N160" s="212"/>
-      <c r="O160" s="212"/>
-      <c r="P160" s="212"/>
-      <c r="Q160" s="212"/>
+      <c r="G160" s="202"/>
+      <c r="H160" s="202"/>
+      <c r="I160" s="202"/>
+      <c r="J160" s="202"/>
+      <c r="K160" s="202"/>
+      <c r="L160" s="202"/>
+      <c r="M160" s="202"/>
+      <c r="N160" s="202"/>
+      <c r="O160" s="202"/>
+      <c r="P160" s="202"/>
+      <c r="Q160" s="202"/>
     </row>
     <row r="161" spans="2:17" ht="17.25" customHeight="1">
       <c r="E161" s="91" t="s">
         <v>413</v>
       </c>
-      <c r="F161" s="227" t="s">
+      <c r="F161" s="201" t="s">
         <v>561</v>
       </c>
-      <c r="G161" s="227"/>
-      <c r="H161" s="227"/>
-      <c r="I161" s="227"/>
-      <c r="J161" s="227"/>
-      <c r="K161" s="227"/>
-      <c r="L161" s="227"/>
-      <c r="M161" s="227"/>
-      <c r="N161" s="227"/>
-      <c r="O161" s="227"/>
-      <c r="P161" s="227"/>
-      <c r="Q161" s="227"/>
+      <c r="G161" s="201"/>
+      <c r="H161" s="201"/>
+      <c r="I161" s="201"/>
+      <c r="J161" s="201"/>
+      <c r="K161" s="201"/>
+      <c r="L161" s="201"/>
+      <c r="M161" s="201"/>
+      <c r="N161" s="201"/>
+      <c r="O161" s="201"/>
+      <c r="P161" s="201"/>
+      <c r="Q161" s="201"/>
     </row>
     <row r="163" spans="2:17">
       <c r="B163" s="90" t="s">
@@ -20873,60 +20873,60 @@
       <c r="E166" s="91" t="s">
         <v>386</v>
       </c>
-      <c r="F166" s="212" t="s">
+      <c r="F166" s="202" t="s">
         <v>202</v>
       </c>
-      <c r="G166" s="212"/>
-      <c r="H166" s="212"/>
-      <c r="I166" s="212"/>
-      <c r="J166" s="212"/>
-      <c r="K166" s="212"/>
-      <c r="L166" s="212"/>
-      <c r="M166" s="212"/>
-      <c r="N166" s="212"/>
-      <c r="O166" s="212"/>
-      <c r="P166" s="212"/>
-      <c r="Q166" s="212"/>
+      <c r="G166" s="202"/>
+      <c r="H166" s="202"/>
+      <c r="I166" s="202"/>
+      <c r="J166" s="202"/>
+      <c r="K166" s="202"/>
+      <c r="L166" s="202"/>
+      <c r="M166" s="202"/>
+      <c r="N166" s="202"/>
+      <c r="O166" s="202"/>
+      <c r="P166" s="202"/>
+      <c r="Q166" s="202"/>
     </row>
     <row r="167" spans="2:17">
       <c r="C167" s="87"/>
       <c r="E167" s="91" t="s">
         <v>389</v>
       </c>
-      <c r="F167" s="212" t="s">
+      <c r="F167" s="202" t="s">
         <v>203</v>
       </c>
-      <c r="G167" s="212"/>
-      <c r="H167" s="212"/>
-      <c r="I167" s="212"/>
-      <c r="J167" s="212"/>
-      <c r="K167" s="212"/>
-      <c r="L167" s="212"/>
-      <c r="M167" s="212"/>
-      <c r="N167" s="212"/>
-      <c r="O167" s="212"/>
-      <c r="P167" s="212"/>
-      <c r="Q167" s="212"/>
+      <c r="G167" s="202"/>
+      <c r="H167" s="202"/>
+      <c r="I167" s="202"/>
+      <c r="J167" s="202"/>
+      <c r="K167" s="202"/>
+      <c r="L167" s="202"/>
+      <c r="M167" s="202"/>
+      <c r="N167" s="202"/>
+      <c r="O167" s="202"/>
+      <c r="P167" s="202"/>
+      <c r="Q167" s="202"/>
     </row>
     <row r="168" spans="2:17">
       <c r="C168" s="87"/>
       <c r="E168" s="91" t="s">
         <v>413</v>
       </c>
-      <c r="F168" s="227" t="s">
+      <c r="F168" s="201" t="s">
         <v>561</v>
       </c>
-      <c r="G168" s="227"/>
-      <c r="H168" s="227"/>
-      <c r="I168" s="227"/>
-      <c r="J168" s="227"/>
-      <c r="K168" s="227"/>
-      <c r="L168" s="227"/>
-      <c r="M168" s="227"/>
-      <c r="N168" s="227"/>
-      <c r="O168" s="227"/>
-      <c r="P168" s="227"/>
-      <c r="Q168" s="227"/>
+      <c r="G168" s="201"/>
+      <c r="H168" s="201"/>
+      <c r="I168" s="201"/>
+      <c r="J168" s="201"/>
+      <c r="K168" s="201"/>
+      <c r="L168" s="201"/>
+      <c r="M168" s="201"/>
+      <c r="N168" s="201"/>
+      <c r="O168" s="201"/>
+      <c r="P168" s="201"/>
+      <c r="Q168" s="201"/>
     </row>
     <row r="170" spans="2:17">
       <c r="B170" s="90" t="s">
@@ -21049,144 +21049,99 @@
       <c r="E173" s="91" t="s">
         <v>386</v>
       </c>
-      <c r="F173" s="212" t="s">
+      <c r="F173" s="202" t="s">
         <v>202</v>
       </c>
-      <c r="G173" s="212"/>
-      <c r="H173" s="212"/>
-      <c r="I173" s="212"/>
-      <c r="J173" s="212"/>
-      <c r="K173" s="212"/>
-      <c r="L173" s="212"/>
-      <c r="M173" s="212"/>
-      <c r="N173" s="212"/>
-      <c r="O173" s="212"/>
-      <c r="P173" s="212"/>
-      <c r="Q173" s="212"/>
+      <c r="G173" s="202"/>
+      <c r="H173" s="202"/>
+      <c r="I173" s="202"/>
+      <c r="J173" s="202"/>
+      <c r="K173" s="202"/>
+      <c r="L173" s="202"/>
+      <c r="M173" s="202"/>
+      <c r="N173" s="202"/>
+      <c r="O173" s="202"/>
+      <c r="P173" s="202"/>
+      <c r="Q173" s="202"/>
     </row>
     <row r="174" spans="2:17">
       <c r="E174" s="91" t="s">
         <v>389</v>
       </c>
-      <c r="F174" s="212" t="s">
+      <c r="F174" s="202" t="s">
         <v>203</v>
       </c>
-      <c r="G174" s="212"/>
-      <c r="H174" s="212"/>
-      <c r="I174" s="212"/>
-      <c r="J174" s="212"/>
-      <c r="K174" s="212"/>
-      <c r="L174" s="212"/>
-      <c r="M174" s="212"/>
-      <c r="N174" s="212"/>
-      <c r="O174" s="212"/>
-      <c r="P174" s="212"/>
-      <c r="Q174" s="212"/>
+      <c r="G174" s="202"/>
+      <c r="H174" s="202"/>
+      <c r="I174" s="202"/>
+      <c r="J174" s="202"/>
+      <c r="K174" s="202"/>
+      <c r="L174" s="202"/>
+      <c r="M174" s="202"/>
+      <c r="N174" s="202"/>
+      <c r="O174" s="202"/>
+      <c r="P174" s="202"/>
+      <c r="Q174" s="202"/>
     </row>
     <row r="175" spans="2:17" ht="17.25" customHeight="1">
       <c r="E175" s="91" t="s">
         <v>413</v>
       </c>
-      <c r="F175" s="227" t="s">
+      <c r="F175" s="201" t="s">
         <v>561</v>
       </c>
-      <c r="G175" s="227"/>
-      <c r="H175" s="227"/>
-      <c r="I175" s="227"/>
-      <c r="J175" s="227"/>
-      <c r="K175" s="227"/>
-      <c r="L175" s="227"/>
-      <c r="M175" s="227"/>
-      <c r="N175" s="227"/>
-      <c r="O175" s="227"/>
-      <c r="P175" s="227"/>
-      <c r="Q175" s="227"/>
+      <c r="G175" s="201"/>
+      <c r="H175" s="201"/>
+      <c r="I175" s="201"/>
+      <c r="J175" s="201"/>
+      <c r="K175" s="201"/>
+      <c r="L175" s="201"/>
+      <c r="M175" s="201"/>
+      <c r="N175" s="201"/>
+      <c r="O175" s="201"/>
+      <c r="P175" s="201"/>
+      <c r="Q175" s="201"/>
     </row>
   </sheetData>
   <mergeCells count="135">
-    <mergeCell ref="F168:Q168"/>
-    <mergeCell ref="F173:Q173"/>
-    <mergeCell ref="F174:Q174"/>
-    <mergeCell ref="F175:Q175"/>
-    <mergeCell ref="J158:Q158"/>
-    <mergeCell ref="F159:Q159"/>
-    <mergeCell ref="F160:Q160"/>
-    <mergeCell ref="F161:Q161"/>
-    <mergeCell ref="F166:Q166"/>
-    <mergeCell ref="F167:Q167"/>
-    <mergeCell ref="F150:Q150"/>
-    <mergeCell ref="F151:Q151"/>
-    <mergeCell ref="F152:Q152"/>
-    <mergeCell ref="F153:Q153"/>
-    <mergeCell ref="F154:Q154"/>
-    <mergeCell ref="J157:Q157"/>
-    <mergeCell ref="F140:Q140"/>
-    <mergeCell ref="F143:Q143"/>
-    <mergeCell ref="F144:Q144"/>
-    <mergeCell ref="F145:Q145"/>
-    <mergeCell ref="F146:Q146"/>
-    <mergeCell ref="F147:Q147"/>
-    <mergeCell ref="F131:Q131"/>
-    <mergeCell ref="F132:Q132"/>
-    <mergeCell ref="F136:Q136"/>
-    <mergeCell ref="F137:Q137"/>
-    <mergeCell ref="F138:Q138"/>
-    <mergeCell ref="F139:Q139"/>
-    <mergeCell ref="F123:Q123"/>
-    <mergeCell ref="F124:Q124"/>
-    <mergeCell ref="F125:Q125"/>
-    <mergeCell ref="H128:Q128"/>
-    <mergeCell ref="H129:Q129"/>
-    <mergeCell ref="F130:Q130"/>
-    <mergeCell ref="J115:Q115"/>
-    <mergeCell ref="F116:Q116"/>
-    <mergeCell ref="F117:Q117"/>
-    <mergeCell ref="F118:Q118"/>
-    <mergeCell ref="H121:Q121"/>
-    <mergeCell ref="H122:Q122"/>
-    <mergeCell ref="J107:Q107"/>
-    <mergeCell ref="J108:Q108"/>
-    <mergeCell ref="F109:Q109"/>
-    <mergeCell ref="F110:Q110"/>
-    <mergeCell ref="F111:Q111"/>
-    <mergeCell ref="J114:Q114"/>
-    <mergeCell ref="F97:Q97"/>
-    <mergeCell ref="J100:Q100"/>
-    <mergeCell ref="J101:Q101"/>
-    <mergeCell ref="F102:Q102"/>
-    <mergeCell ref="F103:Q103"/>
-    <mergeCell ref="F104:Q104"/>
-    <mergeCell ref="F89:Q89"/>
-    <mergeCell ref="F90:Q90"/>
-    <mergeCell ref="M93:Q93"/>
-    <mergeCell ref="M94:Q94"/>
-    <mergeCell ref="F95:Q95"/>
-    <mergeCell ref="F96:Q96"/>
-    <mergeCell ref="F81:Q81"/>
-    <mergeCell ref="F82:Q82"/>
-    <mergeCell ref="F83:Q83"/>
-    <mergeCell ref="I86:Q86"/>
-    <mergeCell ref="I87:Q87"/>
-    <mergeCell ref="F88:Q88"/>
-    <mergeCell ref="F67:Q67"/>
-    <mergeCell ref="F68:Q68"/>
-    <mergeCell ref="F69:Q69"/>
-    <mergeCell ref="F74:Q74"/>
-    <mergeCell ref="F75:Q75"/>
-    <mergeCell ref="F76:Q76"/>
-    <mergeCell ref="F60:Q60"/>
-    <mergeCell ref="F61:Q61"/>
-    <mergeCell ref="F62:Q62"/>
-    <mergeCell ref="F65:M65"/>
-    <mergeCell ref="N65:Q65"/>
-    <mergeCell ref="F66:M66"/>
-    <mergeCell ref="N66:Q66"/>
-    <mergeCell ref="F53:Q53"/>
-    <mergeCell ref="F54:Q54"/>
-    <mergeCell ref="F55:Q55"/>
-    <mergeCell ref="H58:M58"/>
-    <mergeCell ref="N58:Q58"/>
-    <mergeCell ref="H59:Q59"/>
+    <mergeCell ref="E11:Q11"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="E3:Q3"/>
+    <mergeCell ref="E4:Q4"/>
+    <mergeCell ref="E5:Q5"/>
+    <mergeCell ref="E8:Q8"/>
+    <mergeCell ref="E9:Q9"/>
+    <mergeCell ref="E10:Q10"/>
+    <mergeCell ref="J24:M24"/>
+    <mergeCell ref="N24:Q24"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="N25:Q25"/>
+    <mergeCell ref="F26:Q26"/>
+    <mergeCell ref="F29:Q29"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="F19:Q19"/>
+    <mergeCell ref="J22:M22"/>
+    <mergeCell ref="N22:Q22"/>
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="N23:Q23"/>
+    <mergeCell ref="F38:Q38"/>
+    <mergeCell ref="F39:Q39"/>
+    <mergeCell ref="F40:Q40"/>
+    <mergeCell ref="F44:H44"/>
+    <mergeCell ref="I44:K44"/>
+    <mergeCell ref="L44:Q44"/>
+    <mergeCell ref="F30:Q30"/>
+    <mergeCell ref="F31:Q31"/>
+    <mergeCell ref="F32:Q32"/>
+    <mergeCell ref="F33:Q33"/>
+    <mergeCell ref="F36:Q36"/>
+    <mergeCell ref="F37:Q37"/>
     <mergeCell ref="F51:G51"/>
     <mergeCell ref="H51:I51"/>
     <mergeCell ref="J51:L51"/>
@@ -21201,44 +21156,89 @@
     <mergeCell ref="F46:Q46"/>
     <mergeCell ref="F47:Q47"/>
     <mergeCell ref="F48:Q48"/>
-    <mergeCell ref="F38:Q38"/>
-    <mergeCell ref="F39:Q39"/>
-    <mergeCell ref="F40:Q40"/>
-    <mergeCell ref="F44:H44"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="L44:Q44"/>
-    <mergeCell ref="F30:Q30"/>
-    <mergeCell ref="F31:Q31"/>
-    <mergeCell ref="F32:Q32"/>
-    <mergeCell ref="F33:Q33"/>
-    <mergeCell ref="F36:Q36"/>
-    <mergeCell ref="F37:Q37"/>
-    <mergeCell ref="J24:M24"/>
-    <mergeCell ref="N24:Q24"/>
-    <mergeCell ref="J25:M25"/>
-    <mergeCell ref="N25:Q25"/>
-    <mergeCell ref="F26:Q26"/>
-    <mergeCell ref="F29:Q29"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="F19:Q19"/>
-    <mergeCell ref="J22:M22"/>
-    <mergeCell ref="N22:Q22"/>
-    <mergeCell ref="J23:M23"/>
-    <mergeCell ref="N23:Q23"/>
-    <mergeCell ref="E11:Q11"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="E3:Q3"/>
-    <mergeCell ref="E4:Q4"/>
-    <mergeCell ref="E5:Q5"/>
-    <mergeCell ref="E8:Q8"/>
-    <mergeCell ref="E9:Q9"/>
-    <mergeCell ref="E10:Q10"/>
+    <mergeCell ref="F60:Q60"/>
+    <mergeCell ref="F61:Q61"/>
+    <mergeCell ref="F62:Q62"/>
+    <mergeCell ref="F65:M65"/>
+    <mergeCell ref="N65:Q65"/>
+    <mergeCell ref="F66:M66"/>
+    <mergeCell ref="N66:Q66"/>
+    <mergeCell ref="F53:Q53"/>
+    <mergeCell ref="F54:Q54"/>
+    <mergeCell ref="F55:Q55"/>
+    <mergeCell ref="H58:M58"/>
+    <mergeCell ref="N58:Q58"/>
+    <mergeCell ref="H59:Q59"/>
+    <mergeCell ref="F81:Q81"/>
+    <mergeCell ref="F82:Q82"/>
+    <mergeCell ref="F83:Q83"/>
+    <mergeCell ref="I86:Q86"/>
+    <mergeCell ref="I87:Q87"/>
+    <mergeCell ref="F88:Q88"/>
+    <mergeCell ref="F67:Q67"/>
+    <mergeCell ref="F68:Q68"/>
+    <mergeCell ref="F69:Q69"/>
+    <mergeCell ref="F74:Q74"/>
+    <mergeCell ref="F75:Q75"/>
+    <mergeCell ref="F76:Q76"/>
+    <mergeCell ref="F97:Q97"/>
+    <mergeCell ref="J100:Q100"/>
+    <mergeCell ref="J101:Q101"/>
+    <mergeCell ref="F102:Q102"/>
+    <mergeCell ref="F103:Q103"/>
+    <mergeCell ref="F104:Q104"/>
+    <mergeCell ref="F89:Q89"/>
+    <mergeCell ref="F90:Q90"/>
+    <mergeCell ref="M93:Q93"/>
+    <mergeCell ref="M94:Q94"/>
+    <mergeCell ref="F95:Q95"/>
+    <mergeCell ref="F96:Q96"/>
+    <mergeCell ref="J115:Q115"/>
+    <mergeCell ref="F116:Q116"/>
+    <mergeCell ref="F117:Q117"/>
+    <mergeCell ref="F118:Q118"/>
+    <mergeCell ref="H121:Q121"/>
+    <mergeCell ref="H122:Q122"/>
+    <mergeCell ref="J107:Q107"/>
+    <mergeCell ref="J108:Q108"/>
+    <mergeCell ref="F109:Q109"/>
+    <mergeCell ref="F110:Q110"/>
+    <mergeCell ref="F111:Q111"/>
+    <mergeCell ref="J114:Q114"/>
+    <mergeCell ref="F131:Q131"/>
+    <mergeCell ref="F132:Q132"/>
+    <mergeCell ref="F136:Q136"/>
+    <mergeCell ref="F137:Q137"/>
+    <mergeCell ref="F138:Q138"/>
+    <mergeCell ref="F139:Q139"/>
+    <mergeCell ref="F123:Q123"/>
+    <mergeCell ref="F124:Q124"/>
+    <mergeCell ref="F125:Q125"/>
+    <mergeCell ref="H128:Q128"/>
+    <mergeCell ref="H129:Q129"/>
+    <mergeCell ref="F130:Q130"/>
+    <mergeCell ref="F150:Q150"/>
+    <mergeCell ref="F151:Q151"/>
+    <mergeCell ref="F152:Q152"/>
+    <mergeCell ref="F153:Q153"/>
+    <mergeCell ref="F154:Q154"/>
+    <mergeCell ref="J157:Q157"/>
+    <mergeCell ref="F140:Q140"/>
+    <mergeCell ref="F143:Q143"/>
+    <mergeCell ref="F144:Q144"/>
+    <mergeCell ref="F145:Q145"/>
+    <mergeCell ref="F146:Q146"/>
+    <mergeCell ref="F147:Q147"/>
+    <mergeCell ref="F168:Q168"/>
+    <mergeCell ref="F173:Q173"/>
+    <mergeCell ref="F174:Q174"/>
+    <mergeCell ref="F175:Q175"/>
+    <mergeCell ref="J158:Q158"/>
+    <mergeCell ref="F159:Q159"/>
+    <mergeCell ref="F160:Q160"/>
+    <mergeCell ref="F161:Q161"/>
+    <mergeCell ref="F166:Q166"/>
+    <mergeCell ref="F167:Q167"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="N128">
@@ -22435,7 +22435,7 @@
       </c>
       <c r="H39" s="17"/>
       <c r="I39" s="17"/>
-      <c r="J39" s="228">
+      <c r="J39" s="157">
         <f>G39/4095</f>
         <v>0.59047619047619049</v>
       </c>
@@ -22459,7 +22459,7 @@
       </c>
       <c r="H40" s="17"/>
       <c r="I40" s="17"/>
-      <c r="J40" s="228">
+      <c r="J40" s="157">
         <f>G40/4095</f>
         <v>0.83345543345543349</v>
       </c>
@@ -22483,7 +22483,7 @@
       </c>
       <c r="H41" s="17"/>
       <c r="I41" s="17"/>
-      <c r="J41" s="228">
+      <c r="J41" s="157">
         <f>G41/4095</f>
         <v>0.97435897435897434</v>
       </c>
